--- a/artfynd/A 38630-2024 artfynd.xlsx
+++ b/artfynd/A 38630-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121388949</v>
+        <v>121388941</v>
       </c>
       <c r="B2" t="n">
-        <v>57348</v>
+        <v>57351</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>435790</v>
+        <v>435759</v>
       </c>
       <c r="R2" t="n">
-        <v>7058674</v>
+        <v>7058331</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121388909</v>
+        <v>121388938</v>
       </c>
       <c r="B3" t="n">
-        <v>57348</v>
+        <v>57351</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>436008</v>
+        <v>435877</v>
       </c>
       <c r="R3" t="n">
-        <v>7057730</v>
+        <v>7058290</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121388910</v>
+        <v>121388916</v>
       </c>
       <c r="B4" t="n">
-        <v>57348</v>
+        <v>57351</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>436007</v>
+        <v>435983</v>
       </c>
       <c r="R4" t="n">
-        <v>7057694</v>
+        <v>7057467</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121388930</v>
+        <v>121388918</v>
       </c>
       <c r="B5" t="n">
-        <v>57348</v>
+        <v>57351</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>435898</v>
+        <v>435965</v>
       </c>
       <c r="R5" t="n">
-        <v>7058090</v>
+        <v>7057511</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121388926</v>
+        <v>121388900</v>
       </c>
       <c r="B6" t="n">
-        <v>57348</v>
+        <v>57351</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>435857</v>
+        <v>435952</v>
       </c>
       <c r="R6" t="n">
-        <v>7057933</v>
+        <v>7058237</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121388938</v>
+        <v>121388945</v>
       </c>
       <c r="B7" t="n">
-        <v>57348</v>
+        <v>57351</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1250,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>435877</v>
+        <v>435762</v>
       </c>
       <c r="R7" t="n">
-        <v>7058290</v>
+        <v>7058369</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1290,7 +1290,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>ringhack färska till äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121388931</v>
+        <v>121388925</v>
       </c>
       <c r="B8" t="n">
-        <v>57348</v>
+        <v>57351</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>435865</v>
+        <v>435850</v>
       </c>
       <c r="R8" t="n">
-        <v>7058110</v>
+        <v>7057928</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1424,10 +1424,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121388942</v>
+        <v>121388953</v>
       </c>
       <c r="B9" t="n">
-        <v>57348</v>
+        <v>57504</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1440,34 +1440,42 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Ångsjön, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>435757</v>
+        <v>435836</v>
       </c>
       <c r="R9" t="n">
-        <v>7058329</v>
+        <v>7058421</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1500,11 +1508,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-11-28</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1531,10 +1534,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121388921</v>
+        <v>121388917</v>
       </c>
       <c r="B10" t="n">
-        <v>57348</v>
+        <v>57351</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1571,10 +1574,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>435927</v>
+        <v>435975</v>
       </c>
       <c r="R10" t="n">
-        <v>7057591</v>
+        <v>7057462</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1611,7 +1614,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1638,10 +1641,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121388902</v>
+        <v>121388895</v>
       </c>
       <c r="B11" t="n">
-        <v>57348</v>
+        <v>57351</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1678,10 +1681,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>435918</v>
+        <v>435847</v>
       </c>
       <c r="R11" t="n">
-        <v>7058070</v>
+        <v>7058626</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1718,7 +1721,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1745,10 +1748,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121388937</v>
+        <v>121388924</v>
       </c>
       <c r="B12" t="n">
-        <v>57348</v>
+        <v>57351</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1785,10 +1788,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>435873</v>
+        <v>435972</v>
       </c>
       <c r="R12" t="n">
-        <v>7058244</v>
+        <v>7057798</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1825,7 +1828,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1852,10 +1855,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121388940</v>
+        <v>121388897</v>
       </c>
       <c r="B13" t="n">
-        <v>57348</v>
+        <v>57351</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1892,10 +1895,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>435760</v>
+        <v>435853</v>
       </c>
       <c r="R13" t="n">
-        <v>7058327</v>
+        <v>7058608</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1959,10 +1962,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121388908</v>
+        <v>121388903</v>
       </c>
       <c r="B14" t="n">
-        <v>57348</v>
+        <v>57351</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1999,10 +2002,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>436018</v>
+        <v>435913</v>
       </c>
       <c r="R14" t="n">
-        <v>7057811</v>
+        <v>7058004</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2039,7 +2042,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2066,10 +2069,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121388935</v>
+        <v>121388915</v>
       </c>
       <c r="B15" t="n">
-        <v>57348</v>
+        <v>57351</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2106,10 +2109,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>435868</v>
+        <v>435989</v>
       </c>
       <c r="R15" t="n">
-        <v>7058203</v>
+        <v>7057570</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2146,7 +2149,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2173,10 +2176,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121388912</v>
+        <v>121388898</v>
       </c>
       <c r="B16" t="n">
-        <v>57348</v>
+        <v>57351</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2213,10 +2216,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>436005</v>
+        <v>435841</v>
       </c>
       <c r="R16" t="n">
-        <v>7057657</v>
+        <v>7058582</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2280,10 +2283,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121388920</v>
+        <v>121388921</v>
       </c>
       <c r="B17" t="n">
-        <v>57348</v>
+        <v>57351</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2320,10 +2323,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>435928</v>
+        <v>435927</v>
       </c>
       <c r="R17" t="n">
-        <v>7057577</v>
+        <v>7057591</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2360,7 +2363,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2387,10 +2390,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121388916</v>
+        <v>121388949</v>
       </c>
       <c r="B18" t="n">
-        <v>57348</v>
+        <v>57351</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2427,10 +2430,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>435983</v>
+        <v>435790</v>
       </c>
       <c r="R18" t="n">
-        <v>7057467</v>
+        <v>7058674</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2467,7 +2470,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2494,10 +2497,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121388936</v>
+        <v>121388946</v>
       </c>
       <c r="B19" t="n">
-        <v>57348</v>
+        <v>57351</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2534,10 +2537,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>435878</v>
+        <v>435771</v>
       </c>
       <c r="R19" t="n">
-        <v>7058242</v>
+        <v>7058417</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2574,7 +2577,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2601,10 +2604,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121388952</v>
+        <v>121388936</v>
       </c>
       <c r="B20" t="n">
-        <v>57348</v>
+        <v>57351</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2641,10 +2644,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>435812</v>
+        <v>435878</v>
       </c>
       <c r="R20" t="n">
-        <v>7058763</v>
+        <v>7058242</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2681,7 +2684,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2708,10 +2711,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121388933</v>
+        <v>121388906</v>
       </c>
       <c r="B21" t="n">
-        <v>57348</v>
+        <v>57351</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2748,10 +2751,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>435884</v>
+        <v>435931</v>
       </c>
       <c r="R21" t="n">
-        <v>7058208</v>
+        <v>7057902</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2815,10 +2818,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121388929</v>
+        <v>121388908</v>
       </c>
       <c r="B22" t="n">
-        <v>57348</v>
+        <v>57351</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2855,10 +2858,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>435896</v>
+        <v>436018</v>
       </c>
       <c r="R22" t="n">
-        <v>7058085</v>
+        <v>7057811</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2895,7 +2898,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2922,10 +2925,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121388917</v>
+        <v>121388940</v>
       </c>
       <c r="B23" t="n">
-        <v>57348</v>
+        <v>57351</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2962,10 +2965,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>435975</v>
+        <v>435760</v>
       </c>
       <c r="R23" t="n">
-        <v>7057462</v>
+        <v>7058327</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3029,10 +3032,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121388897</v>
+        <v>121388919</v>
       </c>
       <c r="B24" t="n">
-        <v>57348</v>
+        <v>57351</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3069,10 +3072,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>435853</v>
+        <v>435924</v>
       </c>
       <c r="R24" t="n">
-        <v>7058608</v>
+        <v>7057563</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3109,7 +3112,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3136,10 +3139,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121388950</v>
+        <v>121388896</v>
       </c>
       <c r="B25" t="n">
-        <v>57348</v>
+        <v>57351</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3176,10 +3179,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>435782</v>
+        <v>435860</v>
       </c>
       <c r="R25" t="n">
-        <v>7058658</v>
+        <v>7058614</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3216,7 +3219,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3243,10 +3246,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121388900</v>
+        <v>121388926</v>
       </c>
       <c r="B26" t="n">
-        <v>57348</v>
+        <v>57351</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3283,10 +3286,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>435952</v>
+        <v>435857</v>
       </c>
       <c r="R26" t="n">
-        <v>7058237</v>
+        <v>7057933</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3323,7 +3326,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3350,10 +3353,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121388895</v>
+        <v>121388942</v>
       </c>
       <c r="B27" t="n">
-        <v>57348</v>
+        <v>57351</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3390,10 +3393,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>435847</v>
+        <v>435757</v>
       </c>
       <c r="R27" t="n">
-        <v>7058626</v>
+        <v>7058329</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3430,7 +3433,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>ringhack färska till äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3457,10 +3460,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121388896</v>
+        <v>121388902</v>
       </c>
       <c r="B28" t="n">
-        <v>57348</v>
+        <v>57351</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3497,10 +3500,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>435860</v>
+        <v>435918</v>
       </c>
       <c r="R28" t="n">
-        <v>7058614</v>
+        <v>7058070</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3537,7 +3540,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3564,10 +3567,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121388893</v>
+        <v>121388911</v>
       </c>
       <c r="B29" t="n">
-        <v>57348</v>
+        <v>57351</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3604,10 +3607,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>435833</v>
+        <v>436006</v>
       </c>
       <c r="R29" t="n">
-        <v>7058665</v>
+        <v>7057655</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3644,7 +3647,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3671,10 +3674,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121388914</v>
+        <v>121388907</v>
       </c>
       <c r="B30" t="n">
-        <v>57348</v>
+        <v>57351</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3711,10 +3714,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>435985</v>
+        <v>435997</v>
       </c>
       <c r="R30" t="n">
-        <v>7057600</v>
+        <v>7057821</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3751,7 +3754,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3778,10 +3781,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121388905</v>
+        <v>121388912</v>
       </c>
       <c r="B31" t="n">
-        <v>57348</v>
+        <v>57351</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3818,10 +3821,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>435889</v>
+        <v>436005</v>
       </c>
       <c r="R31" t="n">
-        <v>7057953</v>
+        <v>7057657</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3858,7 +3861,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3885,10 +3888,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121388906</v>
+        <v>121388909</v>
       </c>
       <c r="B32" t="n">
-        <v>57348</v>
+        <v>57351</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3925,10 +3928,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>435931</v>
+        <v>436008</v>
       </c>
       <c r="R32" t="n">
-        <v>7057902</v>
+        <v>7057730</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3965,7 +3968,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3992,10 +3995,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121388941</v>
+        <v>121388901</v>
       </c>
       <c r="B33" t="n">
-        <v>57348</v>
+        <v>57351</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4032,10 +4035,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>435759</v>
+        <v>435925</v>
       </c>
       <c r="R33" t="n">
-        <v>7058331</v>
+        <v>7058082</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4099,10 +4102,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121388911</v>
+        <v>121388893</v>
       </c>
       <c r="B34" t="n">
-        <v>57348</v>
+        <v>57351</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4139,10 +4142,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>436006</v>
+        <v>435833</v>
       </c>
       <c r="R34" t="n">
-        <v>7057655</v>
+        <v>7058665</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4179,7 +4182,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4206,10 +4209,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121388947</v>
+        <v>121388914</v>
       </c>
       <c r="B35" t="n">
-        <v>57348</v>
+        <v>57351</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4246,10 +4249,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>435805</v>
+        <v>435985</v>
       </c>
       <c r="R35" t="n">
-        <v>7058511</v>
+        <v>7057600</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4286,7 +4289,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4313,10 +4316,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121388915</v>
+        <v>121388939</v>
       </c>
       <c r="B36" t="n">
-        <v>57348</v>
+        <v>57351</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4353,10 +4356,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>435989</v>
+        <v>435870</v>
       </c>
       <c r="R36" t="n">
-        <v>7057570</v>
+        <v>7058288</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4393,7 +4396,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4420,10 +4423,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121388899</v>
+        <v>121388951</v>
       </c>
       <c r="B37" t="n">
-        <v>57348</v>
+        <v>57351</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4460,10 +4463,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>435865</v>
+        <v>435794</v>
       </c>
       <c r="R37" t="n">
-        <v>7058514</v>
+        <v>7058714</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4500,7 +4503,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4527,10 +4530,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121388918</v>
+        <v>121388928</v>
       </c>
       <c r="B38" t="n">
-        <v>57348</v>
+        <v>57351</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4567,10 +4570,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>435965</v>
+        <v>435802</v>
       </c>
       <c r="R38" t="n">
-        <v>7057511</v>
+        <v>7058016</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4607,7 +4610,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4634,10 +4637,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121388946</v>
+        <v>121388920</v>
       </c>
       <c r="B39" t="n">
-        <v>57348</v>
+        <v>57351</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4674,10 +4677,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>435771</v>
+        <v>435928</v>
       </c>
       <c r="R39" t="n">
-        <v>7058417</v>
+        <v>7057577</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4714,7 +4717,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>ringhack färska till äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4741,10 +4744,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121388928</v>
+        <v>121388904</v>
       </c>
       <c r="B40" t="n">
-        <v>57348</v>
+        <v>57351</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4781,10 +4784,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>435802</v>
+        <v>435893</v>
       </c>
       <c r="R40" t="n">
-        <v>7058016</v>
+        <v>7058002</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4821,7 +4824,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4848,10 +4851,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121388924</v>
+        <v>121388927</v>
       </c>
       <c r="B41" t="n">
-        <v>57348</v>
+        <v>57351</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4888,10 +4891,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>435972</v>
+        <v>435855</v>
       </c>
       <c r="R41" t="n">
-        <v>7057798</v>
+        <v>7057933</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4928,7 +4931,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4955,10 +4958,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121388934</v>
+        <v>121388930</v>
       </c>
       <c r="B42" t="n">
-        <v>57348</v>
+        <v>57351</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4995,10 +4998,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>435875</v>
+        <v>435898</v>
       </c>
       <c r="R42" t="n">
-        <v>7058202</v>
+        <v>7058090</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5035,7 +5038,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5062,10 +5065,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121388901</v>
+        <v>121388947</v>
       </c>
       <c r="B43" t="n">
-        <v>57348</v>
+        <v>57351</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5102,10 +5105,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>435925</v>
+        <v>435805</v>
       </c>
       <c r="R43" t="n">
-        <v>7058082</v>
+        <v>7058511</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5169,10 +5172,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121388944</v>
+        <v>121388932</v>
       </c>
       <c r="B44" t="n">
-        <v>57348</v>
+        <v>57351</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5209,10 +5212,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>435747</v>
+        <v>435890</v>
       </c>
       <c r="R44" t="n">
-        <v>7058359</v>
+        <v>7058190</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5249,7 +5252,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>ringhack på tall</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5276,10 +5279,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121388943</v>
+        <v>121388913</v>
       </c>
       <c r="B45" t="n">
-        <v>57348</v>
+        <v>57351</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5316,10 +5319,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>435742</v>
+        <v>436005</v>
       </c>
       <c r="R45" t="n">
-        <v>7058327</v>
+        <v>7057639</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5356,7 +5359,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5383,10 +5386,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121388898</v>
+        <v>121388929</v>
       </c>
       <c r="B46" t="n">
-        <v>57348</v>
+        <v>57351</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5423,10 +5426,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>435841</v>
+        <v>435896</v>
       </c>
       <c r="R46" t="n">
-        <v>7058582</v>
+        <v>7058085</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5463,7 +5466,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5490,10 +5493,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121388923</v>
+        <v>121388933</v>
       </c>
       <c r="B47" t="n">
-        <v>57348</v>
+        <v>57351</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5530,10 +5533,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>435967</v>
+        <v>435884</v>
       </c>
       <c r="R47" t="n">
-        <v>7057788</v>
+        <v>7058208</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5597,10 +5600,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121388948</v>
+        <v>121388952</v>
       </c>
       <c r="B48" t="n">
-        <v>57348</v>
+        <v>57351</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5637,10 +5640,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>435777</v>
+        <v>435812</v>
       </c>
       <c r="R48" t="n">
-        <v>7058633</v>
+        <v>7058763</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5677,7 +5680,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5704,10 +5707,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121388919</v>
+        <v>121388931</v>
       </c>
       <c r="B49" t="n">
-        <v>57348</v>
+        <v>57351</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5744,10 +5747,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>435924</v>
+        <v>435865</v>
       </c>
       <c r="R49" t="n">
-        <v>7057563</v>
+        <v>7058110</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5784,7 +5787,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5811,10 +5814,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121388927</v>
+        <v>121388899</v>
       </c>
       <c r="B50" t="n">
-        <v>57348</v>
+        <v>57351</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5851,10 +5854,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>435855</v>
+        <v>435865</v>
       </c>
       <c r="R50" t="n">
-        <v>7057933</v>
+        <v>7058514</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5891,7 +5894,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5918,10 +5921,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121388903</v>
+        <v>121388894</v>
       </c>
       <c r="B51" t="n">
-        <v>57348</v>
+        <v>57351</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5958,10 +5961,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>435913</v>
+        <v>435836</v>
       </c>
       <c r="R51" t="n">
-        <v>7058004</v>
+        <v>7058627</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5998,7 +6001,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>ringhack färska till äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6025,10 +6028,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121388945</v>
+        <v>121388934</v>
       </c>
       <c r="B52" t="n">
-        <v>57348</v>
+        <v>57351</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6065,10 +6068,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>435762</v>
+        <v>435875</v>
       </c>
       <c r="R52" t="n">
-        <v>7058369</v>
+        <v>7058202</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6132,10 +6135,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121388932</v>
+        <v>121388910</v>
       </c>
       <c r="B53" t="n">
-        <v>57348</v>
+        <v>57351</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6172,10 +6175,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>435890</v>
+        <v>436007</v>
       </c>
       <c r="R53" t="n">
-        <v>7058190</v>
+        <v>7057694</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6212,7 +6215,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6239,10 +6242,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121388907</v>
+        <v>121388937</v>
       </c>
       <c r="B54" t="n">
-        <v>57348</v>
+        <v>57351</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6279,10 +6282,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>435997</v>
+        <v>435873</v>
       </c>
       <c r="R54" t="n">
-        <v>7057821</v>
+        <v>7058244</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6319,7 +6322,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6346,10 +6349,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121388953</v>
+        <v>121388905</v>
       </c>
       <c r="B55" t="n">
-        <v>57501</v>
+        <v>57351</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6362,42 +6365,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Ångsjön, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>435836</v>
+        <v>435889</v>
       </c>
       <c r="R55" t="n">
-        <v>7058421</v>
+        <v>7057953</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6430,6 +6425,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2024-11-28</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6456,10 +6456,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121388925</v>
+        <v>121388950</v>
       </c>
       <c r="B56" t="n">
-        <v>57348</v>
+        <v>57351</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6496,10 +6496,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>435850</v>
+        <v>435782</v>
       </c>
       <c r="R56" t="n">
-        <v>7057928</v>
+        <v>7058658</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6536,7 +6536,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6563,10 +6563,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121388904</v>
+        <v>121388935</v>
       </c>
       <c r="B57" t="n">
-        <v>57348</v>
+        <v>57351</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6603,10 +6603,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>435893</v>
+        <v>435868</v>
       </c>
       <c r="R57" t="n">
-        <v>7058002</v>
+        <v>7058203</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6643,7 +6643,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6670,10 +6670,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121388951</v>
+        <v>121388943</v>
       </c>
       <c r="B58" t="n">
-        <v>57348</v>
+        <v>57351</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6710,10 +6710,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>435794</v>
+        <v>435742</v>
       </c>
       <c r="R58" t="n">
-        <v>7058714</v>
+        <v>7058327</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6777,10 +6777,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121388939</v>
+        <v>121388923</v>
       </c>
       <c r="B59" t="n">
-        <v>57348</v>
+        <v>57351</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6817,10 +6817,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>435870</v>
+        <v>435967</v>
       </c>
       <c r="R59" t="n">
-        <v>7058288</v>
+        <v>7057788</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6857,7 +6857,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6884,10 +6884,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121388913</v>
+        <v>121388948</v>
       </c>
       <c r="B60" t="n">
-        <v>57348</v>
+        <v>57351</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6924,10 +6924,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>436005</v>
+        <v>435777</v>
       </c>
       <c r="R60" t="n">
-        <v>7057639</v>
+        <v>7058633</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6964,7 +6964,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6991,10 +6991,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121388894</v>
+        <v>121388944</v>
       </c>
       <c r="B61" t="n">
-        <v>57348</v>
+        <v>57351</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7031,10 +7031,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>435836</v>
+        <v>435747</v>
       </c>
       <c r="R61" t="n">
-        <v>7058627</v>
+        <v>7058359</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7071,7 +7071,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack på tall</t>
         </is>
       </c>
       <c r="AD61" t="b">

--- a/artfynd/A 38630-2024 artfynd.xlsx
+++ b/artfynd/A 38630-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121388941</v>
+        <v>121388949</v>
       </c>
       <c r="B2" t="n">
         <v>57351</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>435759</v>
+        <v>435790</v>
       </c>
       <c r="R2" t="n">
-        <v>7058331</v>
+        <v>7058674</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121388938</v>
+        <v>121388945</v>
       </c>
       <c r="B3" t="n">
         <v>57351</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>435877</v>
+        <v>435762</v>
       </c>
       <c r="R3" t="n">
-        <v>7058290</v>
+        <v>7058369</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>ringhack färska till äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121388916</v>
+        <v>121388897</v>
       </c>
       <c r="B4" t="n">
         <v>57351</v>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>435983</v>
+        <v>435853</v>
       </c>
       <c r="R4" t="n">
-        <v>7057467</v>
+        <v>7058608</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121388918</v>
+        <v>121388930</v>
       </c>
       <c r="B5" t="n">
         <v>57351</v>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>435965</v>
+        <v>435898</v>
       </c>
       <c r="R5" t="n">
-        <v>7057511</v>
+        <v>7058090</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,7 +1103,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121388900</v>
+        <v>121388934</v>
       </c>
       <c r="B6" t="n">
         <v>57351</v>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>435952</v>
+        <v>435875</v>
       </c>
       <c r="R6" t="n">
-        <v>7058237</v>
+        <v>7058202</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,7 +1210,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121388945</v>
+        <v>121388926</v>
       </c>
       <c r="B7" t="n">
         <v>57351</v>
@@ -1250,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>435762</v>
+        <v>435857</v>
       </c>
       <c r="R7" t="n">
-        <v>7058369</v>
+        <v>7057933</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1290,7 +1290,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,7 +1317,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121388925</v>
+        <v>121388918</v>
       </c>
       <c r="B8" t="n">
         <v>57351</v>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>435850</v>
+        <v>435965</v>
       </c>
       <c r="R8" t="n">
-        <v>7057928</v>
+        <v>7057511</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1424,10 +1424,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121388953</v>
+        <v>121388925</v>
       </c>
       <c r="B9" t="n">
-        <v>57504</v>
+        <v>57351</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1440,42 +1440,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Ångsjön, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>435836</v>
+        <v>435850</v>
       </c>
       <c r="R9" t="n">
-        <v>7058421</v>
+        <v>7057928</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1508,6 +1500,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-11-28</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1534,7 +1531,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121388917</v>
+        <v>121388950</v>
       </c>
       <c r="B10" t="n">
         <v>57351</v>
@@ -1574,10 +1571,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>435975</v>
+        <v>435782</v>
       </c>
       <c r="R10" t="n">
-        <v>7057462</v>
+        <v>7058658</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1614,7 +1611,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1641,7 +1638,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121388895</v>
+        <v>121388923</v>
       </c>
       <c r="B11" t="n">
         <v>57351</v>
@@ -1681,10 +1678,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>435847</v>
+        <v>435967</v>
       </c>
       <c r="R11" t="n">
-        <v>7058626</v>
+        <v>7057788</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1721,7 +1718,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>ringhack färska till äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1748,10 +1745,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121388924</v>
+        <v>121388953</v>
       </c>
       <c r="B12" t="n">
-        <v>57351</v>
+        <v>57504</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1764,34 +1761,42 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Ångsjön, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>435972</v>
+        <v>435836</v>
       </c>
       <c r="R12" t="n">
-        <v>7057798</v>
+        <v>7058421</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1824,11 +1829,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-11-28</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1855,7 +1855,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121388897</v>
+        <v>121388912</v>
       </c>
       <c r="B13" t="n">
         <v>57351</v>
@@ -1895,10 +1895,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>435853</v>
+        <v>436005</v>
       </c>
       <c r="R13" t="n">
-        <v>7058608</v>
+        <v>7057657</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1935,7 +1935,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1962,7 +1962,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121388903</v>
+        <v>121388895</v>
       </c>
       <c r="B14" t="n">
         <v>57351</v>
@@ -2002,10 +2002,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>435913</v>
+        <v>435847</v>
       </c>
       <c r="R14" t="n">
-        <v>7058004</v>
+        <v>7058626</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2069,7 +2069,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121388915</v>
+        <v>121388951</v>
       </c>
       <c r="B15" t="n">
         <v>57351</v>
@@ -2109,10 +2109,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>435989</v>
+        <v>435794</v>
       </c>
       <c r="R15" t="n">
-        <v>7057570</v>
+        <v>7058714</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2176,7 +2176,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121388898</v>
+        <v>121388902</v>
       </c>
       <c r="B16" t="n">
         <v>57351</v>
@@ -2216,10 +2216,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>435841</v>
+        <v>435918</v>
       </c>
       <c r="R16" t="n">
-        <v>7058582</v>
+        <v>7058070</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2256,7 +2256,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2283,7 +2283,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121388921</v>
+        <v>121388932</v>
       </c>
       <c r="B17" t="n">
         <v>57351</v>
@@ -2323,10 +2323,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>435927</v>
+        <v>435890</v>
       </c>
       <c r="R17" t="n">
-        <v>7057591</v>
+        <v>7058190</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2363,7 +2363,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2390,7 +2390,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121388949</v>
+        <v>121388935</v>
       </c>
       <c r="B18" t="n">
         <v>57351</v>
@@ -2430,10 +2430,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>435790</v>
+        <v>435868</v>
       </c>
       <c r="R18" t="n">
-        <v>7058674</v>
+        <v>7058203</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2497,7 +2497,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121388946</v>
+        <v>121388914</v>
       </c>
       <c r="B19" t="n">
         <v>57351</v>
@@ -2537,10 +2537,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>435771</v>
+        <v>435985</v>
       </c>
       <c r="R19" t="n">
-        <v>7058417</v>
+        <v>7057600</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2577,7 +2577,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>ringhack färska till äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2604,7 +2604,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121388936</v>
+        <v>121388913</v>
       </c>
       <c r="B20" t="n">
         <v>57351</v>
@@ -2644,10 +2644,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>435878</v>
+        <v>436005</v>
       </c>
       <c r="R20" t="n">
-        <v>7058242</v>
+        <v>7057639</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2684,7 +2684,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2711,7 +2711,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121388906</v>
+        <v>121388915</v>
       </c>
       <c r="B21" t="n">
         <v>57351</v>
@@ -2751,10 +2751,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>435931</v>
+        <v>435989</v>
       </c>
       <c r="R21" t="n">
-        <v>7057902</v>
+        <v>7057570</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2818,7 +2818,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121388908</v>
+        <v>121388904</v>
       </c>
       <c r="B22" t="n">
         <v>57351</v>
@@ -2858,10 +2858,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>436018</v>
+        <v>435893</v>
       </c>
       <c r="R22" t="n">
-        <v>7057811</v>
+        <v>7058002</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2898,7 +2898,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2925,7 +2925,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121388940</v>
+        <v>121388907</v>
       </c>
       <c r="B23" t="n">
         <v>57351</v>
@@ -2965,10 +2965,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>435760</v>
+        <v>435997</v>
       </c>
       <c r="R23" t="n">
-        <v>7058327</v>
+        <v>7057821</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3005,7 +3005,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3032,7 +3032,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121388919</v>
+        <v>121388896</v>
       </c>
       <c r="B24" t="n">
         <v>57351</v>
@@ -3072,10 +3072,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>435924</v>
+        <v>435860</v>
       </c>
       <c r="R24" t="n">
-        <v>7057563</v>
+        <v>7058614</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3139,7 +3139,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121388896</v>
+        <v>121388905</v>
       </c>
       <c r="B25" t="n">
         <v>57351</v>
@@ -3179,10 +3179,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>435860</v>
+        <v>435889</v>
       </c>
       <c r="R25" t="n">
-        <v>7058614</v>
+        <v>7057953</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3219,7 +3219,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3246,7 +3246,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121388926</v>
+        <v>121388940</v>
       </c>
       <c r="B26" t="n">
         <v>57351</v>
@@ -3286,10 +3286,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>435857</v>
+        <v>435760</v>
       </c>
       <c r="R26" t="n">
-        <v>7057933</v>
+        <v>7058327</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3353,7 +3353,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121388942</v>
+        <v>121388946</v>
       </c>
       <c r="B27" t="n">
         <v>57351</v>
@@ -3393,10 +3393,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>435757</v>
+        <v>435771</v>
       </c>
       <c r="R27" t="n">
-        <v>7058329</v>
+        <v>7058417</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3433,7 +3433,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3460,7 +3460,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121388902</v>
+        <v>121388952</v>
       </c>
       <c r="B28" t="n">
         <v>57351</v>
@@ -3500,10 +3500,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>435918</v>
+        <v>435812</v>
       </c>
       <c r="R28" t="n">
-        <v>7058070</v>
+        <v>7058763</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3540,7 +3540,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3674,7 +3674,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121388907</v>
+        <v>121388900</v>
       </c>
       <c r="B30" t="n">
         <v>57351</v>
@@ -3714,10 +3714,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>435997</v>
+        <v>435952</v>
       </c>
       <c r="R30" t="n">
-        <v>7057821</v>
+        <v>7058237</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3781,7 +3781,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121388912</v>
+        <v>121388908</v>
       </c>
       <c r="B31" t="n">
         <v>57351</v>
@@ -3821,10 +3821,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>436005</v>
+        <v>436018</v>
       </c>
       <c r="R31" t="n">
-        <v>7057657</v>
+        <v>7057811</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3888,7 +3888,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121388909</v>
+        <v>121388948</v>
       </c>
       <c r="B32" t="n">
         <v>57351</v>
@@ -3928,10 +3928,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>436008</v>
+        <v>435777</v>
       </c>
       <c r="R32" t="n">
-        <v>7057730</v>
+        <v>7058633</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3968,7 +3968,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3995,7 +3995,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121388901</v>
+        <v>121388920</v>
       </c>
       <c r="B33" t="n">
         <v>57351</v>
@@ -4035,10 +4035,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>435925</v>
+        <v>435928</v>
       </c>
       <c r="R33" t="n">
-        <v>7058082</v>
+        <v>7057577</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4075,7 +4075,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4209,7 +4209,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121388914</v>
+        <v>121388929</v>
       </c>
       <c r="B35" t="n">
         <v>57351</v>
@@ -4249,10 +4249,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>435985</v>
+        <v>435896</v>
       </c>
       <c r="R35" t="n">
-        <v>7057600</v>
+        <v>7058085</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4316,7 +4316,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121388939</v>
+        <v>121388931</v>
       </c>
       <c r="B36" t="n">
         <v>57351</v>
@@ -4356,10 +4356,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>435870</v>
+        <v>435865</v>
       </c>
       <c r="R36" t="n">
-        <v>7058288</v>
+        <v>7058110</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4396,7 +4396,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4423,7 +4423,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121388951</v>
+        <v>121388901</v>
       </c>
       <c r="B37" t="n">
         <v>57351</v>
@@ -4463,10 +4463,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>435794</v>
+        <v>435925</v>
       </c>
       <c r="R37" t="n">
-        <v>7058714</v>
+        <v>7058082</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4530,7 +4530,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121388928</v>
+        <v>121388944</v>
       </c>
       <c r="B38" t="n">
         <v>57351</v>
@@ -4570,10 +4570,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>435802</v>
+        <v>435747</v>
       </c>
       <c r="R38" t="n">
-        <v>7058016</v>
+        <v>7058359</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4610,7 +4610,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack på tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4637,7 +4637,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121388920</v>
+        <v>121388942</v>
       </c>
       <c r="B39" t="n">
         <v>57351</v>
@@ -4677,10 +4677,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>435928</v>
+        <v>435757</v>
       </c>
       <c r="R39" t="n">
-        <v>7057577</v>
+        <v>7058329</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4717,7 +4717,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4744,7 +4744,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121388904</v>
+        <v>121388937</v>
       </c>
       <c r="B40" t="n">
         <v>57351</v>
@@ -4784,10 +4784,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>435893</v>
+        <v>435873</v>
       </c>
       <c r="R40" t="n">
-        <v>7058002</v>
+        <v>7058244</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4824,7 +4824,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4851,7 +4851,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121388927</v>
+        <v>121388906</v>
       </c>
       <c r="B41" t="n">
         <v>57351</v>
@@ -4891,10 +4891,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>435855</v>
+        <v>435931</v>
       </c>
       <c r="R41" t="n">
-        <v>7057933</v>
+        <v>7057902</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4931,7 +4931,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4958,7 +4958,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121388930</v>
+        <v>121388903</v>
       </c>
       <c r="B42" t="n">
         <v>57351</v>
@@ -4998,10 +4998,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>435898</v>
+        <v>435913</v>
       </c>
       <c r="R42" t="n">
-        <v>7058090</v>
+        <v>7058004</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5038,7 +5038,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5065,7 +5065,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121388947</v>
+        <v>121388909</v>
       </c>
       <c r="B43" t="n">
         <v>57351</v>
@@ -5105,10 +5105,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>435805</v>
+        <v>436008</v>
       </c>
       <c r="R43" t="n">
-        <v>7058511</v>
+        <v>7057730</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5172,7 +5172,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121388932</v>
+        <v>121388938</v>
       </c>
       <c r="B44" t="n">
         <v>57351</v>
@@ -5212,10 +5212,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>435890</v>
+        <v>435877</v>
       </c>
       <c r="R44" t="n">
-        <v>7058190</v>
+        <v>7058290</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5252,7 +5252,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5279,7 +5279,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121388913</v>
+        <v>121388943</v>
       </c>
       <c r="B45" t="n">
         <v>57351</v>
@@ -5319,10 +5319,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>436005</v>
+        <v>435742</v>
       </c>
       <c r="R45" t="n">
-        <v>7057639</v>
+        <v>7058327</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5359,7 +5359,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5386,7 +5386,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121388929</v>
+        <v>121388917</v>
       </c>
       <c r="B46" t="n">
         <v>57351</v>
@@ -5426,10 +5426,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>435896</v>
+        <v>435975</v>
       </c>
       <c r="R46" t="n">
-        <v>7058085</v>
+        <v>7057462</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5493,7 +5493,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121388933</v>
+        <v>121388921</v>
       </c>
       <c r="B47" t="n">
         <v>57351</v>
@@ -5533,10 +5533,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>435884</v>
+        <v>435927</v>
       </c>
       <c r="R47" t="n">
-        <v>7058208</v>
+        <v>7057591</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5573,7 +5573,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5600,7 +5600,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121388952</v>
+        <v>121388939</v>
       </c>
       <c r="B48" t="n">
         <v>57351</v>
@@ -5640,10 +5640,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>435812</v>
+        <v>435870</v>
       </c>
       <c r="R48" t="n">
-        <v>7058763</v>
+        <v>7058288</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5680,7 +5680,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5707,7 +5707,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121388931</v>
+        <v>121388928</v>
       </c>
       <c r="B49" t="n">
         <v>57351</v>
@@ -5747,10 +5747,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>435865</v>
+        <v>435802</v>
       </c>
       <c r="R49" t="n">
-        <v>7058110</v>
+        <v>7058016</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5787,7 +5787,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5814,7 +5814,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121388899</v>
+        <v>121388898</v>
       </c>
       <c r="B50" t="n">
         <v>57351</v>
@@ -5854,10 +5854,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>435865</v>
+        <v>435841</v>
       </c>
       <c r="R50" t="n">
-        <v>7058514</v>
+        <v>7058582</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5921,7 +5921,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121388894</v>
+        <v>121388924</v>
       </c>
       <c r="B51" t="n">
         <v>57351</v>
@@ -5961,10 +5961,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>435836</v>
+        <v>435972</v>
       </c>
       <c r="R51" t="n">
-        <v>7058627</v>
+        <v>7057798</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6028,7 +6028,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121388934</v>
+        <v>121388899</v>
       </c>
       <c r="B52" t="n">
         <v>57351</v>
@@ -6068,10 +6068,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>435875</v>
+        <v>435865</v>
       </c>
       <c r="R52" t="n">
-        <v>7058202</v>
+        <v>7058514</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6135,7 +6135,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121388910</v>
+        <v>121388894</v>
       </c>
       <c r="B53" t="n">
         <v>57351</v>
@@ -6175,10 +6175,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>436007</v>
+        <v>435836</v>
       </c>
       <c r="R53" t="n">
-        <v>7057694</v>
+        <v>7058627</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6215,7 +6215,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6242,7 +6242,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121388937</v>
+        <v>121388927</v>
       </c>
       <c r="B54" t="n">
         <v>57351</v>
@@ -6282,10 +6282,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>435873</v>
+        <v>435855</v>
       </c>
       <c r="R54" t="n">
-        <v>7058244</v>
+        <v>7057933</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6322,7 +6322,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6349,7 +6349,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121388905</v>
+        <v>121388919</v>
       </c>
       <c r="B55" t="n">
         <v>57351</v>
@@ -6389,10 +6389,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>435889</v>
+        <v>435924</v>
       </c>
       <c r="R55" t="n">
-        <v>7057953</v>
+        <v>7057563</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6429,7 +6429,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6456,7 +6456,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121388950</v>
+        <v>121388936</v>
       </c>
       <c r="B56" t="n">
         <v>57351</v>
@@ -6496,10 +6496,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>435782</v>
+        <v>435878</v>
       </c>
       <c r="R56" t="n">
-        <v>7058658</v>
+        <v>7058242</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6536,7 +6536,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6563,7 +6563,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121388935</v>
+        <v>121388941</v>
       </c>
       <c r="B57" t="n">
         <v>57351</v>
@@ -6603,10 +6603,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>435868</v>
+        <v>435759</v>
       </c>
       <c r="R57" t="n">
-        <v>7058203</v>
+        <v>7058331</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6643,7 +6643,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6670,7 +6670,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121388943</v>
+        <v>121388947</v>
       </c>
       <c r="B58" t="n">
         <v>57351</v>
@@ -6710,10 +6710,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>435742</v>
+        <v>435805</v>
       </c>
       <c r="R58" t="n">
-        <v>7058327</v>
+        <v>7058511</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6750,7 +6750,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6777,7 +6777,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121388923</v>
+        <v>121388916</v>
       </c>
       <c r="B59" t="n">
         <v>57351</v>
@@ -6817,10 +6817,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>435967</v>
+        <v>435983</v>
       </c>
       <c r="R59" t="n">
-        <v>7057788</v>
+        <v>7057467</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6857,7 +6857,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6884,7 +6884,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121388948</v>
+        <v>121388933</v>
       </c>
       <c r="B60" t="n">
         <v>57351</v>
@@ -6924,10 +6924,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>435777</v>
+        <v>435884</v>
       </c>
       <c r="R60" t="n">
-        <v>7058633</v>
+        <v>7058208</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6991,7 +6991,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121388944</v>
+        <v>121388910</v>
       </c>
       <c r="B61" t="n">
         <v>57351</v>
@@ -7031,10 +7031,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>435747</v>
+        <v>436007</v>
       </c>
       <c r="R61" t="n">
-        <v>7058359</v>
+        <v>7057694</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7071,7 +7071,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>ringhack på tall</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD61" t="b">

--- a/artfynd/A 38630-2024 artfynd.xlsx
+++ b/artfynd/A 38630-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121388949</v>
+        <v>121388919</v>
       </c>
       <c r="B2" t="n">
         <v>57351</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>435790</v>
+        <v>435924</v>
       </c>
       <c r="R2" t="n">
-        <v>7058674</v>
+        <v>7057563</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121388945</v>
+        <v>121388929</v>
       </c>
       <c r="B3" t="n">
         <v>57351</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>435762</v>
+        <v>435896</v>
       </c>
       <c r="R3" t="n">
-        <v>7058369</v>
+        <v>7058085</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121388897</v>
+        <v>121388931</v>
       </c>
       <c r="B4" t="n">
         <v>57351</v>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>435853</v>
+        <v>435865</v>
       </c>
       <c r="R4" t="n">
-        <v>7058608</v>
+        <v>7058110</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121388930</v>
+        <v>121388913</v>
       </c>
       <c r="B5" t="n">
         <v>57351</v>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>435898</v>
+        <v>436005</v>
       </c>
       <c r="R5" t="n">
-        <v>7058090</v>
+        <v>7057639</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,7 +1103,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121388934</v>
+        <v>121388910</v>
       </c>
       <c r="B6" t="n">
         <v>57351</v>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>435875</v>
+        <v>436007</v>
       </c>
       <c r="R6" t="n">
-        <v>7058202</v>
+        <v>7057694</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,7 +1210,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121388926</v>
+        <v>121388938</v>
       </c>
       <c r="B7" t="n">
         <v>57351</v>
@@ -1250,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>435857</v>
+        <v>435877</v>
       </c>
       <c r="R7" t="n">
-        <v>7057933</v>
+        <v>7058290</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1290,7 +1290,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,7 +1317,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121388918</v>
+        <v>121388930</v>
       </c>
       <c r="B8" t="n">
         <v>57351</v>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>435965</v>
+        <v>435898</v>
       </c>
       <c r="R8" t="n">
-        <v>7057511</v>
+        <v>7058090</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1397,7 +1397,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1424,7 +1424,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121388925</v>
+        <v>121388949</v>
       </c>
       <c r="B9" t="n">
         <v>57351</v>
@@ -1464,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>435850</v>
+        <v>435790</v>
       </c>
       <c r="R9" t="n">
-        <v>7057928</v>
+        <v>7058674</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1531,7 +1531,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121388950</v>
+        <v>121388912</v>
       </c>
       <c r="B10" t="n">
         <v>57351</v>
@@ -1571,10 +1571,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>435782</v>
+        <v>436005</v>
       </c>
       <c r="R10" t="n">
-        <v>7058658</v>
+        <v>7057657</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1611,7 +1611,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1638,7 +1638,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121388923</v>
+        <v>121388952</v>
       </c>
       <c r="B11" t="n">
         <v>57351</v>
@@ -1678,10 +1678,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>435967</v>
+        <v>435812</v>
       </c>
       <c r="R11" t="n">
-        <v>7057788</v>
+        <v>7058763</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1718,7 +1718,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1745,10 +1745,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121388953</v>
+        <v>121388906</v>
       </c>
       <c r="B12" t="n">
-        <v>57504</v>
+        <v>57351</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1761,42 +1761,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Ångsjön, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>435836</v>
+        <v>435931</v>
       </c>
       <c r="R12" t="n">
-        <v>7058421</v>
+        <v>7057902</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1829,6 +1821,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-11-28</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1855,7 +1852,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121388912</v>
+        <v>121388923</v>
       </c>
       <c r="B13" t="n">
         <v>57351</v>
@@ -1895,10 +1892,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>436005</v>
+        <v>435967</v>
       </c>
       <c r="R13" t="n">
-        <v>7057657</v>
+        <v>7057788</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1935,7 +1932,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1962,7 +1959,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121388895</v>
+        <v>121388898</v>
       </c>
       <c r="B14" t="n">
         <v>57351</v>
@@ -2002,10 +1999,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>435847</v>
+        <v>435841</v>
       </c>
       <c r="R14" t="n">
-        <v>7058626</v>
+        <v>7058582</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2042,7 +2039,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>ringhack färska till äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2069,7 +2066,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121388951</v>
+        <v>121388893</v>
       </c>
       <c r="B15" t="n">
         <v>57351</v>
@@ -2109,10 +2106,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>435794</v>
+        <v>435833</v>
       </c>
       <c r="R15" t="n">
-        <v>7058714</v>
+        <v>7058665</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2149,7 +2146,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2176,7 +2173,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121388902</v>
+        <v>121388942</v>
       </c>
       <c r="B16" t="n">
         <v>57351</v>
@@ -2216,10 +2213,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>435918</v>
+        <v>435757</v>
       </c>
       <c r="R16" t="n">
-        <v>7058070</v>
+        <v>7058329</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2283,7 +2280,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121388932</v>
+        <v>121388927</v>
       </c>
       <c r="B17" t="n">
         <v>57351</v>
@@ -2323,10 +2320,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>435890</v>
+        <v>435855</v>
       </c>
       <c r="R17" t="n">
-        <v>7058190</v>
+        <v>7057933</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2363,7 +2360,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2390,7 +2387,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121388935</v>
+        <v>121388916</v>
       </c>
       <c r="B18" t="n">
         <v>57351</v>
@@ -2430,10 +2427,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>435868</v>
+        <v>435983</v>
       </c>
       <c r="R18" t="n">
-        <v>7058203</v>
+        <v>7057467</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2470,7 +2467,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2497,7 +2494,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121388914</v>
+        <v>121388936</v>
       </c>
       <c r="B19" t="n">
         <v>57351</v>
@@ -2537,10 +2534,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>435985</v>
+        <v>435878</v>
       </c>
       <c r="R19" t="n">
-        <v>7057600</v>
+        <v>7058242</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2604,7 +2601,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121388913</v>
+        <v>121388926</v>
       </c>
       <c r="B20" t="n">
         <v>57351</v>
@@ -2644,10 +2641,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>436005</v>
+        <v>435857</v>
       </c>
       <c r="R20" t="n">
-        <v>7057639</v>
+        <v>7057933</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2684,7 +2681,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2711,7 +2708,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121388915</v>
+        <v>121388924</v>
       </c>
       <c r="B21" t="n">
         <v>57351</v>
@@ -2751,10 +2748,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>435989</v>
+        <v>435972</v>
       </c>
       <c r="R21" t="n">
-        <v>7057570</v>
+        <v>7057798</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2791,7 +2788,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2818,7 +2815,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121388904</v>
+        <v>121388907</v>
       </c>
       <c r="B22" t="n">
         <v>57351</v>
@@ -2858,10 +2855,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>435893</v>
+        <v>435997</v>
       </c>
       <c r="R22" t="n">
-        <v>7058002</v>
+        <v>7057821</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2898,7 +2895,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2925,7 +2922,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121388907</v>
+        <v>121388944</v>
       </c>
       <c r="B23" t="n">
         <v>57351</v>
@@ -2965,10 +2962,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>435997</v>
+        <v>435747</v>
       </c>
       <c r="R23" t="n">
-        <v>7057821</v>
+        <v>7058359</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3005,7 +3002,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3032,7 +3029,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121388896</v>
+        <v>121388940</v>
       </c>
       <c r="B24" t="n">
         <v>57351</v>
@@ -3072,10 +3069,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>435860</v>
+        <v>435760</v>
       </c>
       <c r="R24" t="n">
-        <v>7058614</v>
+        <v>7058327</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3112,7 +3109,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3139,7 +3136,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121388905</v>
+        <v>121388935</v>
       </c>
       <c r="B25" t="n">
         <v>57351</v>
@@ -3179,10 +3176,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>435889</v>
+        <v>435868</v>
       </c>
       <c r="R25" t="n">
-        <v>7057953</v>
+        <v>7058203</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3219,7 +3216,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3246,7 +3243,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121388940</v>
+        <v>121388905</v>
       </c>
       <c r="B26" t="n">
         <v>57351</v>
@@ -3286,10 +3283,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>435760</v>
+        <v>435889</v>
       </c>
       <c r="R26" t="n">
-        <v>7058327</v>
+        <v>7057953</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3353,7 +3350,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121388946</v>
+        <v>121388925</v>
       </c>
       <c r="B27" t="n">
         <v>57351</v>
@@ -3393,10 +3390,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>435771</v>
+        <v>435850</v>
       </c>
       <c r="R27" t="n">
-        <v>7058417</v>
+        <v>7057928</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3433,7 +3430,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>ringhack färska till äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3460,10 +3457,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121388952</v>
+        <v>121388953</v>
       </c>
       <c r="B28" t="n">
-        <v>57351</v>
+        <v>57504</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3476,34 +3473,42 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Ångsjön, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>435812</v>
+        <v>435836</v>
       </c>
       <c r="R28" t="n">
-        <v>7058763</v>
+        <v>7058421</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3536,11 +3541,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-11-28</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>ringhack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3567,7 +3567,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121388911</v>
+        <v>121388933</v>
       </c>
       <c r="B29" t="n">
         <v>57351</v>
@@ -3607,10 +3607,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>436006</v>
+        <v>435884</v>
       </c>
       <c r="R29" t="n">
-        <v>7057655</v>
+        <v>7058208</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3647,7 +3647,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3674,7 +3674,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121388900</v>
+        <v>121388928</v>
       </c>
       <c r="B30" t="n">
         <v>57351</v>
@@ -3714,10 +3714,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>435952</v>
+        <v>435802</v>
       </c>
       <c r="R30" t="n">
-        <v>7058237</v>
+        <v>7058016</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3781,7 +3781,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121388908</v>
+        <v>121388920</v>
       </c>
       <c r="B31" t="n">
         <v>57351</v>
@@ -3821,10 +3821,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>436018</v>
+        <v>435928</v>
       </c>
       <c r="R31" t="n">
-        <v>7057811</v>
+        <v>7057577</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3861,7 +3861,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3888,7 +3888,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121388948</v>
+        <v>121388950</v>
       </c>
       <c r="B32" t="n">
         <v>57351</v>
@@ -3928,10 +3928,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>435777</v>
+        <v>435782</v>
       </c>
       <c r="R32" t="n">
-        <v>7058633</v>
+        <v>7058658</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3968,7 +3968,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3995,7 +3995,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121388920</v>
+        <v>121388896</v>
       </c>
       <c r="B33" t="n">
         <v>57351</v>
@@ -4035,10 +4035,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>435928</v>
+        <v>435860</v>
       </c>
       <c r="R33" t="n">
-        <v>7057577</v>
+        <v>7058614</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4075,7 +4075,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4102,7 +4102,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121388893</v>
+        <v>121388914</v>
       </c>
       <c r="B34" t="n">
         <v>57351</v>
@@ -4142,10 +4142,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>435833</v>
+        <v>435985</v>
       </c>
       <c r="R34" t="n">
-        <v>7058665</v>
+        <v>7057600</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4182,7 +4182,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4209,7 +4209,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121388929</v>
+        <v>121388894</v>
       </c>
       <c r="B35" t="n">
         <v>57351</v>
@@ -4249,10 +4249,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>435896</v>
+        <v>435836</v>
       </c>
       <c r="R35" t="n">
-        <v>7058085</v>
+        <v>7058627</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4289,7 +4289,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4316,7 +4316,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121388931</v>
+        <v>121388946</v>
       </c>
       <c r="B36" t="n">
         <v>57351</v>
@@ -4356,10 +4356,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>435865</v>
+        <v>435771</v>
       </c>
       <c r="R36" t="n">
-        <v>7058110</v>
+        <v>7058417</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4396,7 +4396,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4423,7 +4423,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121388901</v>
+        <v>121388947</v>
       </c>
       <c r="B37" t="n">
         <v>57351</v>
@@ -4463,10 +4463,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>435925</v>
+        <v>435805</v>
       </c>
       <c r="R37" t="n">
-        <v>7058082</v>
+        <v>7058511</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4530,7 +4530,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121388944</v>
+        <v>121388917</v>
       </c>
       <c r="B38" t="n">
         <v>57351</v>
@@ -4570,10 +4570,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>435747</v>
+        <v>435975</v>
       </c>
       <c r="R38" t="n">
-        <v>7058359</v>
+        <v>7057462</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4610,7 +4610,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>ringhack på tall</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4637,7 +4637,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121388942</v>
+        <v>121388909</v>
       </c>
       <c r="B39" t="n">
         <v>57351</v>
@@ -4677,10 +4677,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>435757</v>
+        <v>436008</v>
       </c>
       <c r="R39" t="n">
-        <v>7058329</v>
+        <v>7057730</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4717,7 +4717,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4744,7 +4744,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121388937</v>
+        <v>121388918</v>
       </c>
       <c r="B40" t="n">
         <v>57351</v>
@@ -4784,10 +4784,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>435873</v>
+        <v>435965</v>
       </c>
       <c r="R40" t="n">
-        <v>7058244</v>
+        <v>7057511</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4851,7 +4851,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121388906</v>
+        <v>121388939</v>
       </c>
       <c r="B41" t="n">
         <v>57351</v>
@@ -4891,10 +4891,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>435931</v>
+        <v>435870</v>
       </c>
       <c r="R41" t="n">
-        <v>7057902</v>
+        <v>7058288</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4931,7 +4931,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4958,7 +4958,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121388903</v>
+        <v>121388901</v>
       </c>
       <c r="B42" t="n">
         <v>57351</v>
@@ -4998,10 +4998,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>435913</v>
+        <v>435925</v>
       </c>
       <c r="R42" t="n">
-        <v>7058004</v>
+        <v>7058082</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5038,7 +5038,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>ringhack färska till äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5065,7 +5065,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121388909</v>
+        <v>121388945</v>
       </c>
       <c r="B43" t="n">
         <v>57351</v>
@@ -5105,10 +5105,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>436008</v>
+        <v>435762</v>
       </c>
       <c r="R43" t="n">
-        <v>7057730</v>
+        <v>7058369</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5172,7 +5172,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121388938</v>
+        <v>121388921</v>
       </c>
       <c r="B44" t="n">
         <v>57351</v>
@@ -5212,10 +5212,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>435877</v>
+        <v>435927</v>
       </c>
       <c r="R44" t="n">
-        <v>7058290</v>
+        <v>7057591</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5252,7 +5252,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>ringhack färska till äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5279,7 +5279,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121388943</v>
+        <v>121388899</v>
       </c>
       <c r="B45" t="n">
         <v>57351</v>
@@ -5319,10 +5319,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>435742</v>
+        <v>435865</v>
       </c>
       <c r="R45" t="n">
-        <v>7058327</v>
+        <v>7058514</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5359,7 +5359,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5386,7 +5386,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121388917</v>
+        <v>121388903</v>
       </c>
       <c r="B46" t="n">
         <v>57351</v>
@@ -5426,10 +5426,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>435975</v>
+        <v>435913</v>
       </c>
       <c r="R46" t="n">
-        <v>7057462</v>
+        <v>7058004</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5466,7 +5466,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5493,7 +5493,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121388921</v>
+        <v>121388937</v>
       </c>
       <c r="B47" t="n">
         <v>57351</v>
@@ -5533,10 +5533,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>435927</v>
+        <v>435873</v>
       </c>
       <c r="R47" t="n">
-        <v>7057591</v>
+        <v>7058244</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5573,7 +5573,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5600,7 +5600,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121388939</v>
+        <v>121388948</v>
       </c>
       <c r="B48" t="n">
         <v>57351</v>
@@ -5640,10 +5640,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>435870</v>
+        <v>435777</v>
       </c>
       <c r="R48" t="n">
-        <v>7058288</v>
+        <v>7058633</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5680,7 +5680,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5707,7 +5707,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121388928</v>
+        <v>121388911</v>
       </c>
       <c r="B49" t="n">
         <v>57351</v>
@@ -5747,10 +5747,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>435802</v>
+        <v>436006</v>
       </c>
       <c r="R49" t="n">
-        <v>7058016</v>
+        <v>7057655</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5814,7 +5814,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121388898</v>
+        <v>121388897</v>
       </c>
       <c r="B50" t="n">
         <v>57351</v>
@@ -5854,10 +5854,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>435841</v>
+        <v>435853</v>
       </c>
       <c r="R50" t="n">
-        <v>7058582</v>
+        <v>7058608</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5894,7 +5894,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5921,7 +5921,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121388924</v>
+        <v>121388934</v>
       </c>
       <c r="B51" t="n">
         <v>57351</v>
@@ -5961,10 +5961,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>435972</v>
+        <v>435875</v>
       </c>
       <c r="R51" t="n">
-        <v>7057798</v>
+        <v>7058202</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6028,7 +6028,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121388899</v>
+        <v>121388900</v>
       </c>
       <c r="B52" t="n">
         <v>57351</v>
@@ -6068,10 +6068,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>435865</v>
+        <v>435952</v>
       </c>
       <c r="R52" t="n">
-        <v>7058514</v>
+        <v>7058237</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6108,7 +6108,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6135,7 +6135,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121388894</v>
+        <v>121388902</v>
       </c>
       <c r="B53" t="n">
         <v>57351</v>
@@ -6175,10 +6175,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>435836</v>
+        <v>435918</v>
       </c>
       <c r="R53" t="n">
-        <v>7058627</v>
+        <v>7058070</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6215,7 +6215,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6242,7 +6242,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121388927</v>
+        <v>121388941</v>
       </c>
       <c r="B54" t="n">
         <v>57351</v>
@@ -6282,10 +6282,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>435855</v>
+        <v>435759</v>
       </c>
       <c r="R54" t="n">
-        <v>7057933</v>
+        <v>7058331</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6322,7 +6322,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6349,7 +6349,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121388919</v>
+        <v>121388915</v>
       </c>
       <c r="B55" t="n">
         <v>57351</v>
@@ -6389,10 +6389,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>435924</v>
+        <v>435989</v>
       </c>
       <c r="R55" t="n">
-        <v>7057563</v>
+        <v>7057570</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6429,7 +6429,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6456,7 +6456,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121388936</v>
+        <v>121388904</v>
       </c>
       <c r="B56" t="n">
         <v>57351</v>
@@ -6496,10 +6496,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>435878</v>
+        <v>435893</v>
       </c>
       <c r="R56" t="n">
-        <v>7058242</v>
+        <v>7058002</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6536,7 +6536,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6563,7 +6563,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121388941</v>
+        <v>121388943</v>
       </c>
       <c r="B57" t="n">
         <v>57351</v>
@@ -6603,10 +6603,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>435759</v>
+        <v>435742</v>
       </c>
       <c r="R57" t="n">
-        <v>7058331</v>
+        <v>7058327</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6643,7 +6643,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6670,7 +6670,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121388947</v>
+        <v>121388932</v>
       </c>
       <c r="B58" t="n">
         <v>57351</v>
@@ -6710,10 +6710,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>435805</v>
+        <v>435890</v>
       </c>
       <c r="R58" t="n">
-        <v>7058511</v>
+        <v>7058190</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6750,7 +6750,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6777,7 +6777,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121388916</v>
+        <v>121388951</v>
       </c>
       <c r="B59" t="n">
         <v>57351</v>
@@ -6817,10 +6817,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>435983</v>
+        <v>435794</v>
       </c>
       <c r="R59" t="n">
-        <v>7057467</v>
+        <v>7058714</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6857,7 +6857,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6884,7 +6884,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121388933</v>
+        <v>121388895</v>
       </c>
       <c r="B60" t="n">
         <v>57351</v>
@@ -6924,10 +6924,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>435884</v>
+        <v>435847</v>
       </c>
       <c r="R60" t="n">
-        <v>7058208</v>
+        <v>7058626</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6964,7 +6964,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6991,7 +6991,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121388910</v>
+        <v>121388908</v>
       </c>
       <c r="B61" t="n">
         <v>57351</v>
@@ -7031,10 +7031,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>436007</v>
+        <v>436018</v>
       </c>
       <c r="R61" t="n">
-        <v>7057694</v>
+        <v>7057811</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7071,7 +7071,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD61" t="b">

--- a/artfynd/A 38630-2024 artfynd.xlsx
+++ b/artfynd/A 38630-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121388919</v>
+        <v>121388910</v>
       </c>
       <c r="B2" t="n">
         <v>57351</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>435924</v>
+        <v>436007</v>
       </c>
       <c r="R2" t="n">
-        <v>7057563</v>
+        <v>7057694</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121388929</v>
+        <v>121388913</v>
       </c>
       <c r="B3" t="n">
         <v>57351</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>435896</v>
+        <v>436005</v>
       </c>
       <c r="R3" t="n">
-        <v>7058085</v>
+        <v>7057639</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121388931</v>
+        <v>121388898</v>
       </c>
       <c r="B4" t="n">
         <v>57351</v>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>435865</v>
+        <v>435841</v>
       </c>
       <c r="R4" t="n">
-        <v>7058110</v>
+        <v>7058582</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121388913</v>
+        <v>121388912</v>
       </c>
       <c r="B5" t="n">
         <v>57351</v>
@@ -1039,7 +1039,7 @@
         <v>436005</v>
       </c>
       <c r="R5" t="n">
-        <v>7057639</v>
+        <v>7057657</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,7 +1103,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121388910</v>
+        <v>121388934</v>
       </c>
       <c r="B6" t="n">
         <v>57351</v>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>436007</v>
+        <v>435875</v>
       </c>
       <c r="R6" t="n">
-        <v>7057694</v>
+        <v>7058202</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,7 +1210,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121388938</v>
+        <v>121388924</v>
       </c>
       <c r="B7" t="n">
         <v>57351</v>
@@ -1250,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>435877</v>
+        <v>435972</v>
       </c>
       <c r="R7" t="n">
-        <v>7058290</v>
+        <v>7057798</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1290,7 +1290,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>ringhack färska till äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,7 +1317,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121388930</v>
+        <v>121388948</v>
       </c>
       <c r="B8" t="n">
         <v>57351</v>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>435898</v>
+        <v>435777</v>
       </c>
       <c r="R8" t="n">
-        <v>7058090</v>
+        <v>7058633</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1397,7 +1397,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1424,7 +1424,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121388949</v>
+        <v>121388911</v>
       </c>
       <c r="B9" t="n">
         <v>57351</v>
@@ -1464,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>435790</v>
+        <v>436006</v>
       </c>
       <c r="R9" t="n">
-        <v>7058674</v>
+        <v>7057655</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1531,7 +1531,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121388912</v>
+        <v>121388950</v>
       </c>
       <c r="B10" t="n">
         <v>57351</v>
@@ -1571,10 +1571,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>436005</v>
+        <v>435782</v>
       </c>
       <c r="R10" t="n">
-        <v>7057657</v>
+        <v>7058658</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1611,7 +1611,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1638,7 +1638,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121388952</v>
+        <v>121388895</v>
       </c>
       <c r="B11" t="n">
         <v>57351</v>
@@ -1678,10 +1678,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>435812</v>
+        <v>435847</v>
       </c>
       <c r="R11" t="n">
-        <v>7058763</v>
+        <v>7058626</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1718,7 +1718,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1745,7 +1745,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121388906</v>
+        <v>121388941</v>
       </c>
       <c r="B12" t="n">
         <v>57351</v>
@@ -1785,10 +1785,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>435931</v>
+        <v>435759</v>
       </c>
       <c r="R12" t="n">
-        <v>7057902</v>
+        <v>7058331</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1825,7 +1825,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1852,7 +1852,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121388923</v>
+        <v>121388932</v>
       </c>
       <c r="B13" t="n">
         <v>57351</v>
@@ -1892,10 +1892,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>435967</v>
+        <v>435890</v>
       </c>
       <c r="R13" t="n">
-        <v>7057788</v>
+        <v>7058190</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1959,7 +1959,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121388898</v>
+        <v>121388925</v>
       </c>
       <c r="B14" t="n">
         <v>57351</v>
@@ -1999,10 +1999,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>435841</v>
+        <v>435850</v>
       </c>
       <c r="R14" t="n">
-        <v>7058582</v>
+        <v>7057928</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2039,7 +2039,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2066,7 +2066,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121388893</v>
+        <v>121388921</v>
       </c>
       <c r="B15" t="n">
         <v>57351</v>
@@ -2106,10 +2106,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>435833</v>
+        <v>435927</v>
       </c>
       <c r="R15" t="n">
-        <v>7058665</v>
+        <v>7057591</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2173,7 +2173,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121388942</v>
+        <v>121388900</v>
       </c>
       <c r="B16" t="n">
         <v>57351</v>
@@ -2213,10 +2213,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>435757</v>
+        <v>435952</v>
       </c>
       <c r="R16" t="n">
-        <v>7058329</v>
+        <v>7058237</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2280,7 +2280,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121388927</v>
+        <v>121388951</v>
       </c>
       <c r="B17" t="n">
         <v>57351</v>
@@ -2320,10 +2320,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>435855</v>
+        <v>435794</v>
       </c>
       <c r="R17" t="n">
-        <v>7057933</v>
+        <v>7058714</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2360,7 +2360,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2387,7 +2387,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121388916</v>
+        <v>121388933</v>
       </c>
       <c r="B18" t="n">
         <v>57351</v>
@@ -2427,10 +2427,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>435983</v>
+        <v>435884</v>
       </c>
       <c r="R18" t="n">
-        <v>7057467</v>
+        <v>7058208</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2467,7 +2467,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2494,7 +2494,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121388936</v>
+        <v>121388894</v>
       </c>
       <c r="B19" t="n">
         <v>57351</v>
@@ -2534,10 +2534,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>435878</v>
+        <v>435836</v>
       </c>
       <c r="R19" t="n">
-        <v>7058242</v>
+        <v>7058627</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2574,7 +2574,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2601,7 +2601,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121388926</v>
+        <v>121388942</v>
       </c>
       <c r="B20" t="n">
         <v>57351</v>
@@ -2641,10 +2641,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>435857</v>
+        <v>435757</v>
       </c>
       <c r="R20" t="n">
-        <v>7057933</v>
+        <v>7058329</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2681,7 +2681,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2708,7 +2708,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121388924</v>
+        <v>121388916</v>
       </c>
       <c r="B21" t="n">
         <v>57351</v>
@@ -2748,10 +2748,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>435972</v>
+        <v>435983</v>
       </c>
       <c r="R21" t="n">
-        <v>7057798</v>
+        <v>7057467</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2815,7 +2815,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121388907</v>
+        <v>121388906</v>
       </c>
       <c r="B22" t="n">
         <v>57351</v>
@@ -2855,10 +2855,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>435997</v>
+        <v>435931</v>
       </c>
       <c r="R22" t="n">
-        <v>7057821</v>
+        <v>7057902</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2895,7 +2895,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2922,7 +2922,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121388944</v>
+        <v>121388939</v>
       </c>
       <c r="B23" t="n">
         <v>57351</v>
@@ -2962,10 +2962,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>435747</v>
+        <v>435870</v>
       </c>
       <c r="R23" t="n">
-        <v>7058359</v>
+        <v>7058288</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3002,7 +3002,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>ringhack på tall</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3029,10 +3029,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121388940</v>
+        <v>121388953</v>
       </c>
       <c r="B24" t="n">
-        <v>57351</v>
+        <v>57504</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3045,34 +3045,42 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Ångsjön, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>435760</v>
+        <v>435836</v>
       </c>
       <c r="R24" t="n">
-        <v>7058327</v>
+        <v>7058421</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3105,11 +3113,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-11-28</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3136,7 +3139,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121388935</v>
+        <v>121388905</v>
       </c>
       <c r="B25" t="n">
         <v>57351</v>
@@ -3176,10 +3179,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>435868</v>
+        <v>435889</v>
       </c>
       <c r="R25" t="n">
-        <v>7058203</v>
+        <v>7057953</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3216,7 +3219,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3243,7 +3246,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121388905</v>
+        <v>121388952</v>
       </c>
       <c r="B26" t="n">
         <v>57351</v>
@@ -3283,10 +3286,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>435889</v>
+        <v>435812</v>
       </c>
       <c r="R26" t="n">
-        <v>7057953</v>
+        <v>7058763</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3323,7 +3326,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3350,7 +3353,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121388925</v>
+        <v>121388902</v>
       </c>
       <c r="B27" t="n">
         <v>57351</v>
@@ -3390,10 +3393,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>435850</v>
+        <v>435918</v>
       </c>
       <c r="R27" t="n">
-        <v>7057928</v>
+        <v>7058070</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3430,7 +3433,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3457,10 +3460,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121388953</v>
+        <v>121388928</v>
       </c>
       <c r="B28" t="n">
-        <v>57504</v>
+        <v>57351</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3473,42 +3476,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Ångsjön, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>435836</v>
+        <v>435802</v>
       </c>
       <c r="R28" t="n">
-        <v>7058421</v>
+        <v>7058016</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3541,6 +3536,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-11-28</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3567,7 +3567,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121388933</v>
+        <v>121388915</v>
       </c>
       <c r="B29" t="n">
         <v>57351</v>
@@ -3607,10 +3607,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>435884</v>
+        <v>435989</v>
       </c>
       <c r="R29" t="n">
-        <v>7058208</v>
+        <v>7057570</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3674,7 +3674,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121388928</v>
+        <v>121388945</v>
       </c>
       <c r="B30" t="n">
         <v>57351</v>
@@ -3714,10 +3714,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>435802</v>
+        <v>435762</v>
       </c>
       <c r="R30" t="n">
-        <v>7058016</v>
+        <v>7058369</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3754,7 +3754,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3781,7 +3781,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121388920</v>
+        <v>121388949</v>
       </c>
       <c r="B31" t="n">
         <v>57351</v>
@@ -3821,10 +3821,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>435928</v>
+        <v>435790</v>
       </c>
       <c r="R31" t="n">
-        <v>7057577</v>
+        <v>7058674</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3888,7 +3888,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121388950</v>
+        <v>121388914</v>
       </c>
       <c r="B32" t="n">
         <v>57351</v>
@@ -3928,10 +3928,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>435782</v>
+        <v>435985</v>
       </c>
       <c r="R32" t="n">
-        <v>7058658</v>
+        <v>7057600</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3968,7 +3968,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3995,7 +3995,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121388896</v>
+        <v>121388930</v>
       </c>
       <c r="B33" t="n">
         <v>57351</v>
@@ -4035,10 +4035,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>435860</v>
+        <v>435898</v>
       </c>
       <c r="R33" t="n">
-        <v>7058614</v>
+        <v>7058090</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4075,7 +4075,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4102,7 +4102,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121388914</v>
+        <v>121388938</v>
       </c>
       <c r="B34" t="n">
         <v>57351</v>
@@ -4142,10 +4142,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>435985</v>
+        <v>435877</v>
       </c>
       <c r="R34" t="n">
-        <v>7057600</v>
+        <v>7058290</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4182,7 +4182,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4209,7 +4209,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121388894</v>
+        <v>121388899</v>
       </c>
       <c r="B35" t="n">
         <v>57351</v>
@@ -4249,10 +4249,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>435836</v>
+        <v>435865</v>
       </c>
       <c r="R35" t="n">
-        <v>7058627</v>
+        <v>7058514</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4316,7 +4316,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121388946</v>
+        <v>121388929</v>
       </c>
       <c r="B36" t="n">
         <v>57351</v>
@@ -4356,10 +4356,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>435771</v>
+        <v>435896</v>
       </c>
       <c r="R36" t="n">
-        <v>7058417</v>
+        <v>7058085</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4396,7 +4396,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>ringhack färska till äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4530,7 +4530,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121388917</v>
+        <v>121388919</v>
       </c>
       <c r="B38" t="n">
         <v>57351</v>
@@ -4570,10 +4570,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>435975</v>
+        <v>435924</v>
       </c>
       <c r="R38" t="n">
-        <v>7057462</v>
+        <v>7057563</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4610,7 +4610,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4637,7 +4637,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121388909</v>
+        <v>121388903</v>
       </c>
       <c r="B39" t="n">
         <v>57351</v>
@@ -4677,10 +4677,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>436008</v>
+        <v>435913</v>
       </c>
       <c r="R39" t="n">
-        <v>7057730</v>
+        <v>7058004</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4717,7 +4717,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4744,7 +4744,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121388918</v>
+        <v>121388946</v>
       </c>
       <c r="B40" t="n">
         <v>57351</v>
@@ -4784,10 +4784,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>435965</v>
+        <v>435771</v>
       </c>
       <c r="R40" t="n">
-        <v>7057511</v>
+        <v>7058417</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4824,7 +4824,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4851,7 +4851,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121388939</v>
+        <v>121388904</v>
       </c>
       <c r="B41" t="n">
         <v>57351</v>
@@ -4891,10 +4891,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>435870</v>
+        <v>435893</v>
       </c>
       <c r="R41" t="n">
-        <v>7058288</v>
+        <v>7058002</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4931,7 +4931,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4958,7 +4958,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121388901</v>
+        <v>121388927</v>
       </c>
       <c r="B42" t="n">
         <v>57351</v>
@@ -4998,10 +4998,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>435925</v>
+        <v>435855</v>
       </c>
       <c r="R42" t="n">
-        <v>7058082</v>
+        <v>7057933</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5038,7 +5038,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5065,7 +5065,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121388945</v>
+        <v>121388935</v>
       </c>
       <c r="B43" t="n">
         <v>57351</v>
@@ -5105,10 +5105,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>435762</v>
+        <v>435868</v>
       </c>
       <c r="R43" t="n">
-        <v>7058369</v>
+        <v>7058203</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5172,7 +5172,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121388921</v>
+        <v>121388931</v>
       </c>
       <c r="B44" t="n">
         <v>57351</v>
@@ -5212,10 +5212,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>435927</v>
+        <v>435865</v>
       </c>
       <c r="R44" t="n">
-        <v>7057591</v>
+        <v>7058110</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5252,7 +5252,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5279,7 +5279,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121388899</v>
+        <v>121388923</v>
       </c>
       <c r="B45" t="n">
         <v>57351</v>
@@ -5319,10 +5319,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>435865</v>
+        <v>435967</v>
       </c>
       <c r="R45" t="n">
-        <v>7058514</v>
+        <v>7057788</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5359,7 +5359,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5386,7 +5386,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121388903</v>
+        <v>121388909</v>
       </c>
       <c r="B46" t="n">
         <v>57351</v>
@@ -5426,10 +5426,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>435913</v>
+        <v>436008</v>
       </c>
       <c r="R46" t="n">
-        <v>7058004</v>
+        <v>7057730</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5466,7 +5466,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>ringhack färska till äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5493,7 +5493,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121388937</v>
+        <v>121388917</v>
       </c>
       <c r="B47" t="n">
         <v>57351</v>
@@ -5533,10 +5533,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>435873</v>
+        <v>435975</v>
       </c>
       <c r="R47" t="n">
-        <v>7058244</v>
+        <v>7057462</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5600,7 +5600,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121388948</v>
+        <v>121388897</v>
       </c>
       <c r="B48" t="n">
         <v>57351</v>
@@ -5640,10 +5640,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>435777</v>
+        <v>435853</v>
       </c>
       <c r="R48" t="n">
-        <v>7058633</v>
+        <v>7058608</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5707,7 +5707,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121388911</v>
+        <v>121388937</v>
       </c>
       <c r="B49" t="n">
         <v>57351</v>
@@ -5747,10 +5747,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>436006</v>
+        <v>435873</v>
       </c>
       <c r="R49" t="n">
-        <v>7057655</v>
+        <v>7058244</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5787,7 +5787,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5814,7 +5814,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121388897</v>
+        <v>121388918</v>
       </c>
       <c r="B50" t="n">
         <v>57351</v>
@@ -5854,10 +5854,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>435853</v>
+        <v>435965</v>
       </c>
       <c r="R50" t="n">
-        <v>7058608</v>
+        <v>7057511</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5921,7 +5921,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121388934</v>
+        <v>121388940</v>
       </c>
       <c r="B51" t="n">
         <v>57351</v>
@@ -5961,10 +5961,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>435875</v>
+        <v>435760</v>
       </c>
       <c r="R51" t="n">
-        <v>7058202</v>
+        <v>7058327</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6001,7 +6001,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6028,7 +6028,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121388900</v>
+        <v>121388936</v>
       </c>
       <c r="B52" t="n">
         <v>57351</v>
@@ -6068,10 +6068,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>435952</v>
+        <v>435878</v>
       </c>
       <c r="R52" t="n">
-        <v>7058237</v>
+        <v>7058242</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6108,7 +6108,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6135,7 +6135,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121388902</v>
+        <v>121388943</v>
       </c>
       <c r="B53" t="n">
         <v>57351</v>
@@ -6175,10 +6175,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>435918</v>
+        <v>435742</v>
       </c>
       <c r="R53" t="n">
-        <v>7058070</v>
+        <v>7058327</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6215,7 +6215,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6242,7 +6242,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121388941</v>
+        <v>121388896</v>
       </c>
       <c r="B54" t="n">
         <v>57351</v>
@@ -6282,10 +6282,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>435759</v>
+        <v>435860</v>
       </c>
       <c r="R54" t="n">
-        <v>7058331</v>
+        <v>7058614</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6322,7 +6322,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6349,7 +6349,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121388915</v>
+        <v>121388926</v>
       </c>
       <c r="B55" t="n">
         <v>57351</v>
@@ -6389,10 +6389,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>435989</v>
+        <v>435857</v>
       </c>
       <c r="R55" t="n">
-        <v>7057570</v>
+        <v>7057933</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6456,7 +6456,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121388904</v>
+        <v>121388893</v>
       </c>
       <c r="B56" t="n">
         <v>57351</v>
@@ -6496,10 +6496,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>435893</v>
+        <v>435833</v>
       </c>
       <c r="R56" t="n">
-        <v>7058002</v>
+        <v>7058665</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6536,7 +6536,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6563,7 +6563,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121388943</v>
+        <v>121388944</v>
       </c>
       <c r="B57" t="n">
         <v>57351</v>
@@ -6603,10 +6603,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>435742</v>
+        <v>435747</v>
       </c>
       <c r="R57" t="n">
-        <v>7058327</v>
+        <v>7058359</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6643,7 +6643,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack på tall</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6670,7 +6670,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121388932</v>
+        <v>121388907</v>
       </c>
       <c r="B58" t="n">
         <v>57351</v>
@@ -6710,10 +6710,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>435890</v>
+        <v>435997</v>
       </c>
       <c r="R58" t="n">
-        <v>7058190</v>
+        <v>7057821</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6750,7 +6750,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6777,7 +6777,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121388951</v>
+        <v>121388908</v>
       </c>
       <c r="B59" t="n">
         <v>57351</v>
@@ -6817,10 +6817,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>435794</v>
+        <v>436018</v>
       </c>
       <c r="R59" t="n">
-        <v>7058714</v>
+        <v>7057811</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6857,7 +6857,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6884,7 +6884,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121388895</v>
+        <v>121388901</v>
       </c>
       <c r="B60" t="n">
         <v>57351</v>
@@ -6924,10 +6924,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>435847</v>
+        <v>435925</v>
       </c>
       <c r="R60" t="n">
-        <v>7058626</v>
+        <v>7058082</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6964,7 +6964,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>ringhack färska till äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6991,7 +6991,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121388908</v>
+        <v>121388920</v>
       </c>
       <c r="B61" t="n">
         <v>57351</v>
@@ -7031,10 +7031,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>436018</v>
+        <v>435928</v>
       </c>
       <c r="R61" t="n">
-        <v>7057811</v>
+        <v>7057577</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7071,7 +7071,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD61" t="b">

--- a/artfynd/A 38630-2024 artfynd.xlsx
+++ b/artfynd/A 38630-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121388910</v>
+        <v>121388942</v>
       </c>
       <c r="B2" t="n">
-        <v>57351</v>
+        <v>57354</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>436007</v>
+        <v>435757</v>
       </c>
       <c r="R2" t="n">
-        <v>7057694</v>
+        <v>7058329</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121388913</v>
+        <v>121388919</v>
       </c>
       <c r="B3" t="n">
-        <v>57351</v>
+        <v>57354</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>436005</v>
+        <v>435924</v>
       </c>
       <c r="R3" t="n">
-        <v>7057639</v>
+        <v>7057563</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121388898</v>
+        <v>121388921</v>
       </c>
       <c r="B4" t="n">
-        <v>57351</v>
+        <v>57354</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>435841</v>
+        <v>435927</v>
       </c>
       <c r="R4" t="n">
-        <v>7058582</v>
+        <v>7057591</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121388912</v>
+        <v>121388938</v>
       </c>
       <c r="B5" t="n">
-        <v>57351</v>
+        <v>57354</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>436005</v>
+        <v>435877</v>
       </c>
       <c r="R5" t="n">
-        <v>7057657</v>
+        <v>7058290</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121388934</v>
+        <v>121388900</v>
       </c>
       <c r="B6" t="n">
-        <v>57351</v>
+        <v>57354</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>435875</v>
+        <v>435952</v>
       </c>
       <c r="R6" t="n">
-        <v>7058202</v>
+        <v>7058237</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121388924</v>
+        <v>121388901</v>
       </c>
       <c r="B7" t="n">
-        <v>57351</v>
+        <v>57354</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1250,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>435972</v>
+        <v>435925</v>
       </c>
       <c r="R7" t="n">
-        <v>7057798</v>
+        <v>7058082</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1290,7 +1290,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121388948</v>
+        <v>121388905</v>
       </c>
       <c r="B8" t="n">
-        <v>57351</v>
+        <v>57354</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>435777</v>
+        <v>435889</v>
       </c>
       <c r="R8" t="n">
-        <v>7058633</v>
+        <v>7057953</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1424,10 +1424,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121388911</v>
+        <v>121388933</v>
       </c>
       <c r="B9" t="n">
-        <v>57351</v>
+        <v>57354</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1464,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>436006</v>
+        <v>435884</v>
       </c>
       <c r="R9" t="n">
-        <v>7057655</v>
+        <v>7058208</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1531,10 +1531,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121388950</v>
+        <v>121388931</v>
       </c>
       <c r="B10" t="n">
-        <v>57351</v>
+        <v>57354</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1571,10 +1571,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>435782</v>
+        <v>435865</v>
       </c>
       <c r="R10" t="n">
-        <v>7058658</v>
+        <v>7058110</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1611,7 +1611,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1638,10 +1638,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121388895</v>
+        <v>121388909</v>
       </c>
       <c r="B11" t="n">
-        <v>57351</v>
+        <v>57354</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1678,10 +1678,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>435847</v>
+        <v>436008</v>
       </c>
       <c r="R11" t="n">
-        <v>7058626</v>
+        <v>7057730</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1718,7 +1718,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>ringhack färska till äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1745,10 +1745,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121388941</v>
+        <v>121388911</v>
       </c>
       <c r="B12" t="n">
-        <v>57351</v>
+        <v>57354</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1785,10 +1785,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>435759</v>
+        <v>436006</v>
       </c>
       <c r="R12" t="n">
-        <v>7058331</v>
+        <v>7057655</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1852,10 +1852,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121388932</v>
+        <v>121388903</v>
       </c>
       <c r="B13" t="n">
-        <v>57351</v>
+        <v>57354</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1892,10 +1892,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>435890</v>
+        <v>435913</v>
       </c>
       <c r="R13" t="n">
-        <v>7058190</v>
+        <v>7058004</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1959,10 +1959,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121388925</v>
+        <v>121388898</v>
       </c>
       <c r="B14" t="n">
-        <v>57351</v>
+        <v>57354</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1999,10 +1999,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>435850</v>
+        <v>435841</v>
       </c>
       <c r="R14" t="n">
-        <v>7057928</v>
+        <v>7058582</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2039,7 +2039,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2066,10 +2066,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121388921</v>
+        <v>121388907</v>
       </c>
       <c r="B15" t="n">
-        <v>57351</v>
+        <v>57354</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2106,10 +2106,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>435927</v>
+        <v>435997</v>
       </c>
       <c r="R15" t="n">
-        <v>7057591</v>
+        <v>7057821</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2173,10 +2173,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121388900</v>
+        <v>121388916</v>
       </c>
       <c r="B16" t="n">
-        <v>57351</v>
+        <v>57354</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2213,10 +2213,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>435952</v>
+        <v>435983</v>
       </c>
       <c r="R16" t="n">
-        <v>7058237</v>
+        <v>7057467</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2280,10 +2280,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121388951</v>
+        <v>121388924</v>
       </c>
       <c r="B17" t="n">
-        <v>57351</v>
+        <v>57354</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2320,10 +2320,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>435794</v>
+        <v>435972</v>
       </c>
       <c r="R17" t="n">
-        <v>7058714</v>
+        <v>7057798</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2360,7 +2360,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2387,10 +2387,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121388933</v>
+        <v>121388941</v>
       </c>
       <c r="B18" t="n">
-        <v>57351</v>
+        <v>57354</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2427,10 +2427,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>435884</v>
+        <v>435759</v>
       </c>
       <c r="R18" t="n">
-        <v>7058208</v>
+        <v>7058331</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2467,7 +2467,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2494,10 +2494,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121388894</v>
+        <v>121388945</v>
       </c>
       <c r="B19" t="n">
-        <v>57351</v>
+        <v>57354</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2534,10 +2534,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>435836</v>
+        <v>435762</v>
       </c>
       <c r="R19" t="n">
-        <v>7058627</v>
+        <v>7058369</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2601,10 +2601,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121388942</v>
+        <v>121388893</v>
       </c>
       <c r="B20" t="n">
-        <v>57351</v>
+        <v>57354</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2641,10 +2641,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>435757</v>
+        <v>435833</v>
       </c>
       <c r="R20" t="n">
-        <v>7058329</v>
+        <v>7058665</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2681,7 +2681,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2708,10 +2708,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121388916</v>
+        <v>121388927</v>
       </c>
       <c r="B21" t="n">
-        <v>57351</v>
+        <v>57354</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2748,10 +2748,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>435983</v>
+        <v>435855</v>
       </c>
       <c r="R21" t="n">
-        <v>7057467</v>
+        <v>7057933</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2815,10 +2815,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121388906</v>
+        <v>121388897</v>
       </c>
       <c r="B22" t="n">
-        <v>57351</v>
+        <v>57354</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2855,10 +2855,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>435931</v>
+        <v>435853</v>
       </c>
       <c r="R22" t="n">
-        <v>7057902</v>
+        <v>7058608</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2922,10 +2922,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121388939</v>
+        <v>121388937</v>
       </c>
       <c r="B23" t="n">
-        <v>57351</v>
+        <v>57354</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2962,10 +2962,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>435870</v>
+        <v>435873</v>
       </c>
       <c r="R23" t="n">
-        <v>7058288</v>
+        <v>7058244</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3002,7 +3002,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3029,10 +3029,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121388953</v>
+        <v>121388896</v>
       </c>
       <c r="B24" t="n">
-        <v>57504</v>
+        <v>57354</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3045,42 +3045,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Ångsjön, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>435836</v>
+        <v>435860</v>
       </c>
       <c r="R24" t="n">
-        <v>7058421</v>
+        <v>7058614</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3113,6 +3105,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-11-28</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3139,10 +3136,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121388905</v>
+        <v>121388925</v>
       </c>
       <c r="B25" t="n">
-        <v>57351</v>
+        <v>57354</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3179,10 +3176,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>435889</v>
+        <v>435850</v>
       </c>
       <c r="R25" t="n">
-        <v>7057953</v>
+        <v>7057928</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3246,10 +3243,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121388952</v>
+        <v>121388918</v>
       </c>
       <c r="B26" t="n">
-        <v>57351</v>
+        <v>57354</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3286,10 +3283,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>435812</v>
+        <v>435965</v>
       </c>
       <c r="R26" t="n">
-        <v>7058763</v>
+        <v>7057511</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3326,7 +3323,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3353,10 +3350,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121388902</v>
+        <v>121388895</v>
       </c>
       <c r="B27" t="n">
-        <v>57351</v>
+        <v>57354</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3393,10 +3390,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>435918</v>
+        <v>435847</v>
       </c>
       <c r="R27" t="n">
-        <v>7058070</v>
+        <v>7058626</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3433,7 +3430,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3460,10 +3457,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121388928</v>
+        <v>121388951</v>
       </c>
       <c r="B28" t="n">
-        <v>57351</v>
+        <v>57354</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3500,10 +3497,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>435802</v>
+        <v>435794</v>
       </c>
       <c r="R28" t="n">
-        <v>7058016</v>
+        <v>7058714</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3540,7 +3537,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3567,10 +3564,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121388915</v>
+        <v>121388950</v>
       </c>
       <c r="B29" t="n">
-        <v>57351</v>
+        <v>57354</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3607,10 +3604,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>435989</v>
+        <v>435782</v>
       </c>
       <c r="R29" t="n">
-        <v>7057570</v>
+        <v>7058658</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3647,7 +3644,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3674,10 +3671,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121388945</v>
+        <v>121388943</v>
       </c>
       <c r="B30" t="n">
-        <v>57351</v>
+        <v>57354</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3714,10 +3711,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>435762</v>
+        <v>435742</v>
       </c>
       <c r="R30" t="n">
-        <v>7058369</v>
+        <v>7058327</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3754,7 +3751,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3781,10 +3778,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121388949</v>
+        <v>121388940</v>
       </c>
       <c r="B31" t="n">
-        <v>57351</v>
+        <v>57354</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3821,10 +3818,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>435790</v>
+        <v>435760</v>
       </c>
       <c r="R31" t="n">
-        <v>7058674</v>
+        <v>7058327</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3888,10 +3885,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121388914</v>
+        <v>121388899</v>
       </c>
       <c r="B32" t="n">
-        <v>57351</v>
+        <v>57354</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3928,10 +3925,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>435985</v>
+        <v>435865</v>
       </c>
       <c r="R32" t="n">
-        <v>7057600</v>
+        <v>7058514</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3968,7 +3965,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3998,7 +3995,7 @@
         <v>121388930</v>
       </c>
       <c r="B33" t="n">
-        <v>57351</v>
+        <v>57354</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4102,10 +4099,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121388938</v>
+        <v>121388913</v>
       </c>
       <c r="B34" t="n">
-        <v>57351</v>
+        <v>57354</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4142,10 +4139,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>435877</v>
+        <v>436005</v>
       </c>
       <c r="R34" t="n">
-        <v>7058290</v>
+        <v>7057639</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4182,7 +4179,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>ringhack färska till äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4209,10 +4206,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121388899</v>
+        <v>121388912</v>
       </c>
       <c r="B35" t="n">
-        <v>57351</v>
+        <v>57354</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4249,10 +4246,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>435865</v>
+        <v>436005</v>
       </c>
       <c r="R35" t="n">
-        <v>7058514</v>
+        <v>7057657</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4319,7 +4316,7 @@
         <v>121388929</v>
       </c>
       <c r="B36" t="n">
-        <v>57351</v>
+        <v>57354</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4423,10 +4420,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121388947</v>
+        <v>121388952</v>
       </c>
       <c r="B37" t="n">
-        <v>57351</v>
+        <v>57354</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4463,10 +4460,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>435805</v>
+        <v>435812</v>
       </c>
       <c r="R37" t="n">
-        <v>7058511</v>
+        <v>7058763</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4503,7 +4500,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4530,10 +4527,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121388919</v>
+        <v>121388932</v>
       </c>
       <c r="B38" t="n">
-        <v>57351</v>
+        <v>57354</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4570,10 +4567,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>435924</v>
+        <v>435890</v>
       </c>
       <c r="R38" t="n">
-        <v>7057563</v>
+        <v>7058190</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4610,7 +4607,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4637,10 +4634,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121388903</v>
+        <v>121388902</v>
       </c>
       <c r="B39" t="n">
-        <v>57351</v>
+        <v>57354</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4677,10 +4674,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>435913</v>
+        <v>435918</v>
       </c>
       <c r="R39" t="n">
-        <v>7058004</v>
+        <v>7058070</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4717,7 +4714,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>ringhack färska till äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4744,10 +4741,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121388946</v>
+        <v>121388917</v>
       </c>
       <c r="B40" t="n">
-        <v>57351</v>
+        <v>57354</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4784,10 +4781,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>435771</v>
+        <v>435975</v>
       </c>
       <c r="R40" t="n">
-        <v>7058417</v>
+        <v>7057462</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4824,7 +4821,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>ringhack färska till äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4851,10 +4848,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121388904</v>
+        <v>121388944</v>
       </c>
       <c r="B41" t="n">
-        <v>57351</v>
+        <v>57354</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4891,10 +4888,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>435893</v>
+        <v>435747</v>
       </c>
       <c r="R41" t="n">
-        <v>7058002</v>
+        <v>7058359</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4931,7 +4928,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack på tall</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4958,10 +4955,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121388927</v>
+        <v>121388908</v>
       </c>
       <c r="B42" t="n">
-        <v>57351</v>
+        <v>57354</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4998,10 +4995,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>435855</v>
+        <v>436018</v>
       </c>
       <c r="R42" t="n">
-        <v>7057933</v>
+        <v>7057811</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5038,7 +5035,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5065,10 +5062,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121388935</v>
+        <v>121388928</v>
       </c>
       <c r="B43" t="n">
-        <v>57351</v>
+        <v>57354</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5105,10 +5102,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>435868</v>
+        <v>435802</v>
       </c>
       <c r="R43" t="n">
-        <v>7058203</v>
+        <v>7058016</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5145,7 +5142,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5172,10 +5169,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121388931</v>
+        <v>121388894</v>
       </c>
       <c r="B44" t="n">
-        <v>57351</v>
+        <v>57354</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5212,10 +5209,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>435865</v>
+        <v>435836</v>
       </c>
       <c r="R44" t="n">
-        <v>7058110</v>
+        <v>7058627</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5252,7 +5249,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5279,10 +5276,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121388923</v>
+        <v>121388904</v>
       </c>
       <c r="B45" t="n">
-        <v>57351</v>
+        <v>57354</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5319,10 +5316,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>435967</v>
+        <v>435893</v>
       </c>
       <c r="R45" t="n">
-        <v>7057788</v>
+        <v>7058002</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5359,7 +5356,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5386,10 +5383,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121388909</v>
+        <v>121388947</v>
       </c>
       <c r="B46" t="n">
-        <v>57351</v>
+        <v>57354</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5426,10 +5423,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>436008</v>
+        <v>435805</v>
       </c>
       <c r="R46" t="n">
-        <v>7057730</v>
+        <v>7058511</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5466,7 +5463,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5493,10 +5490,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121388917</v>
+        <v>121388949</v>
       </c>
       <c r="B47" t="n">
-        <v>57351</v>
+        <v>57354</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5533,10 +5530,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>435975</v>
+        <v>435790</v>
       </c>
       <c r="R47" t="n">
-        <v>7057462</v>
+        <v>7058674</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5600,10 +5597,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121388897</v>
+        <v>121388946</v>
       </c>
       <c r="B48" t="n">
-        <v>57351</v>
+        <v>57354</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5640,10 +5637,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>435853</v>
+        <v>435771</v>
       </c>
       <c r="R48" t="n">
-        <v>7058608</v>
+        <v>7058417</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5680,7 +5677,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5707,10 +5704,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121388937</v>
+        <v>121388910</v>
       </c>
       <c r="B49" t="n">
-        <v>57351</v>
+        <v>57354</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5747,10 +5744,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>435873</v>
+        <v>436007</v>
       </c>
       <c r="R49" t="n">
-        <v>7058244</v>
+        <v>7057694</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5787,7 +5784,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5814,10 +5811,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121388918</v>
+        <v>121388939</v>
       </c>
       <c r="B50" t="n">
-        <v>57351</v>
+        <v>57354</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5854,10 +5851,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>435965</v>
+        <v>435870</v>
       </c>
       <c r="R50" t="n">
-        <v>7057511</v>
+        <v>7058288</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5894,7 +5891,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5921,10 +5918,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121388940</v>
+        <v>121388915</v>
       </c>
       <c r="B51" t="n">
-        <v>57351</v>
+        <v>57354</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5961,10 +5958,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>435760</v>
+        <v>435989</v>
       </c>
       <c r="R51" t="n">
-        <v>7058327</v>
+        <v>7057570</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6028,10 +6025,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121388936</v>
+        <v>121388914</v>
       </c>
       <c r="B52" t="n">
-        <v>57351</v>
+        <v>57354</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6068,10 +6065,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>435878</v>
+        <v>435985</v>
       </c>
       <c r="R52" t="n">
-        <v>7058242</v>
+        <v>7057600</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6135,10 +6132,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121388943</v>
+        <v>121388923</v>
       </c>
       <c r="B53" t="n">
-        <v>57351</v>
+        <v>57354</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6175,10 +6172,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>435742</v>
+        <v>435967</v>
       </c>
       <c r="R53" t="n">
-        <v>7058327</v>
+        <v>7057788</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6242,10 +6239,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121388896</v>
+        <v>121388936</v>
       </c>
       <c r="B54" t="n">
-        <v>57351</v>
+        <v>57354</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6282,10 +6279,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>435860</v>
+        <v>435878</v>
       </c>
       <c r="R54" t="n">
-        <v>7058614</v>
+        <v>7058242</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6322,7 +6319,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6349,10 +6346,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121388926</v>
+        <v>121388948</v>
       </c>
       <c r="B55" t="n">
-        <v>57351</v>
+        <v>57354</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6389,10 +6386,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>435857</v>
+        <v>435777</v>
       </c>
       <c r="R55" t="n">
-        <v>7057933</v>
+        <v>7058633</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6456,10 +6453,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121388893</v>
+        <v>121388920</v>
       </c>
       <c r="B56" t="n">
-        <v>57351</v>
+        <v>57354</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6496,10 +6493,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>435833</v>
+        <v>435928</v>
       </c>
       <c r="R56" t="n">
-        <v>7058665</v>
+        <v>7057577</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6536,7 +6533,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6563,10 +6560,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121388944</v>
+        <v>121388953</v>
       </c>
       <c r="B57" t="n">
-        <v>57351</v>
+        <v>57507</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6579,34 +6576,42 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Ångsjön, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>435747</v>
+        <v>435836</v>
       </c>
       <c r="R57" t="n">
-        <v>7058359</v>
+        <v>7058421</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6639,11 +6644,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2024-11-28</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>ringhack på tall</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6670,10 +6670,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121388907</v>
+        <v>121388906</v>
       </c>
       <c r="B58" t="n">
-        <v>57351</v>
+        <v>57354</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6710,10 +6710,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>435997</v>
+        <v>435931</v>
       </c>
       <c r="R58" t="n">
-        <v>7057821</v>
+        <v>7057902</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6750,7 +6750,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6777,10 +6777,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121388908</v>
+        <v>121388926</v>
       </c>
       <c r="B59" t="n">
-        <v>57351</v>
+        <v>57354</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6817,10 +6817,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>436018</v>
+        <v>435857</v>
       </c>
       <c r="R59" t="n">
-        <v>7057811</v>
+        <v>7057933</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6857,7 +6857,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6884,10 +6884,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121388901</v>
+        <v>121388935</v>
       </c>
       <c r="B60" t="n">
-        <v>57351</v>
+        <v>57354</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6924,10 +6924,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>435925</v>
+        <v>435868</v>
       </c>
       <c r="R60" t="n">
-        <v>7058082</v>
+        <v>7058203</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6964,7 +6964,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6991,10 +6991,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121388920</v>
+        <v>121388934</v>
       </c>
       <c r="B61" t="n">
-        <v>57351</v>
+        <v>57354</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7031,10 +7031,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>435928</v>
+        <v>435875</v>
       </c>
       <c r="R61" t="n">
-        <v>7057577</v>
+        <v>7058202</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7071,7 +7071,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD61" t="b">

--- a/artfynd/A 38630-2024 artfynd.xlsx
+++ b/artfynd/A 38630-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121388942</v>
+        <v>121388917</v>
       </c>
       <c r="B2" t="n">
         <v>57354</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>435757</v>
+        <v>435975</v>
       </c>
       <c r="R2" t="n">
-        <v>7058329</v>
+        <v>7057462</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121388919</v>
+        <v>121388921</v>
       </c>
       <c r="B3" t="n">
         <v>57354</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>435924</v>
+        <v>435927</v>
       </c>
       <c r="R3" t="n">
-        <v>7057563</v>
+        <v>7057591</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121388921</v>
+        <v>121388924</v>
       </c>
       <c r="B4" t="n">
         <v>57354</v>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>435927</v>
+        <v>435972</v>
       </c>
       <c r="R4" t="n">
-        <v>7057591</v>
+        <v>7057798</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121388938</v>
+        <v>121388897</v>
       </c>
       <c r="B5" t="n">
         <v>57354</v>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>435877</v>
+        <v>435853</v>
       </c>
       <c r="R5" t="n">
-        <v>7058290</v>
+        <v>7058608</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>ringhack färska till äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,7 +1103,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121388900</v>
+        <v>121388929</v>
       </c>
       <c r="B6" t="n">
         <v>57354</v>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>435952</v>
+        <v>435896</v>
       </c>
       <c r="R6" t="n">
-        <v>7058237</v>
+        <v>7058085</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,7 +1210,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121388901</v>
+        <v>121388898</v>
       </c>
       <c r="B7" t="n">
         <v>57354</v>
@@ -1250,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>435925</v>
+        <v>435841</v>
       </c>
       <c r="R7" t="n">
-        <v>7058082</v>
+        <v>7058582</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1290,7 +1290,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,7 +1317,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121388905</v>
+        <v>121388927</v>
       </c>
       <c r="B8" t="n">
         <v>57354</v>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>435889</v>
+        <v>435855</v>
       </c>
       <c r="R8" t="n">
-        <v>7057953</v>
+        <v>7057933</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1397,7 +1397,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1424,7 +1424,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121388933</v>
+        <v>121388946</v>
       </c>
       <c r="B9" t="n">
         <v>57354</v>
@@ -1464,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>435884</v>
+        <v>435771</v>
       </c>
       <c r="R9" t="n">
-        <v>7058208</v>
+        <v>7058417</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1531,7 +1531,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121388931</v>
+        <v>121388939</v>
       </c>
       <c r="B10" t="n">
         <v>57354</v>
@@ -1571,10 +1571,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>435865</v>
+        <v>435870</v>
       </c>
       <c r="R10" t="n">
-        <v>7058110</v>
+        <v>7058288</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1611,7 +1611,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1638,7 +1638,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121388909</v>
+        <v>121388902</v>
       </c>
       <c r="B11" t="n">
         <v>57354</v>
@@ -1678,10 +1678,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>436008</v>
+        <v>435918</v>
       </c>
       <c r="R11" t="n">
-        <v>7057730</v>
+        <v>7058070</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1718,7 +1718,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1745,7 +1745,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121388911</v>
+        <v>121388901</v>
       </c>
       <c r="B12" t="n">
         <v>57354</v>
@@ -1785,10 +1785,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>436006</v>
+        <v>435925</v>
       </c>
       <c r="R12" t="n">
-        <v>7057655</v>
+        <v>7058082</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1852,7 +1852,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121388903</v>
+        <v>121388928</v>
       </c>
       <c r="B13" t="n">
         <v>57354</v>
@@ -1892,10 +1892,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>435913</v>
+        <v>435802</v>
       </c>
       <c r="R13" t="n">
-        <v>7058004</v>
+        <v>7058016</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>ringhack färska till äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1959,7 +1959,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121388898</v>
+        <v>121388931</v>
       </c>
       <c r="B14" t="n">
         <v>57354</v>
@@ -1999,10 +1999,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>435841</v>
+        <v>435865</v>
       </c>
       <c r="R14" t="n">
-        <v>7058582</v>
+        <v>7058110</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2039,7 +2039,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2066,7 +2066,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121388907</v>
+        <v>121388899</v>
       </c>
       <c r="B15" t="n">
         <v>57354</v>
@@ -2106,10 +2106,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>435997</v>
+        <v>435865</v>
       </c>
       <c r="R15" t="n">
-        <v>7057821</v>
+        <v>7058514</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2173,7 +2173,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121388916</v>
+        <v>121388900</v>
       </c>
       <c r="B16" t="n">
         <v>57354</v>
@@ -2213,10 +2213,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>435983</v>
+        <v>435952</v>
       </c>
       <c r="R16" t="n">
-        <v>7057467</v>
+        <v>7058237</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2280,7 +2280,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121388924</v>
+        <v>121388907</v>
       </c>
       <c r="B17" t="n">
         <v>57354</v>
@@ -2320,10 +2320,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>435972</v>
+        <v>435997</v>
       </c>
       <c r="R17" t="n">
-        <v>7057798</v>
+        <v>7057821</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2360,7 +2360,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2387,7 +2387,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121388941</v>
+        <v>121388896</v>
       </c>
       <c r="B18" t="n">
         <v>57354</v>
@@ -2427,10 +2427,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>435759</v>
+        <v>435860</v>
       </c>
       <c r="R18" t="n">
-        <v>7058331</v>
+        <v>7058614</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2467,7 +2467,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2494,7 +2494,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121388945</v>
+        <v>121388908</v>
       </c>
       <c r="B19" t="n">
         <v>57354</v>
@@ -2534,10 +2534,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>435762</v>
+        <v>436018</v>
       </c>
       <c r="R19" t="n">
-        <v>7058369</v>
+        <v>7057811</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2601,7 +2601,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121388893</v>
+        <v>121388915</v>
       </c>
       <c r="B20" t="n">
         <v>57354</v>
@@ -2641,10 +2641,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>435833</v>
+        <v>435989</v>
       </c>
       <c r="R20" t="n">
-        <v>7058665</v>
+        <v>7057570</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2681,7 +2681,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2708,10 +2708,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121388927</v>
+        <v>121388953</v>
       </c>
       <c r="B21" t="n">
-        <v>57354</v>
+        <v>57507</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2724,34 +2724,42 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Ångsjön, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>435855</v>
+        <v>435836</v>
       </c>
       <c r="R21" t="n">
-        <v>7057933</v>
+        <v>7058421</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2784,11 +2792,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-11-28</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2815,7 +2818,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121388897</v>
+        <v>121388933</v>
       </c>
       <c r="B22" t="n">
         <v>57354</v>
@@ -2855,10 +2858,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>435853</v>
+        <v>435884</v>
       </c>
       <c r="R22" t="n">
-        <v>7058608</v>
+        <v>7058208</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2922,7 +2925,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121388937</v>
+        <v>121388906</v>
       </c>
       <c r="B23" t="n">
         <v>57354</v>
@@ -2962,10 +2965,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>435873</v>
+        <v>435931</v>
       </c>
       <c r="R23" t="n">
-        <v>7058244</v>
+        <v>7057902</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3029,7 +3032,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121388896</v>
+        <v>121388911</v>
       </c>
       <c r="B24" t="n">
         <v>57354</v>
@@ -3069,10 +3072,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>435860</v>
+        <v>436006</v>
       </c>
       <c r="R24" t="n">
-        <v>7058614</v>
+        <v>7057655</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3109,7 +3112,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3136,7 +3139,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121388925</v>
+        <v>121388894</v>
       </c>
       <c r="B25" t="n">
         <v>57354</v>
@@ -3176,10 +3179,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>435850</v>
+        <v>435836</v>
       </c>
       <c r="R25" t="n">
-        <v>7057928</v>
+        <v>7058627</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3216,7 +3219,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3243,7 +3246,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121388918</v>
+        <v>121388932</v>
       </c>
       <c r="B26" t="n">
         <v>57354</v>
@@ -3283,10 +3286,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>435965</v>
+        <v>435890</v>
       </c>
       <c r="R26" t="n">
-        <v>7057511</v>
+        <v>7058190</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3350,7 +3353,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121388895</v>
+        <v>121388926</v>
       </c>
       <c r="B27" t="n">
         <v>57354</v>
@@ -3390,10 +3393,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>435847</v>
+        <v>435857</v>
       </c>
       <c r="R27" t="n">
-        <v>7058626</v>
+        <v>7057933</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3430,7 +3433,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>ringhack färska till äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3457,7 +3460,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121388951</v>
+        <v>121388949</v>
       </c>
       <c r="B28" t="n">
         <v>57354</v>
@@ -3497,10 +3500,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>435794</v>
+        <v>435790</v>
       </c>
       <c r="R28" t="n">
-        <v>7058714</v>
+        <v>7058674</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3564,7 +3567,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121388950</v>
+        <v>121388947</v>
       </c>
       <c r="B29" t="n">
         <v>57354</v>
@@ -3604,10 +3607,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>435782</v>
+        <v>435805</v>
       </c>
       <c r="R29" t="n">
-        <v>7058658</v>
+        <v>7058511</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3644,7 +3647,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3671,7 +3674,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121388943</v>
+        <v>121388919</v>
       </c>
       <c r="B30" t="n">
         <v>57354</v>
@@ -3711,10 +3714,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>435742</v>
+        <v>435924</v>
       </c>
       <c r="R30" t="n">
-        <v>7058327</v>
+        <v>7057563</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3751,7 +3754,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3778,7 +3781,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121388940</v>
+        <v>121388941</v>
       </c>
       <c r="B31" t="n">
         <v>57354</v>
@@ -3818,10 +3821,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>435760</v>
+        <v>435759</v>
       </c>
       <c r="R31" t="n">
-        <v>7058327</v>
+        <v>7058331</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3858,7 +3861,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3885,7 +3888,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121388899</v>
+        <v>121388952</v>
       </c>
       <c r="B32" t="n">
         <v>57354</v>
@@ -3925,10 +3928,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>435865</v>
+        <v>435812</v>
       </c>
       <c r="R32" t="n">
-        <v>7058514</v>
+        <v>7058763</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3965,7 +3968,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3992,7 +3995,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121388930</v>
+        <v>121388951</v>
       </c>
       <c r="B33" t="n">
         <v>57354</v>
@@ -4032,10 +4035,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>435898</v>
+        <v>435794</v>
       </c>
       <c r="R33" t="n">
-        <v>7058090</v>
+        <v>7058714</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4072,7 +4075,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4099,7 +4102,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121388913</v>
+        <v>121388920</v>
       </c>
       <c r="B34" t="n">
         <v>57354</v>
@@ -4139,10 +4142,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>436005</v>
+        <v>435928</v>
       </c>
       <c r="R34" t="n">
-        <v>7057639</v>
+        <v>7057577</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4179,7 +4182,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4206,7 +4209,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121388912</v>
+        <v>121388923</v>
       </c>
       <c r="B35" t="n">
         <v>57354</v>
@@ -4246,10 +4249,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>436005</v>
+        <v>435967</v>
       </c>
       <c r="R35" t="n">
-        <v>7057657</v>
+        <v>7057788</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4286,7 +4289,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4313,7 +4316,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121388929</v>
+        <v>121388916</v>
       </c>
       <c r="B36" t="n">
         <v>57354</v>
@@ -4353,10 +4356,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>435896</v>
+        <v>435983</v>
       </c>
       <c r="R36" t="n">
-        <v>7058085</v>
+        <v>7057467</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4393,7 +4396,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4420,7 +4423,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121388952</v>
+        <v>121388936</v>
       </c>
       <c r="B37" t="n">
         <v>57354</v>
@@ -4460,10 +4463,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>435812</v>
+        <v>435878</v>
       </c>
       <c r="R37" t="n">
-        <v>7058763</v>
+        <v>7058242</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4500,7 +4503,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4527,7 +4530,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121388932</v>
+        <v>121388905</v>
       </c>
       <c r="B38" t="n">
         <v>57354</v>
@@ -4567,10 +4570,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>435890</v>
+        <v>435889</v>
       </c>
       <c r="R38" t="n">
-        <v>7058190</v>
+        <v>7057953</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4634,7 +4637,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121388902</v>
+        <v>121388930</v>
       </c>
       <c r="B39" t="n">
         <v>57354</v>
@@ -4674,10 +4677,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>435918</v>
+        <v>435898</v>
       </c>
       <c r="R39" t="n">
-        <v>7058070</v>
+        <v>7058090</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4714,7 +4717,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4741,7 +4744,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121388917</v>
+        <v>121388942</v>
       </c>
       <c r="B40" t="n">
         <v>57354</v>
@@ -4781,10 +4784,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>435975</v>
+        <v>435757</v>
       </c>
       <c r="R40" t="n">
-        <v>7057462</v>
+        <v>7058329</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4821,7 +4824,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4848,7 +4851,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121388944</v>
+        <v>121388937</v>
       </c>
       <c r="B41" t="n">
         <v>57354</v>
@@ -4888,10 +4891,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>435747</v>
+        <v>435873</v>
       </c>
       <c r="R41" t="n">
-        <v>7058359</v>
+        <v>7058244</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4928,7 +4931,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>ringhack på tall</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4955,7 +4958,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121388908</v>
+        <v>121388893</v>
       </c>
       <c r="B42" t="n">
         <v>57354</v>
@@ -4995,10 +4998,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>436018</v>
+        <v>435833</v>
       </c>
       <c r="R42" t="n">
-        <v>7057811</v>
+        <v>7058665</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5062,7 +5065,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121388928</v>
+        <v>121388935</v>
       </c>
       <c r="B43" t="n">
         <v>57354</v>
@@ -5102,10 +5105,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>435802</v>
+        <v>435868</v>
       </c>
       <c r="R43" t="n">
-        <v>7058016</v>
+        <v>7058203</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5142,7 +5145,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5169,7 +5172,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121388894</v>
+        <v>121388903</v>
       </c>
       <c r="B44" t="n">
         <v>57354</v>
@@ -5209,10 +5212,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>435836</v>
+        <v>435913</v>
       </c>
       <c r="R44" t="n">
-        <v>7058627</v>
+        <v>7058004</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5249,7 +5252,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5276,7 +5279,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121388904</v>
+        <v>121388895</v>
       </c>
       <c r="B45" t="n">
         <v>57354</v>
@@ -5316,10 +5319,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>435893</v>
+        <v>435847</v>
       </c>
       <c r="R45" t="n">
-        <v>7058002</v>
+        <v>7058626</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5356,7 +5359,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5383,7 +5386,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121388947</v>
+        <v>121388918</v>
       </c>
       <c r="B46" t="n">
         <v>57354</v>
@@ -5423,10 +5426,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>435805</v>
+        <v>435965</v>
       </c>
       <c r="R46" t="n">
-        <v>7058511</v>
+        <v>7057511</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5463,7 +5466,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5490,7 +5493,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121388949</v>
+        <v>121388940</v>
       </c>
       <c r="B47" t="n">
         <v>57354</v>
@@ -5530,10 +5533,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>435790</v>
+        <v>435760</v>
       </c>
       <c r="R47" t="n">
-        <v>7058674</v>
+        <v>7058327</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5597,7 +5600,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121388946</v>
+        <v>121388910</v>
       </c>
       <c r="B48" t="n">
         <v>57354</v>
@@ -5637,10 +5640,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>435771</v>
+        <v>436007</v>
       </c>
       <c r="R48" t="n">
-        <v>7058417</v>
+        <v>7057694</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5677,7 +5680,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>ringhack färska till äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5704,7 +5707,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121388910</v>
+        <v>121388944</v>
       </c>
       <c r="B49" t="n">
         <v>57354</v>
@@ -5744,10 +5747,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>436007</v>
+        <v>435747</v>
       </c>
       <c r="R49" t="n">
-        <v>7057694</v>
+        <v>7058359</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5784,7 +5787,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack på tall</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5811,7 +5814,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121388939</v>
+        <v>121388938</v>
       </c>
       <c r="B50" t="n">
         <v>57354</v>
@@ -5851,10 +5854,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>435870</v>
+        <v>435877</v>
       </c>
       <c r="R50" t="n">
-        <v>7058288</v>
+        <v>7058290</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5891,7 +5894,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5918,7 +5921,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121388915</v>
+        <v>121388950</v>
       </c>
       <c r="B51" t="n">
         <v>57354</v>
@@ -5958,10 +5961,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>435989</v>
+        <v>435782</v>
       </c>
       <c r="R51" t="n">
-        <v>7057570</v>
+        <v>7058658</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5998,7 +6001,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6025,7 +6028,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121388914</v>
+        <v>121388948</v>
       </c>
       <c r="B52" t="n">
         <v>57354</v>
@@ -6065,10 +6068,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>435985</v>
+        <v>435777</v>
       </c>
       <c r="R52" t="n">
-        <v>7057600</v>
+        <v>7058633</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6132,7 +6135,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121388923</v>
+        <v>121388912</v>
       </c>
       <c r="B53" t="n">
         <v>57354</v>
@@ -6172,10 +6175,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>435967</v>
+        <v>436005</v>
       </c>
       <c r="R53" t="n">
-        <v>7057788</v>
+        <v>7057657</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6212,7 +6215,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6239,7 +6242,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121388936</v>
+        <v>121388945</v>
       </c>
       <c r="B54" t="n">
         <v>57354</v>
@@ -6279,10 +6282,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>435878</v>
+        <v>435762</v>
       </c>
       <c r="R54" t="n">
-        <v>7058242</v>
+        <v>7058369</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6319,7 +6322,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6346,7 +6349,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121388948</v>
+        <v>121388925</v>
       </c>
       <c r="B55" t="n">
         <v>57354</v>
@@ -6386,10 +6389,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>435777</v>
+        <v>435850</v>
       </c>
       <c r="R55" t="n">
-        <v>7058633</v>
+        <v>7057928</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6453,7 +6456,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121388920</v>
+        <v>121388904</v>
       </c>
       <c r="B56" t="n">
         <v>57354</v>
@@ -6493,10 +6496,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>435928</v>
+        <v>435893</v>
       </c>
       <c r="R56" t="n">
-        <v>7057577</v>
+        <v>7058002</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6533,7 +6536,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6560,10 +6563,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121388953</v>
+        <v>121388943</v>
       </c>
       <c r="B57" t="n">
-        <v>57507</v>
+        <v>57354</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6576,42 +6579,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Ångsjön, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>435836</v>
+        <v>435742</v>
       </c>
       <c r="R57" t="n">
-        <v>7058421</v>
+        <v>7058327</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6644,6 +6639,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2024-11-28</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6670,7 +6670,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121388906</v>
+        <v>121388909</v>
       </c>
       <c r="B58" t="n">
         <v>57354</v>
@@ -6710,10 +6710,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>435931</v>
+        <v>436008</v>
       </c>
       <c r="R58" t="n">
-        <v>7057902</v>
+        <v>7057730</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6750,7 +6750,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6777,7 +6777,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121388926</v>
+        <v>121388914</v>
       </c>
       <c r="B59" t="n">
         <v>57354</v>
@@ -6817,10 +6817,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>435857</v>
+        <v>435985</v>
       </c>
       <c r="R59" t="n">
-        <v>7057933</v>
+        <v>7057600</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6884,7 +6884,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121388935</v>
+        <v>121388934</v>
       </c>
       <c r="B60" t="n">
         <v>57354</v>
@@ -6924,10 +6924,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>435868</v>
+        <v>435875</v>
       </c>
       <c r="R60" t="n">
-        <v>7058203</v>
+        <v>7058202</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6991,7 +6991,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121388934</v>
+        <v>121388913</v>
       </c>
       <c r="B61" t="n">
         <v>57354</v>
@@ -7031,10 +7031,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>435875</v>
+        <v>436005</v>
       </c>
       <c r="R61" t="n">
-        <v>7058202</v>
+        <v>7057639</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7071,7 +7071,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD61" t="b">

--- a/artfynd/A 38630-2024 artfynd.xlsx
+++ b/artfynd/A 38630-2024 artfynd.xlsx
@@ -3246,7 +3246,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121388932</v>
+        <v>121388949</v>
       </c>
       <c r="B26" t="n">
         <v>57354</v>
@@ -3286,10 +3286,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>435890</v>
+        <v>435790</v>
       </c>
       <c r="R26" t="n">
-        <v>7058190</v>
+        <v>7058674</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3353,7 +3353,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121388926</v>
+        <v>121388932</v>
       </c>
       <c r="B27" t="n">
         <v>57354</v>
@@ -3393,10 +3393,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>435857</v>
+        <v>435890</v>
       </c>
       <c r="R27" t="n">
-        <v>7057933</v>
+        <v>7058190</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3460,7 +3460,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121388949</v>
+        <v>121388926</v>
       </c>
       <c r="B28" t="n">
         <v>57354</v>
@@ -3500,10 +3500,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>435790</v>
+        <v>435857</v>
       </c>
       <c r="R28" t="n">
-        <v>7058674</v>
+        <v>7057933</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -5921,7 +5921,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121388950</v>
+        <v>121388948</v>
       </c>
       <c r="B51" t="n">
         <v>57354</v>
@@ -5961,10 +5961,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>435782</v>
+        <v>435777</v>
       </c>
       <c r="R51" t="n">
-        <v>7058658</v>
+        <v>7058633</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6001,7 +6001,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6028,7 +6028,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121388948</v>
+        <v>121388950</v>
       </c>
       <c r="B52" t="n">
         <v>57354</v>
@@ -6068,10 +6068,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>435777</v>
+        <v>435782</v>
       </c>
       <c r="R52" t="n">
-        <v>7058633</v>
+        <v>7058658</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6108,7 +6108,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6135,7 +6135,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121388912</v>
+        <v>121388945</v>
       </c>
       <c r="B53" t="n">
         <v>57354</v>
@@ -6175,10 +6175,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>436005</v>
+        <v>435762</v>
       </c>
       <c r="R53" t="n">
-        <v>7057657</v>
+        <v>7058369</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6242,7 +6242,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121388945</v>
+        <v>121388925</v>
       </c>
       <c r="B54" t="n">
         <v>57354</v>
@@ -6282,10 +6282,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>435762</v>
+        <v>435850</v>
       </c>
       <c r="R54" t="n">
-        <v>7058369</v>
+        <v>7057928</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6322,7 +6322,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6349,7 +6349,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121388925</v>
+        <v>121388904</v>
       </c>
       <c r="B55" t="n">
         <v>57354</v>
@@ -6389,10 +6389,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>435850</v>
+        <v>435893</v>
       </c>
       <c r="R55" t="n">
-        <v>7057928</v>
+        <v>7058002</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6429,7 +6429,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6456,7 +6456,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121388904</v>
+        <v>121388943</v>
       </c>
       <c r="B56" t="n">
         <v>57354</v>
@@ -6496,10 +6496,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>435893</v>
+        <v>435742</v>
       </c>
       <c r="R56" t="n">
-        <v>7058002</v>
+        <v>7058327</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6536,7 +6536,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6563,7 +6563,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121388943</v>
+        <v>121388912</v>
       </c>
       <c r="B57" t="n">
         <v>57354</v>
@@ -6603,10 +6603,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>435742</v>
+        <v>436005</v>
       </c>
       <c r="R57" t="n">
-        <v>7058327</v>
+        <v>7057657</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6643,7 +6643,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD57" t="b">

--- a/artfynd/A 38630-2024 artfynd.xlsx
+++ b/artfynd/A 38630-2024 artfynd.xlsx
@@ -2708,10 +2708,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121388953</v>
+        <v>121388933</v>
       </c>
       <c r="B21" t="n">
-        <v>57507</v>
+        <v>57354</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2724,42 +2724,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Ångsjön, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>435836</v>
+        <v>435884</v>
       </c>
       <c r="R21" t="n">
-        <v>7058421</v>
+        <v>7058208</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2792,6 +2784,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-11-28</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2818,7 +2815,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121388933</v>
+        <v>121388906</v>
       </c>
       <c r="B22" t="n">
         <v>57354</v>
@@ -2858,10 +2855,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>435884</v>
+        <v>435931</v>
       </c>
       <c r="R22" t="n">
-        <v>7058208</v>
+        <v>7057902</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2925,7 +2922,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121388906</v>
+        <v>121388911</v>
       </c>
       <c r="B23" t="n">
         <v>57354</v>
@@ -2965,10 +2962,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>435931</v>
+        <v>436006</v>
       </c>
       <c r="R23" t="n">
-        <v>7057902</v>
+        <v>7057655</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3005,7 +3002,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3032,7 +3029,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121388911</v>
+        <v>121388894</v>
       </c>
       <c r="B24" t="n">
         <v>57354</v>
@@ -3072,10 +3069,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>436006</v>
+        <v>435836</v>
       </c>
       <c r="R24" t="n">
-        <v>7057655</v>
+        <v>7058627</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3112,7 +3109,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3139,10 +3136,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121388894</v>
+        <v>121388953</v>
       </c>
       <c r="B25" t="n">
-        <v>57354</v>
+        <v>57507</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3155,24 +3152,32 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Ångsjön, Jmt</t>
@@ -3182,7 +3187,7 @@
         <v>435836</v>
       </c>
       <c r="R25" t="n">
-        <v>7058627</v>
+        <v>7058421</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3215,11 +3220,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-11-28</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -6135,7 +6135,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121388945</v>
+        <v>121388912</v>
       </c>
       <c r="B53" t="n">
         <v>57354</v>
@@ -6175,10 +6175,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>435762</v>
+        <v>436005</v>
       </c>
       <c r="R53" t="n">
-        <v>7058369</v>
+        <v>7057657</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6242,7 +6242,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121388925</v>
+        <v>121388945</v>
       </c>
       <c r="B54" t="n">
         <v>57354</v>
@@ -6282,10 +6282,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>435850</v>
+        <v>435762</v>
       </c>
       <c r="R54" t="n">
-        <v>7057928</v>
+        <v>7058369</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6322,7 +6322,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6349,7 +6349,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121388904</v>
+        <v>121388925</v>
       </c>
       <c r="B55" t="n">
         <v>57354</v>
@@ -6389,10 +6389,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>435893</v>
+        <v>435850</v>
       </c>
       <c r="R55" t="n">
-        <v>7058002</v>
+        <v>7057928</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6429,7 +6429,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6456,7 +6456,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121388943</v>
+        <v>121388904</v>
       </c>
       <c r="B56" t="n">
         <v>57354</v>
@@ -6496,10 +6496,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>435742</v>
+        <v>435893</v>
       </c>
       <c r="R56" t="n">
-        <v>7058327</v>
+        <v>7058002</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6536,7 +6536,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6563,7 +6563,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121388912</v>
+        <v>121388943</v>
       </c>
       <c r="B57" t="n">
         <v>57354</v>
@@ -6603,10 +6603,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>436005</v>
+        <v>435742</v>
       </c>
       <c r="R57" t="n">
-        <v>7057657</v>
+        <v>7058327</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6643,7 +6643,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD57" t="b">

--- a/artfynd/A 38630-2024 artfynd.xlsx
+++ b/artfynd/A 38630-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121388917</v>
+        <v>121388938</v>
       </c>
       <c r="B2" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>435975</v>
+        <v>435877</v>
       </c>
       <c r="R2" t="n">
-        <v>7057462</v>
+        <v>7058290</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121388921</v>
+        <v>121388899</v>
       </c>
       <c r="B3" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>435927</v>
+        <v>435865</v>
       </c>
       <c r="R3" t="n">
-        <v>7057591</v>
+        <v>7058514</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121388924</v>
+        <v>121388912</v>
       </c>
       <c r="B4" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>435972</v>
+        <v>436005</v>
       </c>
       <c r="R4" t="n">
-        <v>7057798</v>
+        <v>7057657</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121388897</v>
+        <v>121388952</v>
       </c>
       <c r="B5" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>435853</v>
+        <v>435812</v>
       </c>
       <c r="R5" t="n">
-        <v>7058608</v>
+        <v>7058763</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121388929</v>
+        <v>121388948</v>
       </c>
       <c r="B6" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>435896</v>
+        <v>435777</v>
       </c>
       <c r="R6" t="n">
-        <v>7058085</v>
+        <v>7058633</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1210,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121388898</v>
+        <v>121388894</v>
       </c>
       <c r="B7" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1250,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>435841</v>
+        <v>435836</v>
       </c>
       <c r="R7" t="n">
-        <v>7058582</v>
+        <v>7058627</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1317,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121388927</v>
+        <v>121388946</v>
       </c>
       <c r="B8" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>435855</v>
+        <v>435771</v>
       </c>
       <c r="R8" t="n">
-        <v>7057933</v>
+        <v>7058417</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1397,7 +1397,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1424,10 +1424,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121388946</v>
+        <v>121388945</v>
       </c>
       <c r="B9" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1464,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>435771</v>
+        <v>435762</v>
       </c>
       <c r="R9" t="n">
-        <v>7058417</v>
+        <v>7058369</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>ringhack färska till äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1531,10 +1531,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121388939</v>
+        <v>121388910</v>
       </c>
       <c r="B10" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1571,10 +1571,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>435870</v>
+        <v>436007</v>
       </c>
       <c r="R10" t="n">
-        <v>7058288</v>
+        <v>7057694</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1638,10 +1638,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121388902</v>
+        <v>121388911</v>
       </c>
       <c r="B11" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1678,10 +1678,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>435918</v>
+        <v>436006</v>
       </c>
       <c r="R11" t="n">
-        <v>7058070</v>
+        <v>7057655</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1745,10 +1745,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121388901</v>
+        <v>121388919</v>
       </c>
       <c r="B12" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1785,10 +1785,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>435925</v>
+        <v>435924</v>
       </c>
       <c r="R12" t="n">
-        <v>7058082</v>
+        <v>7057563</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1852,10 +1852,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121388928</v>
+        <v>121388936</v>
       </c>
       <c r="B13" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1892,10 +1892,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>435802</v>
+        <v>435878</v>
       </c>
       <c r="R13" t="n">
-        <v>7058016</v>
+        <v>7058242</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1959,10 +1959,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121388931</v>
+        <v>121388901</v>
       </c>
       <c r="B14" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1999,10 +1999,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>435865</v>
+        <v>435925</v>
       </c>
       <c r="R14" t="n">
-        <v>7058110</v>
+        <v>7058082</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2039,7 +2039,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2066,10 +2066,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121388899</v>
+        <v>121388935</v>
       </c>
       <c r="B15" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2106,10 +2106,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>435865</v>
+        <v>435868</v>
       </c>
       <c r="R15" t="n">
-        <v>7058514</v>
+        <v>7058203</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2173,10 +2173,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121388900</v>
+        <v>121388923</v>
       </c>
       <c r="B16" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2213,10 +2213,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>435952</v>
+        <v>435967</v>
       </c>
       <c r="R16" t="n">
-        <v>7058237</v>
+        <v>7057788</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2253,7 +2253,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2280,10 +2280,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121388907</v>
+        <v>121388949</v>
       </c>
       <c r="B17" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2320,10 +2320,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>435997</v>
+        <v>435790</v>
       </c>
       <c r="R17" t="n">
-        <v>7057821</v>
+        <v>7058674</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2360,7 +2360,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2387,10 +2387,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121388896</v>
+        <v>121388942</v>
       </c>
       <c r="B18" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2427,10 +2427,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>435860</v>
+        <v>435757</v>
       </c>
       <c r="R18" t="n">
-        <v>7058614</v>
+        <v>7058329</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2467,7 +2467,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2494,10 +2494,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121388908</v>
+        <v>121388905</v>
       </c>
       <c r="B19" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2534,10 +2534,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>436018</v>
+        <v>435889</v>
       </c>
       <c r="R19" t="n">
-        <v>7057811</v>
+        <v>7057953</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2574,7 +2574,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2601,10 +2601,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121388915</v>
+        <v>121388940</v>
       </c>
       <c r="B20" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2641,10 +2641,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>435989</v>
+        <v>435760</v>
       </c>
       <c r="R20" t="n">
-        <v>7057570</v>
+        <v>7058327</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2708,10 +2708,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121388933</v>
+        <v>121388944</v>
       </c>
       <c r="B21" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2748,10 +2748,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>435884</v>
+        <v>435747</v>
       </c>
       <c r="R21" t="n">
-        <v>7058208</v>
+        <v>7058359</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack på tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2815,10 +2815,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121388906</v>
+        <v>121388895</v>
       </c>
       <c r="B22" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2855,10 +2855,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>435931</v>
+        <v>435847</v>
       </c>
       <c r="R22" t="n">
-        <v>7057902</v>
+        <v>7058626</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2895,7 +2895,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2922,10 +2922,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121388911</v>
+        <v>121388951</v>
       </c>
       <c r="B23" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2962,10 +2962,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>436006</v>
+        <v>435794</v>
       </c>
       <c r="R23" t="n">
-        <v>7057655</v>
+        <v>7058714</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3002,7 +3002,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3029,10 +3029,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121388894</v>
+        <v>121388921</v>
       </c>
       <c r="B24" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3069,10 +3069,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>435836</v>
+        <v>435927</v>
       </c>
       <c r="R24" t="n">
-        <v>7058627</v>
+        <v>7057591</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3109,7 +3109,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3136,10 +3136,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121388953</v>
+        <v>121388950</v>
       </c>
       <c r="B25" t="n">
-        <v>57507</v>
+        <v>57355</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3152,42 +3152,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Ångsjön, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>435836</v>
+        <v>435782</v>
       </c>
       <c r="R25" t="n">
-        <v>7058421</v>
+        <v>7058658</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3220,6 +3212,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-11-28</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3246,10 +3243,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121388949</v>
+        <v>121388928</v>
       </c>
       <c r="B26" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3286,10 +3283,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>435790</v>
+        <v>435802</v>
       </c>
       <c r="R26" t="n">
-        <v>7058674</v>
+        <v>7058016</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3326,7 +3323,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3353,10 +3350,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121388932</v>
+        <v>121388941</v>
       </c>
       <c r="B27" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3393,10 +3390,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>435890</v>
+        <v>435759</v>
       </c>
       <c r="R27" t="n">
-        <v>7058190</v>
+        <v>7058331</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3433,7 +3430,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3460,10 +3457,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121388926</v>
+        <v>121388915</v>
       </c>
       <c r="B28" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3500,10 +3497,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>435857</v>
+        <v>435989</v>
       </c>
       <c r="R28" t="n">
-        <v>7057933</v>
+        <v>7057570</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3567,10 +3564,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121388947</v>
+        <v>121388914</v>
       </c>
       <c r="B29" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3607,10 +3604,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>435805</v>
+        <v>435985</v>
       </c>
       <c r="R29" t="n">
-        <v>7058511</v>
+        <v>7057600</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3647,7 +3644,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3674,10 +3671,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121388919</v>
+        <v>121388930</v>
       </c>
       <c r="B30" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3714,10 +3711,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>435924</v>
+        <v>435898</v>
       </c>
       <c r="R30" t="n">
-        <v>7057563</v>
+        <v>7058090</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3754,7 +3751,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3781,10 +3778,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121388941</v>
+        <v>121388931</v>
       </c>
       <c r="B31" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3821,10 +3818,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>435759</v>
+        <v>435865</v>
       </c>
       <c r="R31" t="n">
-        <v>7058331</v>
+        <v>7058110</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3861,7 +3858,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3888,10 +3885,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121388952</v>
+        <v>121388909</v>
       </c>
       <c r="B32" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3928,10 +3925,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>435812</v>
+        <v>436008</v>
       </c>
       <c r="R32" t="n">
-        <v>7058763</v>
+        <v>7057730</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3968,7 +3965,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3995,10 +3992,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121388951</v>
+        <v>121388925</v>
       </c>
       <c r="B33" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4035,10 +4032,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>435794</v>
+        <v>435850</v>
       </c>
       <c r="R33" t="n">
-        <v>7058714</v>
+        <v>7057928</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4102,10 +4099,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121388920</v>
+        <v>121388932</v>
       </c>
       <c r="B34" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4142,10 +4139,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>435928</v>
+        <v>435890</v>
       </c>
       <c r="R34" t="n">
-        <v>7057577</v>
+        <v>7058190</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4209,10 +4206,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121388923</v>
+        <v>121388896</v>
       </c>
       <c r="B35" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4249,10 +4246,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>435967</v>
+        <v>435860</v>
       </c>
       <c r="R35" t="n">
-        <v>7057788</v>
+        <v>7058614</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4289,7 +4286,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4319,7 +4316,7 @@
         <v>121388916</v>
       </c>
       <c r="B36" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4423,10 +4420,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121388936</v>
+        <v>121388933</v>
       </c>
       <c r="B37" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4463,10 +4460,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>435878</v>
+        <v>435884</v>
       </c>
       <c r="R37" t="n">
-        <v>7058242</v>
+        <v>7058208</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4530,10 +4527,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121388905</v>
+        <v>121388939</v>
       </c>
       <c r="B38" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4570,10 +4567,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>435889</v>
+        <v>435870</v>
       </c>
       <c r="R38" t="n">
-        <v>7057953</v>
+        <v>7058288</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4610,7 +4607,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4637,10 +4634,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121388930</v>
+        <v>121388902</v>
       </c>
       <c r="B39" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4677,10 +4674,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>435898</v>
+        <v>435918</v>
       </c>
       <c r="R39" t="n">
-        <v>7058090</v>
+        <v>7058070</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4717,7 +4714,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4744,10 +4741,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121388942</v>
+        <v>121388920</v>
       </c>
       <c r="B40" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4784,10 +4781,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>435757</v>
+        <v>435928</v>
       </c>
       <c r="R40" t="n">
-        <v>7058329</v>
+        <v>7057577</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4824,7 +4821,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4851,10 +4848,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121388937</v>
+        <v>121388906</v>
       </c>
       <c r="B41" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4891,10 +4888,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>435873</v>
+        <v>435931</v>
       </c>
       <c r="R41" t="n">
-        <v>7058244</v>
+        <v>7057902</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4958,10 +4955,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121388893</v>
+        <v>121388908</v>
       </c>
       <c r="B42" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4998,10 +4995,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>435833</v>
+        <v>436018</v>
       </c>
       <c r="R42" t="n">
-        <v>7058665</v>
+        <v>7057811</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5065,10 +5062,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121388935</v>
+        <v>121388898</v>
       </c>
       <c r="B43" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5105,10 +5102,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>435868</v>
+        <v>435841</v>
       </c>
       <c r="R43" t="n">
-        <v>7058203</v>
+        <v>7058582</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5172,10 +5169,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121388903</v>
+        <v>121388943</v>
       </c>
       <c r="B44" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5212,10 +5209,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>435913</v>
+        <v>435742</v>
       </c>
       <c r="R44" t="n">
-        <v>7058004</v>
+        <v>7058327</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5252,7 +5249,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>ringhack färska till äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5279,10 +5276,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121388895</v>
+        <v>121388924</v>
       </c>
       <c r="B45" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5319,10 +5316,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>435847</v>
+        <v>435972</v>
       </c>
       <c r="R45" t="n">
-        <v>7058626</v>
+        <v>7057798</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5359,7 +5356,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>ringhack färska till äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5386,10 +5383,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121388918</v>
+        <v>121388903</v>
       </c>
       <c r="B46" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5426,10 +5423,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>435965</v>
+        <v>435913</v>
       </c>
       <c r="R46" t="n">
-        <v>7057511</v>
+        <v>7058004</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5466,7 +5463,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5493,10 +5490,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121388940</v>
+        <v>121388947</v>
       </c>
       <c r="B47" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5533,10 +5530,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>435760</v>
+        <v>435805</v>
       </c>
       <c r="R47" t="n">
-        <v>7058327</v>
+        <v>7058511</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5573,7 +5570,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5600,10 +5597,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121388910</v>
+        <v>121388953</v>
       </c>
       <c r="B48" t="n">
-        <v>57354</v>
+        <v>57508</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5616,34 +5613,42 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Ångsjön, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>436007</v>
+        <v>435836</v>
       </c>
       <c r="R48" t="n">
-        <v>7057694</v>
+        <v>7058421</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5676,11 +5681,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2024-11-28</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5707,10 +5707,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121388944</v>
+        <v>121388926</v>
       </c>
       <c r="B49" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5747,10 +5747,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>435747</v>
+        <v>435857</v>
       </c>
       <c r="R49" t="n">
-        <v>7058359</v>
+        <v>7057933</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5787,7 +5787,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>ringhack på tall</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5814,10 +5814,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121388938</v>
+        <v>121388897</v>
       </c>
       <c r="B50" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5854,10 +5854,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>435877</v>
+        <v>435853</v>
       </c>
       <c r="R50" t="n">
-        <v>7058290</v>
+        <v>7058608</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5894,7 +5894,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>ringhack färska till äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5921,10 +5921,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121388948</v>
+        <v>121388904</v>
       </c>
       <c r="B51" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5961,10 +5961,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>435777</v>
+        <v>435893</v>
       </c>
       <c r="R51" t="n">
-        <v>7058633</v>
+        <v>7058002</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6001,7 +6001,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6028,10 +6028,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121388950</v>
+        <v>121388907</v>
       </c>
       <c r="B52" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6068,10 +6068,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>435782</v>
+        <v>435997</v>
       </c>
       <c r="R52" t="n">
-        <v>7058658</v>
+        <v>7057821</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6108,7 +6108,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6135,10 +6135,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121388912</v>
+        <v>121388913</v>
       </c>
       <c r="B53" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6178,7 +6178,7 @@
         <v>436005</v>
       </c>
       <c r="R53" t="n">
-        <v>7057657</v>
+        <v>7057639</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6215,7 +6215,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6242,10 +6242,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121388945</v>
+        <v>121388927</v>
       </c>
       <c r="B54" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6282,10 +6282,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>435762</v>
+        <v>435855</v>
       </c>
       <c r="R54" t="n">
-        <v>7058369</v>
+        <v>7057933</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6322,7 +6322,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6349,10 +6349,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121388925</v>
+        <v>121388929</v>
       </c>
       <c r="B55" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6389,10 +6389,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>435850</v>
+        <v>435896</v>
       </c>
       <c r="R55" t="n">
-        <v>7057928</v>
+        <v>7058085</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6456,10 +6456,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121388904</v>
+        <v>121388937</v>
       </c>
       <c r="B56" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6496,10 +6496,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>435893</v>
+        <v>435873</v>
       </c>
       <c r="R56" t="n">
-        <v>7058002</v>
+        <v>7058244</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6536,7 +6536,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6563,10 +6563,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121388943</v>
+        <v>121388918</v>
       </c>
       <c r="B57" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6603,10 +6603,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>435742</v>
+        <v>435965</v>
       </c>
       <c r="R57" t="n">
-        <v>7058327</v>
+        <v>7057511</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6670,10 +6670,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121388909</v>
+        <v>121388934</v>
       </c>
       <c r="B58" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6710,10 +6710,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>436008</v>
+        <v>435875</v>
       </c>
       <c r="R58" t="n">
-        <v>7057730</v>
+        <v>7058202</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6777,10 +6777,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121388914</v>
+        <v>121388917</v>
       </c>
       <c r="B59" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6817,10 +6817,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>435985</v>
+        <v>435975</v>
       </c>
       <c r="R59" t="n">
-        <v>7057600</v>
+        <v>7057462</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6884,10 +6884,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121388934</v>
+        <v>121388893</v>
       </c>
       <c r="B60" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6924,10 +6924,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>435875</v>
+        <v>435833</v>
       </c>
       <c r="R60" t="n">
-        <v>7058202</v>
+        <v>7058665</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6991,10 +6991,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121388913</v>
+        <v>121388900</v>
       </c>
       <c r="B61" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7031,10 +7031,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>436005</v>
+        <v>435952</v>
       </c>
       <c r="R61" t="n">
-        <v>7057639</v>
+        <v>7058237</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>

--- a/artfynd/A 38630-2024 artfynd.xlsx
+++ b/artfynd/A 38630-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121388938</v>
+        <v>121388948</v>
       </c>
       <c r="B2" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>435877</v>
+        <v>435777</v>
       </c>
       <c r="R2" t="n">
-        <v>7058290</v>
+        <v>7058633</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>ringhack färska till äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121388899</v>
+        <v>121388915</v>
       </c>
       <c r="B3" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>435865</v>
+        <v>435989</v>
       </c>
       <c r="R3" t="n">
-        <v>7058514</v>
+        <v>7057570</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121388912</v>
+        <v>121388898</v>
       </c>
       <c r="B4" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>436005</v>
+        <v>435841</v>
       </c>
       <c r="R4" t="n">
-        <v>7057657</v>
+        <v>7058582</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121388952</v>
+        <v>121388897</v>
       </c>
       <c r="B5" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>435812</v>
+        <v>435853</v>
       </c>
       <c r="R5" t="n">
-        <v>7058763</v>
+        <v>7058608</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121388948</v>
+        <v>121388894</v>
       </c>
       <c r="B6" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>435777</v>
+        <v>435836</v>
       </c>
       <c r="R6" t="n">
-        <v>7058633</v>
+        <v>7058627</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121388894</v>
+        <v>121388903</v>
       </c>
       <c r="B7" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1250,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>435836</v>
+        <v>435913</v>
       </c>
       <c r="R7" t="n">
-        <v>7058627</v>
+        <v>7058004</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1290,7 +1290,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121388946</v>
+        <v>121388943</v>
       </c>
       <c r="B8" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>435771</v>
+        <v>435742</v>
       </c>
       <c r="R8" t="n">
-        <v>7058417</v>
+        <v>7058327</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1397,7 +1397,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>ringhack färska till äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1424,10 +1424,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121388945</v>
+        <v>121388937</v>
       </c>
       <c r="B9" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1464,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>435762</v>
+        <v>435873</v>
       </c>
       <c r="R9" t="n">
-        <v>7058369</v>
+        <v>7058244</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1531,10 +1531,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121388910</v>
+        <v>121388901</v>
       </c>
       <c r="B10" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1571,10 +1571,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>436007</v>
+        <v>435925</v>
       </c>
       <c r="R10" t="n">
-        <v>7057694</v>
+        <v>7058082</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1638,10 +1638,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121388911</v>
+        <v>121388940</v>
       </c>
       <c r="B11" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1678,10 +1678,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>436006</v>
+        <v>435760</v>
       </c>
       <c r="R11" t="n">
-        <v>7057655</v>
+        <v>7058327</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1718,7 +1718,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1745,10 +1745,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121388919</v>
+        <v>121388953</v>
       </c>
       <c r="B12" t="n">
-        <v>57355</v>
+        <v>57509</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1761,34 +1761,42 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Ångsjön, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>435924</v>
+        <v>435836</v>
       </c>
       <c r="R12" t="n">
-        <v>7057563</v>
+        <v>7058421</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1821,11 +1829,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-11-28</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1852,10 +1855,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121388936</v>
+        <v>121388942</v>
       </c>
       <c r="B13" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1892,10 +1895,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>435878</v>
+        <v>435757</v>
       </c>
       <c r="R13" t="n">
-        <v>7058242</v>
+        <v>7058329</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1932,7 +1935,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1959,10 +1962,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121388901</v>
+        <v>121388918</v>
       </c>
       <c r="B14" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1999,10 +2002,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>435925</v>
+        <v>435965</v>
       </c>
       <c r="R14" t="n">
-        <v>7058082</v>
+        <v>7057511</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2039,7 +2042,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2066,10 +2069,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121388935</v>
+        <v>121388923</v>
       </c>
       <c r="B15" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2106,10 +2109,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>435868</v>
+        <v>435967</v>
       </c>
       <c r="R15" t="n">
-        <v>7058203</v>
+        <v>7057788</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2146,7 +2149,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2173,10 +2176,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121388923</v>
+        <v>121388932</v>
       </c>
       <c r="B16" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2213,10 +2216,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>435967</v>
+        <v>435890</v>
       </c>
       <c r="R16" t="n">
-        <v>7057788</v>
+        <v>7058190</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2280,10 +2283,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121388949</v>
+        <v>121388893</v>
       </c>
       <c r="B17" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2320,10 +2323,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>435790</v>
+        <v>435833</v>
       </c>
       <c r="R17" t="n">
-        <v>7058674</v>
+        <v>7058665</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2360,7 +2363,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2387,10 +2390,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121388942</v>
+        <v>121388952</v>
       </c>
       <c r="B18" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2427,10 +2430,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>435757</v>
+        <v>435812</v>
       </c>
       <c r="R18" t="n">
-        <v>7058329</v>
+        <v>7058763</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2467,7 +2470,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2497,7 +2500,7 @@
         <v>121388905</v>
       </c>
       <c r="B19" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2601,10 +2604,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121388940</v>
+        <v>121388935</v>
       </c>
       <c r="B20" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2641,10 +2644,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>435760</v>
+        <v>435868</v>
       </c>
       <c r="R20" t="n">
-        <v>7058327</v>
+        <v>7058203</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2681,7 +2684,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2708,10 +2711,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121388944</v>
+        <v>121388919</v>
       </c>
       <c r="B21" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2748,10 +2751,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>435747</v>
+        <v>435924</v>
       </c>
       <c r="R21" t="n">
-        <v>7058359</v>
+        <v>7057563</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2788,7 +2791,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>ringhack på tall</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2815,10 +2818,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121388895</v>
+        <v>121388931</v>
       </c>
       <c r="B22" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2855,10 +2858,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>435847</v>
+        <v>435865</v>
       </c>
       <c r="R22" t="n">
-        <v>7058626</v>
+        <v>7058110</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2895,7 +2898,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>ringhack färska till äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2922,10 +2925,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121388951</v>
+        <v>121388921</v>
       </c>
       <c r="B23" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2962,10 +2965,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>435794</v>
+        <v>435927</v>
       </c>
       <c r="R23" t="n">
-        <v>7058714</v>
+        <v>7057591</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3002,7 +3005,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3029,10 +3032,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121388921</v>
+        <v>121388925</v>
       </c>
       <c r="B24" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3069,10 +3072,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>435927</v>
+        <v>435850</v>
       </c>
       <c r="R24" t="n">
-        <v>7057591</v>
+        <v>7057928</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3109,7 +3112,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3136,10 +3139,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121388950</v>
+        <v>121388920</v>
       </c>
       <c r="B25" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3176,10 +3179,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>435782</v>
+        <v>435928</v>
       </c>
       <c r="R25" t="n">
-        <v>7058658</v>
+        <v>7057577</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3216,7 +3219,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3243,10 +3246,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121388928</v>
+        <v>121388900</v>
       </c>
       <c r="B26" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3283,10 +3286,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>435802</v>
+        <v>435952</v>
       </c>
       <c r="R26" t="n">
-        <v>7058016</v>
+        <v>7058237</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3350,10 +3353,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121388941</v>
+        <v>121388928</v>
       </c>
       <c r="B27" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3390,10 +3393,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>435759</v>
+        <v>435802</v>
       </c>
       <c r="R27" t="n">
-        <v>7058331</v>
+        <v>7058016</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3457,10 +3460,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121388915</v>
+        <v>121388904</v>
       </c>
       <c r="B28" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3497,10 +3500,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>435989</v>
+        <v>435893</v>
       </c>
       <c r="R28" t="n">
-        <v>7057570</v>
+        <v>7058002</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3537,7 +3540,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3564,10 +3567,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121388914</v>
+        <v>121388916</v>
       </c>
       <c r="B29" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3604,10 +3607,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>435985</v>
+        <v>435983</v>
       </c>
       <c r="R29" t="n">
-        <v>7057600</v>
+        <v>7057467</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3644,7 +3647,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3671,10 +3674,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121388930</v>
+        <v>121388906</v>
       </c>
       <c r="B30" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3711,10 +3714,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>435898</v>
+        <v>435931</v>
       </c>
       <c r="R30" t="n">
-        <v>7058090</v>
+        <v>7057902</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3751,7 +3754,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3778,10 +3781,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121388931</v>
+        <v>121388911</v>
       </c>
       <c r="B31" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3818,10 +3821,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>435865</v>
+        <v>436006</v>
       </c>
       <c r="R31" t="n">
-        <v>7058110</v>
+        <v>7057655</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3858,7 +3861,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3885,10 +3888,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121388909</v>
+        <v>121388913</v>
       </c>
       <c r="B32" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3925,10 +3928,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>436008</v>
+        <v>436005</v>
       </c>
       <c r="R32" t="n">
-        <v>7057730</v>
+        <v>7057639</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3965,7 +3968,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3992,10 +3995,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121388925</v>
+        <v>121388896</v>
       </c>
       <c r="B33" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4032,10 +4035,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>435850</v>
+        <v>435860</v>
       </c>
       <c r="R33" t="n">
-        <v>7057928</v>
+        <v>7058614</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4072,7 +4075,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4099,10 +4102,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121388932</v>
+        <v>121388929</v>
       </c>
       <c r="B34" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4139,10 +4142,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>435890</v>
+        <v>435896</v>
       </c>
       <c r="R34" t="n">
-        <v>7058190</v>
+        <v>7058085</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4206,10 +4209,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121388896</v>
+        <v>121388908</v>
       </c>
       <c r="B35" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4246,10 +4249,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>435860</v>
+        <v>436018</v>
       </c>
       <c r="R35" t="n">
-        <v>7058614</v>
+        <v>7057811</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4313,10 +4316,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121388916</v>
+        <v>121388941</v>
       </c>
       <c r="B36" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4353,10 +4356,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>435983</v>
+        <v>435759</v>
       </c>
       <c r="R36" t="n">
-        <v>7057467</v>
+        <v>7058331</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4420,10 +4423,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121388933</v>
+        <v>121388938</v>
       </c>
       <c r="B37" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4460,10 +4463,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>435884</v>
+        <v>435877</v>
       </c>
       <c r="R37" t="n">
-        <v>7058208</v>
+        <v>7058290</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4500,7 +4503,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4527,10 +4530,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121388939</v>
+        <v>121388899</v>
       </c>
       <c r="B38" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4567,10 +4570,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>435870</v>
+        <v>435865</v>
       </c>
       <c r="R38" t="n">
-        <v>7058288</v>
+        <v>7058514</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4607,7 +4610,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4634,10 +4637,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121388902</v>
+        <v>121388936</v>
       </c>
       <c r="B39" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4674,10 +4677,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>435918</v>
+        <v>435878</v>
       </c>
       <c r="R39" t="n">
-        <v>7058070</v>
+        <v>7058242</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4714,7 +4717,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4741,10 +4744,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121388920</v>
+        <v>121388945</v>
       </c>
       <c r="B40" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4781,10 +4784,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>435928</v>
+        <v>435762</v>
       </c>
       <c r="R40" t="n">
-        <v>7057577</v>
+        <v>7058369</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4821,7 +4824,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4848,10 +4851,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121388906</v>
+        <v>121388907</v>
       </c>
       <c r="B41" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4888,10 +4891,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>435931</v>
+        <v>435997</v>
       </c>
       <c r="R41" t="n">
-        <v>7057902</v>
+        <v>7057821</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4928,7 +4931,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4955,10 +4958,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121388908</v>
+        <v>121388947</v>
       </c>
       <c r="B42" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4995,10 +4998,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>436018</v>
+        <v>435805</v>
       </c>
       <c r="R42" t="n">
-        <v>7057811</v>
+        <v>7058511</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5035,7 +5038,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5062,10 +5065,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121388898</v>
+        <v>121388934</v>
       </c>
       <c r="B43" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5102,10 +5105,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>435841</v>
+        <v>435875</v>
       </c>
       <c r="R43" t="n">
-        <v>7058582</v>
+        <v>7058202</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5169,10 +5172,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121388943</v>
+        <v>121388910</v>
       </c>
       <c r="B44" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5209,10 +5212,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>435742</v>
+        <v>436007</v>
       </c>
       <c r="R44" t="n">
-        <v>7058327</v>
+        <v>7057694</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5249,7 +5252,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5279,7 +5282,7 @@
         <v>121388924</v>
       </c>
       <c r="B45" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5383,10 +5386,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121388903</v>
+        <v>121388895</v>
       </c>
       <c r="B46" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5423,10 +5426,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>435913</v>
+        <v>435847</v>
       </c>
       <c r="R46" t="n">
-        <v>7058004</v>
+        <v>7058626</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5490,10 +5493,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121388947</v>
+        <v>121388912</v>
       </c>
       <c r="B47" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5530,10 +5533,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>435805</v>
+        <v>436005</v>
       </c>
       <c r="R47" t="n">
-        <v>7058511</v>
+        <v>7057657</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5570,7 +5573,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5597,10 +5600,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121388953</v>
+        <v>121388951</v>
       </c>
       <c r="B48" t="n">
-        <v>57508</v>
+        <v>57356</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5613,42 +5616,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Ångsjön, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>435836</v>
+        <v>435794</v>
       </c>
       <c r="R48" t="n">
-        <v>7058421</v>
+        <v>7058714</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5681,6 +5676,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2024-11-28</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5710,7 +5710,7 @@
         <v>121388926</v>
       </c>
       <c r="B49" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5814,10 +5814,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121388897</v>
+        <v>121388927</v>
       </c>
       <c r="B50" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5854,10 +5854,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>435853</v>
+        <v>435855</v>
       </c>
       <c r="R50" t="n">
-        <v>7058608</v>
+        <v>7057933</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5894,7 +5894,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5921,10 +5921,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121388904</v>
+        <v>121388939</v>
       </c>
       <c r="B51" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5961,10 +5961,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>435893</v>
+        <v>435870</v>
       </c>
       <c r="R51" t="n">
-        <v>7058002</v>
+        <v>7058288</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6001,7 +6001,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6028,10 +6028,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121388907</v>
+        <v>121388909</v>
       </c>
       <c r="B52" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6068,10 +6068,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>435997</v>
+        <v>436008</v>
       </c>
       <c r="R52" t="n">
-        <v>7057821</v>
+        <v>7057730</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6108,7 +6108,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6135,10 +6135,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121388913</v>
+        <v>121388902</v>
       </c>
       <c r="B53" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6175,10 +6175,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>436005</v>
+        <v>435918</v>
       </c>
       <c r="R53" t="n">
-        <v>7057639</v>
+        <v>7058070</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6242,10 +6242,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121388927</v>
+        <v>121388950</v>
       </c>
       <c r="B54" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6282,10 +6282,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>435855</v>
+        <v>435782</v>
       </c>
       <c r="R54" t="n">
-        <v>7057933</v>
+        <v>7058658</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6349,10 +6349,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121388929</v>
+        <v>121388917</v>
       </c>
       <c r="B55" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6389,10 +6389,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>435896</v>
+        <v>435975</v>
       </c>
       <c r="R55" t="n">
-        <v>7058085</v>
+        <v>7057462</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6456,10 +6456,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121388937</v>
+        <v>121388949</v>
       </c>
       <c r="B56" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6496,10 +6496,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>435873</v>
+        <v>435790</v>
       </c>
       <c r="R56" t="n">
-        <v>7058244</v>
+        <v>7058674</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6563,10 +6563,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121388918</v>
+        <v>121388914</v>
       </c>
       <c r="B57" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6603,10 +6603,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>435965</v>
+        <v>435985</v>
       </c>
       <c r="R57" t="n">
-        <v>7057511</v>
+        <v>7057600</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6670,10 +6670,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121388934</v>
+        <v>121388946</v>
       </c>
       <c r="B58" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6710,10 +6710,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>435875</v>
+        <v>435771</v>
       </c>
       <c r="R58" t="n">
-        <v>7058202</v>
+        <v>7058417</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6750,7 +6750,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6777,10 +6777,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121388917</v>
+        <v>121388933</v>
       </c>
       <c r="B59" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6817,10 +6817,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>435975</v>
+        <v>435884</v>
       </c>
       <c r="R59" t="n">
-        <v>7057462</v>
+        <v>7058208</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6884,10 +6884,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121388893</v>
+        <v>121388944</v>
       </c>
       <c r="B60" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6924,10 +6924,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>435833</v>
+        <v>435747</v>
       </c>
       <c r="R60" t="n">
-        <v>7058665</v>
+        <v>7058359</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6964,7 +6964,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack på tall</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6991,10 +6991,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121388900</v>
+        <v>121388930</v>
       </c>
       <c r="B61" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7031,10 +7031,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>435952</v>
+        <v>435898</v>
       </c>
       <c r="R61" t="n">
-        <v>7058237</v>
+        <v>7058090</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7071,7 +7071,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD61" t="b">

--- a/artfynd/A 38630-2024 artfynd.xlsx
+++ b/artfynd/A 38630-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121388948</v>
+        <v>121388917</v>
       </c>
       <c r="B2" t="n">
         <v>57356</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>435777</v>
+        <v>435975</v>
       </c>
       <c r="R2" t="n">
-        <v>7058633</v>
+        <v>7057462</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121388915</v>
+        <v>121388902</v>
       </c>
       <c r="B3" t="n">
         <v>57356</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>435989</v>
+        <v>435918</v>
       </c>
       <c r="R3" t="n">
-        <v>7057570</v>
+        <v>7058070</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121388898</v>
+        <v>121388949</v>
       </c>
       <c r="B4" t="n">
         <v>57356</v>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>435841</v>
+        <v>435790</v>
       </c>
       <c r="R4" t="n">
-        <v>7058582</v>
+        <v>7058674</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121388897</v>
+        <v>121388919</v>
       </c>
       <c r="B5" t="n">
         <v>57356</v>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>435853</v>
+        <v>435924</v>
       </c>
       <c r="R5" t="n">
-        <v>7058608</v>
+        <v>7057563</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,7 +1103,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121388894</v>
+        <v>121388936</v>
       </c>
       <c r="B6" t="n">
         <v>57356</v>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>435836</v>
+        <v>435878</v>
       </c>
       <c r="R6" t="n">
-        <v>7058627</v>
+        <v>7058242</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,7 +1210,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121388903</v>
+        <v>121388944</v>
       </c>
       <c r="B7" t="n">
         <v>57356</v>
@@ -1250,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>435913</v>
+        <v>435747</v>
       </c>
       <c r="R7" t="n">
-        <v>7058004</v>
+        <v>7058359</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1290,7 +1290,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>ringhack färska till äldre</t>
+          <t>ringhack på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,7 +1317,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121388943</v>
+        <v>121388935</v>
       </c>
       <c r="B8" t="n">
         <v>57356</v>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>435742</v>
+        <v>435868</v>
       </c>
       <c r="R8" t="n">
-        <v>7058327</v>
+        <v>7058203</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1397,7 +1397,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1424,7 +1424,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121388937</v>
+        <v>121388913</v>
       </c>
       <c r="B9" t="n">
         <v>57356</v>
@@ -1464,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>435873</v>
+        <v>436005</v>
       </c>
       <c r="R9" t="n">
-        <v>7058244</v>
+        <v>7057639</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1531,7 +1531,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121388901</v>
+        <v>121388946</v>
       </c>
       <c r="B10" t="n">
         <v>57356</v>
@@ -1571,10 +1571,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>435925</v>
+        <v>435771</v>
       </c>
       <c r="R10" t="n">
-        <v>7058082</v>
+        <v>7058417</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1611,7 +1611,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1638,7 +1638,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121388940</v>
+        <v>121388945</v>
       </c>
       <c r="B11" t="n">
         <v>57356</v>
@@ -1678,10 +1678,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>435760</v>
+        <v>435762</v>
       </c>
       <c r="R11" t="n">
-        <v>7058327</v>
+        <v>7058369</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1718,7 +1718,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1745,10 +1745,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121388953</v>
+        <v>121388915</v>
       </c>
       <c r="B12" t="n">
-        <v>57509</v>
+        <v>57356</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1761,42 +1761,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Ångsjön, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>435836</v>
+        <v>435989</v>
       </c>
       <c r="R12" t="n">
-        <v>7058421</v>
+        <v>7057570</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1829,6 +1821,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-11-28</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1855,7 +1852,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121388942</v>
+        <v>121388939</v>
       </c>
       <c r="B13" t="n">
         <v>57356</v>
@@ -1895,10 +1892,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>435757</v>
+        <v>435870</v>
       </c>
       <c r="R13" t="n">
-        <v>7058329</v>
+        <v>7058288</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1962,7 +1959,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121388918</v>
+        <v>121388932</v>
       </c>
       <c r="B14" t="n">
         <v>57356</v>
@@ -2002,10 +1999,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>435965</v>
+        <v>435890</v>
       </c>
       <c r="R14" t="n">
-        <v>7057511</v>
+        <v>7058190</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2069,7 +2066,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121388923</v>
+        <v>121388909</v>
       </c>
       <c r="B15" t="n">
         <v>57356</v>
@@ -2109,10 +2106,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>435967</v>
+        <v>436008</v>
       </c>
       <c r="R15" t="n">
-        <v>7057788</v>
+        <v>7057730</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2149,7 +2146,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2176,7 +2173,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121388932</v>
+        <v>121388927</v>
       </c>
       <c r="B16" t="n">
         <v>57356</v>
@@ -2216,10 +2213,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>435890</v>
+        <v>435855</v>
       </c>
       <c r="R16" t="n">
-        <v>7058190</v>
+        <v>7057933</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2256,7 +2253,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2283,7 +2280,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121388893</v>
+        <v>121388906</v>
       </c>
       <c r="B17" t="n">
         <v>57356</v>
@@ -2323,10 +2320,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>435833</v>
+        <v>435931</v>
       </c>
       <c r="R17" t="n">
-        <v>7058665</v>
+        <v>7057902</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2363,7 +2360,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2390,7 +2387,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121388952</v>
+        <v>121388926</v>
       </c>
       <c r="B18" t="n">
         <v>57356</v>
@@ -2430,10 +2427,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>435812</v>
+        <v>435857</v>
       </c>
       <c r="R18" t="n">
-        <v>7058763</v>
+        <v>7057933</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2470,7 +2467,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2497,7 +2494,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121388905</v>
+        <v>121388940</v>
       </c>
       <c r="B19" t="n">
         <v>57356</v>
@@ -2537,10 +2534,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>435889</v>
+        <v>435760</v>
       </c>
       <c r="R19" t="n">
-        <v>7057953</v>
+        <v>7058327</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2604,7 +2601,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121388935</v>
+        <v>121388897</v>
       </c>
       <c r="B20" t="n">
         <v>57356</v>
@@ -2644,10 +2641,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>435868</v>
+        <v>435853</v>
       </c>
       <c r="R20" t="n">
-        <v>7058203</v>
+        <v>7058608</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2684,7 +2681,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2711,7 +2708,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121388919</v>
+        <v>121388930</v>
       </c>
       <c r="B21" t="n">
         <v>57356</v>
@@ -2751,10 +2748,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>435924</v>
+        <v>435898</v>
       </c>
       <c r="R21" t="n">
-        <v>7057563</v>
+        <v>7058090</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2791,7 +2788,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2818,7 +2815,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121388931</v>
+        <v>121388900</v>
       </c>
       <c r="B22" t="n">
         <v>57356</v>
@@ -2858,10 +2855,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>435865</v>
+        <v>435952</v>
       </c>
       <c r="R22" t="n">
-        <v>7058110</v>
+        <v>7058237</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2898,7 +2895,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2925,7 +2922,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121388921</v>
+        <v>121388933</v>
       </c>
       <c r="B23" t="n">
         <v>57356</v>
@@ -2965,10 +2962,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>435927</v>
+        <v>435884</v>
       </c>
       <c r="R23" t="n">
-        <v>7057591</v>
+        <v>7058208</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3005,7 +3002,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3032,7 +3029,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121388925</v>
+        <v>121388937</v>
       </c>
       <c r="B24" t="n">
         <v>57356</v>
@@ -3072,10 +3069,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>435850</v>
+        <v>435873</v>
       </c>
       <c r="R24" t="n">
-        <v>7057928</v>
+        <v>7058244</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3139,7 +3136,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121388920</v>
+        <v>121388918</v>
       </c>
       <c r="B25" t="n">
         <v>57356</v>
@@ -3179,10 +3176,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>435928</v>
+        <v>435965</v>
       </c>
       <c r="R25" t="n">
-        <v>7057577</v>
+        <v>7057511</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3246,7 +3243,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121388900</v>
+        <v>121388925</v>
       </c>
       <c r="B26" t="n">
         <v>57356</v>
@@ -3286,10 +3283,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>435952</v>
+        <v>435850</v>
       </c>
       <c r="R26" t="n">
-        <v>7058237</v>
+        <v>7057928</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3326,7 +3323,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3353,7 +3350,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121388928</v>
+        <v>121388899</v>
       </c>
       <c r="B27" t="n">
         <v>57356</v>
@@ -3393,10 +3390,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>435802</v>
+        <v>435865</v>
       </c>
       <c r="R27" t="n">
-        <v>7058016</v>
+        <v>7058514</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3433,7 +3430,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3460,7 +3457,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121388904</v>
+        <v>121388938</v>
       </c>
       <c r="B28" t="n">
         <v>57356</v>
@@ -3500,10 +3497,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>435893</v>
+        <v>435877</v>
       </c>
       <c r="R28" t="n">
-        <v>7058002</v>
+        <v>7058290</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3540,7 +3537,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3567,7 +3564,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121388916</v>
+        <v>121388893</v>
       </c>
       <c r="B29" t="n">
         <v>57356</v>
@@ -3607,10 +3604,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>435983</v>
+        <v>435833</v>
       </c>
       <c r="R29" t="n">
-        <v>7057467</v>
+        <v>7058665</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3647,7 +3644,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3674,7 +3671,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121388906</v>
+        <v>121388943</v>
       </c>
       <c r="B30" t="n">
         <v>57356</v>
@@ -3714,10 +3711,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>435931</v>
+        <v>435742</v>
       </c>
       <c r="R30" t="n">
-        <v>7057902</v>
+        <v>7058327</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3781,7 +3778,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121388911</v>
+        <v>121388905</v>
       </c>
       <c r="B31" t="n">
         <v>57356</v>
@@ -3821,10 +3818,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>436006</v>
+        <v>435889</v>
       </c>
       <c r="R31" t="n">
-        <v>7057655</v>
+        <v>7057953</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3861,7 +3858,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3888,7 +3885,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121388913</v>
+        <v>121388941</v>
       </c>
       <c r="B32" t="n">
         <v>57356</v>
@@ -3928,10 +3925,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>436005</v>
+        <v>435759</v>
       </c>
       <c r="R32" t="n">
-        <v>7057639</v>
+        <v>7058331</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3995,7 +3992,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121388896</v>
+        <v>121388942</v>
       </c>
       <c r="B33" t="n">
         <v>57356</v>
@@ -4035,10 +4032,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>435860</v>
+        <v>435757</v>
       </c>
       <c r="R33" t="n">
-        <v>7058614</v>
+        <v>7058329</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4075,7 +4072,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4102,7 +4099,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121388929</v>
+        <v>121388951</v>
       </c>
       <c r="B34" t="n">
         <v>57356</v>
@@ -4142,10 +4139,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>435896</v>
+        <v>435794</v>
       </c>
       <c r="R34" t="n">
-        <v>7058085</v>
+        <v>7058714</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4209,7 +4206,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121388908</v>
+        <v>121388901</v>
       </c>
       <c r="B35" t="n">
         <v>57356</v>
@@ -4249,10 +4246,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>436018</v>
+        <v>435925</v>
       </c>
       <c r="R35" t="n">
-        <v>7057811</v>
+        <v>7058082</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4289,7 +4286,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4316,7 +4313,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121388941</v>
+        <v>121388924</v>
       </c>
       <c r="B36" t="n">
         <v>57356</v>
@@ -4356,10 +4353,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>435759</v>
+        <v>435972</v>
       </c>
       <c r="R36" t="n">
-        <v>7058331</v>
+        <v>7057798</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4396,7 +4393,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4423,7 +4420,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121388938</v>
+        <v>121388912</v>
       </c>
       <c r="B37" t="n">
         <v>57356</v>
@@ -4463,10 +4460,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>435877</v>
+        <v>436005</v>
       </c>
       <c r="R37" t="n">
-        <v>7058290</v>
+        <v>7057657</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4503,7 +4500,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>ringhack färska till äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4530,7 +4527,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121388899</v>
+        <v>121388908</v>
       </c>
       <c r="B38" t="n">
         <v>57356</v>
@@ -4570,10 +4567,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>435865</v>
+        <v>436018</v>
       </c>
       <c r="R38" t="n">
-        <v>7058514</v>
+        <v>7057811</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4637,7 +4634,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121388936</v>
+        <v>121388911</v>
       </c>
       <c r="B39" t="n">
         <v>57356</v>
@@ -4677,10 +4674,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>435878</v>
+        <v>436006</v>
       </c>
       <c r="R39" t="n">
-        <v>7058242</v>
+        <v>7057655</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4717,7 +4714,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4744,7 +4741,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121388945</v>
+        <v>121388898</v>
       </c>
       <c r="B40" t="n">
         <v>57356</v>
@@ -4784,10 +4781,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>435762</v>
+        <v>435841</v>
       </c>
       <c r="R40" t="n">
-        <v>7058369</v>
+        <v>7058582</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4851,7 +4848,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121388907</v>
+        <v>121388904</v>
       </c>
       <c r="B41" t="n">
         <v>57356</v>
@@ -4891,10 +4888,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>435997</v>
+        <v>435893</v>
       </c>
       <c r="R41" t="n">
-        <v>7057821</v>
+        <v>7058002</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4931,7 +4928,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4958,7 +4955,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121388947</v>
+        <v>121388903</v>
       </c>
       <c r="B42" t="n">
         <v>57356</v>
@@ -4998,10 +4995,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>435805</v>
+        <v>435913</v>
       </c>
       <c r="R42" t="n">
-        <v>7058511</v>
+        <v>7058004</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5038,7 +5035,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5065,7 +5062,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121388934</v>
+        <v>121388895</v>
       </c>
       <c r="B43" t="n">
         <v>57356</v>
@@ -5105,10 +5102,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>435875</v>
+        <v>435847</v>
       </c>
       <c r="R43" t="n">
-        <v>7058202</v>
+        <v>7058626</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5145,7 +5142,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5172,7 +5169,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121388910</v>
+        <v>121388907</v>
       </c>
       <c r="B44" t="n">
         <v>57356</v>
@@ -5212,10 +5209,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>436007</v>
+        <v>435997</v>
       </c>
       <c r="R44" t="n">
-        <v>7057694</v>
+        <v>7057821</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5279,7 +5276,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121388924</v>
+        <v>121388916</v>
       </c>
       <c r="B45" t="n">
         <v>57356</v>
@@ -5319,10 +5316,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>435972</v>
+        <v>435983</v>
       </c>
       <c r="R45" t="n">
-        <v>7057798</v>
+        <v>7057467</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5359,7 +5356,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5386,7 +5383,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121388895</v>
+        <v>121388920</v>
       </c>
       <c r="B46" t="n">
         <v>57356</v>
@@ -5426,10 +5423,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>435847</v>
+        <v>435928</v>
       </c>
       <c r="R46" t="n">
-        <v>7058626</v>
+        <v>7057577</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5466,7 +5463,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>ringhack färska till äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5493,7 +5490,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121388912</v>
+        <v>121388950</v>
       </c>
       <c r="B47" t="n">
         <v>57356</v>
@@ -5533,10 +5530,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>436005</v>
+        <v>435782</v>
       </c>
       <c r="R47" t="n">
-        <v>7057657</v>
+        <v>7058658</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5573,7 +5570,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5600,7 +5597,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121388951</v>
+        <v>121388914</v>
       </c>
       <c r="B48" t="n">
         <v>57356</v>
@@ -5640,10 +5637,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>435794</v>
+        <v>435985</v>
       </c>
       <c r="R48" t="n">
-        <v>7058714</v>
+        <v>7057600</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5707,7 +5704,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121388926</v>
+        <v>121388934</v>
       </c>
       <c r="B49" t="n">
         <v>57356</v>
@@ -5747,10 +5744,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>435857</v>
+        <v>435875</v>
       </c>
       <c r="R49" t="n">
-        <v>7057933</v>
+        <v>7058202</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5787,7 +5784,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5814,7 +5811,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121388927</v>
+        <v>121388948</v>
       </c>
       <c r="B50" t="n">
         <v>57356</v>
@@ -5854,10 +5851,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>435855</v>
+        <v>435777</v>
       </c>
       <c r="R50" t="n">
-        <v>7057933</v>
+        <v>7058633</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5894,7 +5891,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5921,7 +5918,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121388939</v>
+        <v>121388923</v>
       </c>
       <c r="B51" t="n">
         <v>57356</v>
@@ -5961,10 +5958,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>435870</v>
+        <v>435967</v>
       </c>
       <c r="R51" t="n">
-        <v>7058288</v>
+        <v>7057788</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6001,7 +5998,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6028,10 +6025,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121388909</v>
+        <v>121388953</v>
       </c>
       <c r="B52" t="n">
-        <v>57356</v>
+        <v>57509</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6044,34 +6041,42 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Ångsjön, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>436008</v>
+        <v>435836</v>
       </c>
       <c r="R52" t="n">
-        <v>7057730</v>
+        <v>7058421</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6104,11 +6109,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2024-11-28</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6135,7 +6135,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121388902</v>
+        <v>121388929</v>
       </c>
       <c r="B53" t="n">
         <v>57356</v>
@@ -6175,10 +6175,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>435918</v>
+        <v>435896</v>
       </c>
       <c r="R53" t="n">
-        <v>7058070</v>
+        <v>7058085</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6215,7 +6215,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6242,7 +6242,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121388950</v>
+        <v>121388896</v>
       </c>
       <c r="B54" t="n">
         <v>57356</v>
@@ -6282,10 +6282,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>435782</v>
+        <v>435860</v>
       </c>
       <c r="R54" t="n">
-        <v>7058658</v>
+        <v>7058614</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6322,7 +6322,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6349,7 +6349,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121388917</v>
+        <v>121388894</v>
       </c>
       <c r="B55" t="n">
         <v>57356</v>
@@ -6389,10 +6389,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>435975</v>
+        <v>435836</v>
       </c>
       <c r="R55" t="n">
-        <v>7057462</v>
+        <v>7058627</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6429,7 +6429,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6456,7 +6456,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121388949</v>
+        <v>121388931</v>
       </c>
       <c r="B56" t="n">
         <v>57356</v>
@@ -6496,10 +6496,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>435790</v>
+        <v>435865</v>
       </c>
       <c r="R56" t="n">
-        <v>7058674</v>
+        <v>7058110</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6563,7 +6563,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121388914</v>
+        <v>121388928</v>
       </c>
       <c r="B57" t="n">
         <v>57356</v>
@@ -6603,10 +6603,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>435985</v>
+        <v>435802</v>
       </c>
       <c r="R57" t="n">
-        <v>7057600</v>
+        <v>7058016</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6643,7 +6643,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6670,7 +6670,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121388946</v>
+        <v>121388921</v>
       </c>
       <c r="B58" t="n">
         <v>57356</v>
@@ -6710,10 +6710,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>435771</v>
+        <v>435927</v>
       </c>
       <c r="R58" t="n">
-        <v>7058417</v>
+        <v>7057591</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6750,7 +6750,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>ringhack färska till äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6777,7 +6777,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121388933</v>
+        <v>121388947</v>
       </c>
       <c r="B59" t="n">
         <v>57356</v>
@@ -6817,10 +6817,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>435884</v>
+        <v>435805</v>
       </c>
       <c r="R59" t="n">
-        <v>7058208</v>
+        <v>7058511</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6857,7 +6857,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6884,7 +6884,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121388944</v>
+        <v>121388952</v>
       </c>
       <c r="B60" t="n">
         <v>57356</v>
@@ -6924,10 +6924,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>435747</v>
+        <v>435812</v>
       </c>
       <c r="R60" t="n">
-        <v>7058359</v>
+        <v>7058763</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6964,7 +6964,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>ringhack på tall</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6991,7 +6991,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121388930</v>
+        <v>121388910</v>
       </c>
       <c r="B61" t="n">
         <v>57356</v>
@@ -7031,10 +7031,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>435898</v>
+        <v>436007</v>
       </c>
       <c r="R61" t="n">
-        <v>7058090</v>
+        <v>7057694</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7071,7 +7071,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD61" t="b">

--- a/artfynd/A 38630-2024 artfynd.xlsx
+++ b/artfynd/A 38630-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121388917</v>
+        <v>121388903</v>
       </c>
       <c r="B2" t="n">
         <v>57356</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>435975</v>
+        <v>435913</v>
       </c>
       <c r="R2" t="n">
-        <v>7057462</v>
+        <v>7058004</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121388902</v>
+        <v>121388920</v>
       </c>
       <c r="B3" t="n">
         <v>57356</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>435918</v>
+        <v>435928</v>
       </c>
       <c r="R3" t="n">
-        <v>7058070</v>
+        <v>7057577</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121388949</v>
+        <v>121388916</v>
       </c>
       <c r="B4" t="n">
         <v>57356</v>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>435790</v>
+        <v>435983</v>
       </c>
       <c r="R4" t="n">
-        <v>7058674</v>
+        <v>7057467</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121388919</v>
+        <v>121388939</v>
       </c>
       <c r="B5" t="n">
         <v>57356</v>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>435924</v>
+        <v>435870</v>
       </c>
       <c r="R5" t="n">
-        <v>7057563</v>
+        <v>7058288</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1103,7 +1103,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121388936</v>
+        <v>121388935</v>
       </c>
       <c r="B6" t="n">
         <v>57356</v>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>435878</v>
+        <v>435868</v>
       </c>
       <c r="R6" t="n">
-        <v>7058242</v>
+        <v>7058203</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121388944</v>
+        <v>121388953</v>
       </c>
       <c r="B7" t="n">
-        <v>57356</v>
+        <v>57509</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1226,34 +1226,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Ångsjön, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>435747</v>
+        <v>435836</v>
       </c>
       <c r="R7" t="n">
-        <v>7058359</v>
+        <v>7058421</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1286,11 +1294,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-11-28</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>ringhack på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,7 +1320,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121388935</v>
+        <v>121388908</v>
       </c>
       <c r="B8" t="n">
         <v>57356</v>
@@ -1357,10 +1360,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>435868</v>
+        <v>436018</v>
       </c>
       <c r="R8" t="n">
-        <v>7058203</v>
+        <v>7057811</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1424,7 +1427,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121388913</v>
+        <v>121388897</v>
       </c>
       <c r="B9" t="n">
         <v>57356</v>
@@ -1464,10 +1467,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>436005</v>
+        <v>435853</v>
       </c>
       <c r="R9" t="n">
-        <v>7057639</v>
+        <v>7058608</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1504,7 +1507,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1531,7 +1534,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121388946</v>
+        <v>121388926</v>
       </c>
       <c r="B10" t="n">
         <v>57356</v>
@@ -1571,10 +1574,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>435771</v>
+        <v>435857</v>
       </c>
       <c r="R10" t="n">
-        <v>7058417</v>
+        <v>7057933</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1611,7 +1614,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>ringhack färska till äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1638,7 +1641,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121388945</v>
+        <v>121388930</v>
       </c>
       <c r="B11" t="n">
         <v>57356</v>
@@ -1678,10 +1681,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>435762</v>
+        <v>435898</v>
       </c>
       <c r="R11" t="n">
-        <v>7058369</v>
+        <v>7058090</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1718,7 +1721,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1745,7 +1748,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121388915</v>
+        <v>121388949</v>
       </c>
       <c r="B12" t="n">
         <v>57356</v>
@@ -1785,10 +1788,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>435989</v>
+        <v>435790</v>
       </c>
       <c r="R12" t="n">
-        <v>7057570</v>
+        <v>7058674</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1852,7 +1855,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121388939</v>
+        <v>121388942</v>
       </c>
       <c r="B13" t="n">
         <v>57356</v>
@@ -1892,10 +1895,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>435870</v>
+        <v>435757</v>
       </c>
       <c r="R13" t="n">
-        <v>7058288</v>
+        <v>7058329</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1959,7 +1962,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121388932</v>
+        <v>121388948</v>
       </c>
       <c r="B14" t="n">
         <v>57356</v>
@@ -1999,10 +2002,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>435890</v>
+        <v>435777</v>
       </c>
       <c r="R14" t="n">
-        <v>7058190</v>
+        <v>7058633</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2066,7 +2069,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121388909</v>
+        <v>121388934</v>
       </c>
       <c r="B15" t="n">
         <v>57356</v>
@@ -2106,10 +2109,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>436008</v>
+        <v>435875</v>
       </c>
       <c r="R15" t="n">
-        <v>7057730</v>
+        <v>7058202</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2173,7 +2176,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121388927</v>
+        <v>121388952</v>
       </c>
       <c r="B16" t="n">
         <v>57356</v>
@@ -2213,10 +2216,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>435855</v>
+        <v>435812</v>
       </c>
       <c r="R16" t="n">
-        <v>7057933</v>
+        <v>7058763</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2280,7 +2283,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121388906</v>
+        <v>121388936</v>
       </c>
       <c r="B17" t="n">
         <v>57356</v>
@@ -2320,10 +2323,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>435931</v>
+        <v>435878</v>
       </c>
       <c r="R17" t="n">
-        <v>7057902</v>
+        <v>7058242</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2387,7 +2390,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121388926</v>
+        <v>121388913</v>
       </c>
       <c r="B18" t="n">
         <v>57356</v>
@@ -2427,10 +2430,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>435857</v>
+        <v>436005</v>
       </c>
       <c r="R18" t="n">
-        <v>7057933</v>
+        <v>7057639</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2467,7 +2470,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2494,7 +2497,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121388940</v>
+        <v>121388923</v>
       </c>
       <c r="B19" t="n">
         <v>57356</v>
@@ -2534,10 +2537,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>435760</v>
+        <v>435967</v>
       </c>
       <c r="R19" t="n">
-        <v>7058327</v>
+        <v>7057788</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2601,7 +2604,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121388897</v>
+        <v>121388918</v>
       </c>
       <c r="B20" t="n">
         <v>57356</v>
@@ -2641,10 +2644,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>435853</v>
+        <v>435965</v>
       </c>
       <c r="R20" t="n">
-        <v>7058608</v>
+        <v>7057511</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2708,7 +2711,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121388930</v>
+        <v>121388893</v>
       </c>
       <c r="B21" t="n">
         <v>57356</v>
@@ -2748,10 +2751,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>435898</v>
+        <v>435833</v>
       </c>
       <c r="R21" t="n">
-        <v>7058090</v>
+        <v>7058665</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2788,7 +2791,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2815,7 +2818,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121388900</v>
+        <v>121388938</v>
       </c>
       <c r="B22" t="n">
         <v>57356</v>
@@ -2855,10 +2858,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>435952</v>
+        <v>435877</v>
       </c>
       <c r="R22" t="n">
-        <v>7058237</v>
+        <v>7058290</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2895,7 +2898,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2922,7 +2925,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121388933</v>
+        <v>121388907</v>
       </c>
       <c r="B23" t="n">
         <v>57356</v>
@@ -2962,10 +2965,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>435884</v>
+        <v>435997</v>
       </c>
       <c r="R23" t="n">
-        <v>7058208</v>
+        <v>7057821</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3002,7 +3005,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3029,7 +3032,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121388937</v>
+        <v>121388929</v>
       </c>
       <c r="B24" t="n">
         <v>57356</v>
@@ -3069,10 +3072,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>435873</v>
+        <v>435896</v>
       </c>
       <c r="R24" t="n">
-        <v>7058244</v>
+        <v>7058085</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3136,7 +3139,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121388918</v>
+        <v>121388925</v>
       </c>
       <c r="B25" t="n">
         <v>57356</v>
@@ -3176,10 +3179,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>435965</v>
+        <v>435850</v>
       </c>
       <c r="R25" t="n">
-        <v>7057511</v>
+        <v>7057928</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3243,7 +3246,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121388925</v>
+        <v>121388919</v>
       </c>
       <c r="B26" t="n">
         <v>57356</v>
@@ -3283,10 +3286,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>435850</v>
+        <v>435924</v>
       </c>
       <c r="R26" t="n">
-        <v>7057928</v>
+        <v>7057563</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3323,7 +3326,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3350,7 +3353,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121388899</v>
+        <v>121388898</v>
       </c>
       <c r="B27" t="n">
         <v>57356</v>
@@ -3390,10 +3393,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>435865</v>
+        <v>435841</v>
       </c>
       <c r="R27" t="n">
-        <v>7058514</v>
+        <v>7058582</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3457,7 +3460,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121388938</v>
+        <v>121388946</v>
       </c>
       <c r="B28" t="n">
         <v>57356</v>
@@ -3497,10 +3500,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>435877</v>
+        <v>435771</v>
       </c>
       <c r="R28" t="n">
-        <v>7058290</v>
+        <v>7058417</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3564,7 +3567,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121388893</v>
+        <v>121388933</v>
       </c>
       <c r="B29" t="n">
         <v>57356</v>
@@ -3604,10 +3607,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>435833</v>
+        <v>435884</v>
       </c>
       <c r="R29" t="n">
-        <v>7058665</v>
+        <v>7058208</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3644,7 +3647,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3671,7 +3674,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121388943</v>
+        <v>121388937</v>
       </c>
       <c r="B30" t="n">
         <v>57356</v>
@@ -3711,10 +3714,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>435742</v>
+        <v>435873</v>
       </c>
       <c r="R30" t="n">
-        <v>7058327</v>
+        <v>7058244</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3778,7 +3781,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121388905</v>
+        <v>121388911</v>
       </c>
       <c r="B31" t="n">
         <v>57356</v>
@@ -3818,10 +3821,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>435889</v>
+        <v>436006</v>
       </c>
       <c r="R31" t="n">
-        <v>7057953</v>
+        <v>7057655</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3858,7 +3861,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3885,7 +3888,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121388941</v>
+        <v>121388940</v>
       </c>
       <c r="B32" t="n">
         <v>57356</v>
@@ -3925,10 +3928,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>435759</v>
+        <v>435760</v>
       </c>
       <c r="R32" t="n">
-        <v>7058331</v>
+        <v>7058327</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3965,7 +3968,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3992,7 +3995,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121388942</v>
+        <v>121388924</v>
       </c>
       <c r="B33" t="n">
         <v>57356</v>
@@ -4032,10 +4035,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>435757</v>
+        <v>435972</v>
       </c>
       <c r="R33" t="n">
-        <v>7058329</v>
+        <v>7057798</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4072,7 +4075,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4099,7 +4102,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121388951</v>
+        <v>121388899</v>
       </c>
       <c r="B34" t="n">
         <v>57356</v>
@@ -4139,10 +4142,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>435794</v>
+        <v>435865</v>
       </c>
       <c r="R34" t="n">
-        <v>7058714</v>
+        <v>7058514</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4179,7 +4182,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4206,7 +4209,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121388901</v>
+        <v>121388931</v>
       </c>
       <c r="B35" t="n">
         <v>57356</v>
@@ -4246,10 +4249,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>435925</v>
+        <v>435865</v>
       </c>
       <c r="R35" t="n">
-        <v>7058082</v>
+        <v>7058110</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4286,7 +4289,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4313,7 +4316,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121388924</v>
+        <v>121388902</v>
       </c>
       <c r="B36" t="n">
         <v>57356</v>
@@ -4353,10 +4356,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>435972</v>
+        <v>435918</v>
       </c>
       <c r="R36" t="n">
-        <v>7057798</v>
+        <v>7058070</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4393,7 +4396,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4420,7 +4423,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121388912</v>
+        <v>121388941</v>
       </c>
       <c r="B37" t="n">
         <v>57356</v>
@@ -4460,10 +4463,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>436005</v>
+        <v>435759</v>
       </c>
       <c r="R37" t="n">
-        <v>7057657</v>
+        <v>7058331</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4500,7 +4503,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4527,7 +4530,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121388908</v>
+        <v>121388945</v>
       </c>
       <c r="B38" t="n">
         <v>57356</v>
@@ -4567,10 +4570,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>436018</v>
+        <v>435762</v>
       </c>
       <c r="R38" t="n">
-        <v>7057811</v>
+        <v>7058369</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4634,7 +4637,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121388911</v>
+        <v>121388894</v>
       </c>
       <c r="B39" t="n">
         <v>57356</v>
@@ -4674,10 +4677,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>436006</v>
+        <v>435836</v>
       </c>
       <c r="R39" t="n">
-        <v>7057655</v>
+        <v>7058627</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4714,7 +4717,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4741,7 +4744,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121388898</v>
+        <v>121388896</v>
       </c>
       <c r="B40" t="n">
         <v>57356</v>
@@ -4781,10 +4784,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>435841</v>
+        <v>435860</v>
       </c>
       <c r="R40" t="n">
-        <v>7058582</v>
+        <v>7058614</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4848,7 +4851,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121388904</v>
+        <v>121388906</v>
       </c>
       <c r="B41" t="n">
         <v>57356</v>
@@ -4888,10 +4891,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>435893</v>
+        <v>435931</v>
       </c>
       <c r="R41" t="n">
-        <v>7058002</v>
+        <v>7057902</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4928,7 +4931,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4955,7 +4958,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121388903</v>
+        <v>121388900</v>
       </c>
       <c r="B42" t="n">
         <v>57356</v>
@@ -4995,10 +4998,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>435913</v>
+        <v>435952</v>
       </c>
       <c r="R42" t="n">
-        <v>7058004</v>
+        <v>7058237</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5035,7 +5038,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>ringhack färska till äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5062,7 +5065,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121388895</v>
+        <v>121388943</v>
       </c>
       <c r="B43" t="n">
         <v>57356</v>
@@ -5102,10 +5105,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>435847</v>
+        <v>435742</v>
       </c>
       <c r="R43" t="n">
-        <v>7058626</v>
+        <v>7058327</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5142,7 +5145,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>ringhack färska till äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5169,7 +5172,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121388907</v>
+        <v>121388917</v>
       </c>
       <c r="B44" t="n">
         <v>57356</v>
@@ -5209,10 +5212,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>435997</v>
+        <v>435975</v>
       </c>
       <c r="R44" t="n">
-        <v>7057821</v>
+        <v>7057462</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5249,7 +5252,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5276,7 +5279,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121388916</v>
+        <v>121388909</v>
       </c>
       <c r="B45" t="n">
         <v>57356</v>
@@ -5316,10 +5319,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>435983</v>
+        <v>436008</v>
       </c>
       <c r="R45" t="n">
-        <v>7057467</v>
+        <v>7057730</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5356,7 +5359,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5383,7 +5386,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121388920</v>
+        <v>121388914</v>
       </c>
       <c r="B46" t="n">
         <v>57356</v>
@@ -5423,10 +5426,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>435928</v>
+        <v>435985</v>
       </c>
       <c r="R46" t="n">
-        <v>7057577</v>
+        <v>7057600</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5597,7 +5600,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121388914</v>
+        <v>121388895</v>
       </c>
       <c r="B48" t="n">
         <v>57356</v>
@@ -5637,10 +5640,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>435985</v>
+        <v>435847</v>
       </c>
       <c r="R48" t="n">
-        <v>7057600</v>
+        <v>7058626</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5677,7 +5680,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5704,7 +5707,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121388934</v>
+        <v>121388928</v>
       </c>
       <c r="B49" t="n">
         <v>57356</v>
@@ -5744,10 +5747,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>435875</v>
+        <v>435802</v>
       </c>
       <c r="R49" t="n">
-        <v>7058202</v>
+        <v>7058016</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5784,7 +5787,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5811,7 +5814,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121388948</v>
+        <v>121388947</v>
       </c>
       <c r="B50" t="n">
         <v>57356</v>
@@ -5851,10 +5854,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>435777</v>
+        <v>435805</v>
       </c>
       <c r="R50" t="n">
-        <v>7058633</v>
+        <v>7058511</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5891,7 +5894,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5918,7 +5921,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121388923</v>
+        <v>121388912</v>
       </c>
       <c r="B51" t="n">
         <v>57356</v>
@@ -5958,10 +5961,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>435967</v>
+        <v>436005</v>
       </c>
       <c r="R51" t="n">
-        <v>7057788</v>
+        <v>7057657</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5998,7 +6001,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6025,10 +6028,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121388953</v>
+        <v>121388932</v>
       </c>
       <c r="B52" t="n">
-        <v>57509</v>
+        <v>57356</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6041,42 +6044,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Ångsjön, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>435836</v>
+        <v>435890</v>
       </c>
       <c r="R52" t="n">
-        <v>7058421</v>
+        <v>7058190</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6109,6 +6104,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2024-11-28</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6135,7 +6135,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121388929</v>
+        <v>121388904</v>
       </c>
       <c r="B53" t="n">
         <v>57356</v>
@@ -6175,10 +6175,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>435896</v>
+        <v>435893</v>
       </c>
       <c r="R53" t="n">
-        <v>7058085</v>
+        <v>7058002</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6215,7 +6215,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6242,7 +6242,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121388896</v>
+        <v>121388927</v>
       </c>
       <c r="B54" t="n">
         <v>57356</v>
@@ -6282,10 +6282,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>435860</v>
+        <v>435855</v>
       </c>
       <c r="R54" t="n">
-        <v>7058614</v>
+        <v>7057933</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6322,7 +6322,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6349,7 +6349,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121388894</v>
+        <v>121388951</v>
       </c>
       <c r="B55" t="n">
         <v>57356</v>
@@ -6389,10 +6389,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>435836</v>
+        <v>435794</v>
       </c>
       <c r="R55" t="n">
-        <v>7058627</v>
+        <v>7058714</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6429,7 +6429,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6456,7 +6456,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121388931</v>
+        <v>121388901</v>
       </c>
       <c r="B56" t="n">
         <v>57356</v>
@@ -6496,10 +6496,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>435865</v>
+        <v>435925</v>
       </c>
       <c r="R56" t="n">
-        <v>7058110</v>
+        <v>7058082</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6536,7 +6536,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6563,7 +6563,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121388928</v>
+        <v>121388915</v>
       </c>
       <c r="B57" t="n">
         <v>57356</v>
@@ -6603,10 +6603,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>435802</v>
+        <v>435989</v>
       </c>
       <c r="R57" t="n">
-        <v>7058016</v>
+        <v>7057570</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6643,7 +6643,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6670,7 +6670,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121388921</v>
+        <v>121388910</v>
       </c>
       <c r="B58" t="n">
         <v>57356</v>
@@ -6710,10 +6710,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>435927</v>
+        <v>436007</v>
       </c>
       <c r="R58" t="n">
-        <v>7057591</v>
+        <v>7057694</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6777,7 +6777,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121388947</v>
+        <v>121388905</v>
       </c>
       <c r="B59" t="n">
         <v>57356</v>
@@ -6817,10 +6817,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>435805</v>
+        <v>435889</v>
       </c>
       <c r="R59" t="n">
-        <v>7058511</v>
+        <v>7057953</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6857,7 +6857,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6884,7 +6884,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121388952</v>
+        <v>121388921</v>
       </c>
       <c r="B60" t="n">
         <v>57356</v>
@@ -6924,10 +6924,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>435812</v>
+        <v>435927</v>
       </c>
       <c r="R60" t="n">
-        <v>7058763</v>
+        <v>7057591</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6964,7 +6964,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6991,7 +6991,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121388910</v>
+        <v>121388944</v>
       </c>
       <c r="B61" t="n">
         <v>57356</v>
@@ -7031,10 +7031,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>436007</v>
+        <v>435747</v>
       </c>
       <c r="R61" t="n">
-        <v>7057694</v>
+        <v>7058359</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7071,7 +7071,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack på tall</t>
         </is>
       </c>
       <c r="AD61" t="b">

--- a/artfynd/A 38630-2024 artfynd.xlsx
+++ b/artfynd/A 38630-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121388903</v>
+        <v>121388915</v>
       </c>
       <c r="B2" t="n">
         <v>57356</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>435913</v>
+        <v>435989</v>
       </c>
       <c r="R2" t="n">
-        <v>7058004</v>
+        <v>7057570</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>ringhack färska till äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121388920</v>
+        <v>121388932</v>
       </c>
       <c r="B3" t="n">
         <v>57356</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>435928</v>
+        <v>435890</v>
       </c>
       <c r="R3" t="n">
-        <v>7057577</v>
+        <v>7058190</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121388916</v>
+        <v>121388914</v>
       </c>
       <c r="B4" t="n">
         <v>57356</v>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>435983</v>
+        <v>435985</v>
       </c>
       <c r="R4" t="n">
-        <v>7057467</v>
+        <v>7057600</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121388939</v>
+        <v>121388946</v>
       </c>
       <c r="B5" t="n">
         <v>57356</v>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>435870</v>
+        <v>435771</v>
       </c>
       <c r="R5" t="n">
-        <v>7058288</v>
+        <v>7058417</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,7 +1103,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121388935</v>
+        <v>121388893</v>
       </c>
       <c r="B6" t="n">
         <v>57356</v>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>435868</v>
+        <v>435833</v>
       </c>
       <c r="R6" t="n">
-        <v>7058203</v>
+        <v>7058665</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1210,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121388953</v>
+        <v>121388950</v>
       </c>
       <c r="B7" t="n">
-        <v>57509</v>
+        <v>57356</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1226,42 +1226,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Ångsjön, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>435836</v>
+        <v>435782</v>
       </c>
       <c r="R7" t="n">
-        <v>7058421</v>
+        <v>7058658</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1294,6 +1286,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-11-28</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1320,7 +1317,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121388908</v>
+        <v>121388913</v>
       </c>
       <c r="B8" t="n">
         <v>57356</v>
@@ -1360,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>436018</v>
+        <v>436005</v>
       </c>
       <c r="R8" t="n">
-        <v>7057811</v>
+        <v>7057639</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1400,7 +1397,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1427,7 +1424,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121388897</v>
+        <v>121388935</v>
       </c>
       <c r="B9" t="n">
         <v>57356</v>
@@ -1467,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>435853</v>
+        <v>435868</v>
       </c>
       <c r="R9" t="n">
-        <v>7058608</v>
+        <v>7058203</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1507,7 +1504,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1534,7 +1531,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121388926</v>
+        <v>121388941</v>
       </c>
       <c r="B10" t="n">
         <v>57356</v>
@@ -1574,10 +1571,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>435857</v>
+        <v>435759</v>
       </c>
       <c r="R10" t="n">
-        <v>7057933</v>
+        <v>7058331</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1614,7 +1611,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1641,7 +1638,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121388930</v>
+        <v>121388952</v>
       </c>
       <c r="B11" t="n">
         <v>57356</v>
@@ -1681,10 +1678,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>435898</v>
+        <v>435812</v>
       </c>
       <c r="R11" t="n">
-        <v>7058090</v>
+        <v>7058763</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1748,7 +1745,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121388949</v>
+        <v>121388894</v>
       </c>
       <c r="B12" t="n">
         <v>57356</v>
@@ -1788,10 +1785,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>435790</v>
+        <v>435836</v>
       </c>
       <c r="R12" t="n">
-        <v>7058674</v>
+        <v>7058627</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1828,7 +1825,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1855,7 +1852,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121388942</v>
+        <v>121388930</v>
       </c>
       <c r="B13" t="n">
         <v>57356</v>
@@ -1895,10 +1892,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>435757</v>
+        <v>435898</v>
       </c>
       <c r="R13" t="n">
-        <v>7058329</v>
+        <v>7058090</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1935,7 +1932,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1962,7 +1959,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121388948</v>
+        <v>121388926</v>
       </c>
       <c r="B14" t="n">
         <v>57356</v>
@@ -2002,10 +1999,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>435777</v>
+        <v>435857</v>
       </c>
       <c r="R14" t="n">
-        <v>7058633</v>
+        <v>7057933</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2069,7 +2066,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121388934</v>
+        <v>121388899</v>
       </c>
       <c r="B15" t="n">
         <v>57356</v>
@@ -2109,10 +2106,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>435875</v>
+        <v>435865</v>
       </c>
       <c r="R15" t="n">
-        <v>7058202</v>
+        <v>7058514</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2176,7 +2173,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121388952</v>
+        <v>121388933</v>
       </c>
       <c r="B16" t="n">
         <v>57356</v>
@@ -2216,10 +2213,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>435812</v>
+        <v>435884</v>
       </c>
       <c r="R16" t="n">
-        <v>7058763</v>
+        <v>7058208</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2256,7 +2253,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2283,7 +2280,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121388936</v>
+        <v>121388910</v>
       </c>
       <c r="B17" t="n">
         <v>57356</v>
@@ -2323,10 +2320,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>435878</v>
+        <v>436007</v>
       </c>
       <c r="R17" t="n">
-        <v>7058242</v>
+        <v>7057694</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2363,7 +2360,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2390,7 +2387,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121388913</v>
+        <v>121388947</v>
       </c>
       <c r="B18" t="n">
         <v>57356</v>
@@ -2430,10 +2427,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>436005</v>
+        <v>435805</v>
       </c>
       <c r="R18" t="n">
-        <v>7057639</v>
+        <v>7058511</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2497,7 +2494,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121388923</v>
+        <v>121388945</v>
       </c>
       <c r="B19" t="n">
         <v>57356</v>
@@ -2537,10 +2534,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>435967</v>
+        <v>435762</v>
       </c>
       <c r="R19" t="n">
-        <v>7057788</v>
+        <v>7058369</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2577,7 +2574,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2604,7 +2601,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121388918</v>
+        <v>121388903</v>
       </c>
       <c r="B20" t="n">
         <v>57356</v>
@@ -2644,10 +2641,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>435965</v>
+        <v>435913</v>
       </c>
       <c r="R20" t="n">
-        <v>7057511</v>
+        <v>7058004</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2684,7 +2681,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2711,7 +2708,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121388893</v>
+        <v>121388907</v>
       </c>
       <c r="B21" t="n">
         <v>57356</v>
@@ -2751,10 +2748,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>435833</v>
+        <v>435997</v>
       </c>
       <c r="R21" t="n">
-        <v>7058665</v>
+        <v>7057821</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2791,7 +2788,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2818,7 +2815,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121388938</v>
+        <v>121388916</v>
       </c>
       <c r="B22" t="n">
         <v>57356</v>
@@ -2858,10 +2855,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>435877</v>
+        <v>435983</v>
       </c>
       <c r="R22" t="n">
-        <v>7058290</v>
+        <v>7057467</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2898,7 +2895,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>ringhack färska till äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2925,7 +2922,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121388907</v>
+        <v>121388948</v>
       </c>
       <c r="B23" t="n">
         <v>57356</v>
@@ -2965,10 +2962,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>435997</v>
+        <v>435777</v>
       </c>
       <c r="R23" t="n">
-        <v>7057821</v>
+        <v>7058633</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3005,7 +3002,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3032,7 +3029,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121388929</v>
+        <v>121388928</v>
       </c>
       <c r="B24" t="n">
         <v>57356</v>
@@ -3072,10 +3069,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>435896</v>
+        <v>435802</v>
       </c>
       <c r="R24" t="n">
-        <v>7058085</v>
+        <v>7058016</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3112,7 +3109,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3139,7 +3136,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121388925</v>
+        <v>121388937</v>
       </c>
       <c r="B25" t="n">
         <v>57356</v>
@@ -3179,10 +3176,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>435850</v>
+        <v>435873</v>
       </c>
       <c r="R25" t="n">
-        <v>7057928</v>
+        <v>7058244</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3246,7 +3243,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121388919</v>
+        <v>121388897</v>
       </c>
       <c r="B26" t="n">
         <v>57356</v>
@@ -3286,10 +3283,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>435924</v>
+        <v>435853</v>
       </c>
       <c r="R26" t="n">
-        <v>7057563</v>
+        <v>7058608</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3326,7 +3323,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3353,7 +3350,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121388898</v>
+        <v>121388927</v>
       </c>
       <c r="B27" t="n">
         <v>57356</v>
@@ -3393,10 +3390,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>435841</v>
+        <v>435855</v>
       </c>
       <c r="R27" t="n">
-        <v>7058582</v>
+        <v>7057933</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3433,7 +3430,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3460,7 +3457,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121388946</v>
+        <v>121388938</v>
       </c>
       <c r="B28" t="n">
         <v>57356</v>
@@ -3500,10 +3497,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>435771</v>
+        <v>435877</v>
       </c>
       <c r="R28" t="n">
-        <v>7058417</v>
+        <v>7058290</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3567,7 +3564,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121388933</v>
+        <v>121388905</v>
       </c>
       <c r="B29" t="n">
         <v>57356</v>
@@ -3607,10 +3604,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>435884</v>
+        <v>435889</v>
       </c>
       <c r="R29" t="n">
-        <v>7058208</v>
+        <v>7057953</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3674,7 +3671,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121388937</v>
+        <v>121388895</v>
       </c>
       <c r="B30" t="n">
         <v>57356</v>
@@ -3714,10 +3711,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>435873</v>
+        <v>435847</v>
       </c>
       <c r="R30" t="n">
-        <v>7058244</v>
+        <v>7058626</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3754,7 +3751,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3781,7 +3778,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121388911</v>
+        <v>121388940</v>
       </c>
       <c r="B31" t="n">
         <v>57356</v>
@@ -3821,10 +3818,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>436006</v>
+        <v>435760</v>
       </c>
       <c r="R31" t="n">
-        <v>7057655</v>
+        <v>7058327</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3861,7 +3858,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3888,7 +3885,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121388940</v>
+        <v>121388902</v>
       </c>
       <c r="B32" t="n">
         <v>57356</v>
@@ -3928,10 +3925,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>435760</v>
+        <v>435918</v>
       </c>
       <c r="R32" t="n">
-        <v>7058327</v>
+        <v>7058070</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3968,7 +3965,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3995,7 +3992,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121388924</v>
+        <v>121388929</v>
       </c>
       <c r="B33" t="n">
         <v>57356</v>
@@ -4035,10 +4032,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>435972</v>
+        <v>435896</v>
       </c>
       <c r="R33" t="n">
-        <v>7057798</v>
+        <v>7058085</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4075,7 +4072,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4102,7 +4099,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121388899</v>
+        <v>121388918</v>
       </c>
       <c r="B34" t="n">
         <v>57356</v>
@@ -4142,10 +4139,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>435865</v>
+        <v>435965</v>
       </c>
       <c r="R34" t="n">
-        <v>7058514</v>
+        <v>7057511</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4182,7 +4179,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4209,7 +4206,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121388931</v>
+        <v>121388912</v>
       </c>
       <c r="B35" t="n">
         <v>57356</v>
@@ -4249,10 +4246,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>435865</v>
+        <v>436005</v>
       </c>
       <c r="R35" t="n">
-        <v>7058110</v>
+        <v>7057657</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4289,7 +4286,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4316,7 +4313,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121388902</v>
+        <v>121388936</v>
       </c>
       <c r="B36" t="n">
         <v>57356</v>
@@ -4356,10 +4353,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>435918</v>
+        <v>435878</v>
       </c>
       <c r="R36" t="n">
-        <v>7058070</v>
+        <v>7058242</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4396,7 +4393,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4423,7 +4420,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121388941</v>
+        <v>121388944</v>
       </c>
       <c r="B37" t="n">
         <v>57356</v>
@@ -4463,10 +4460,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>435759</v>
+        <v>435747</v>
       </c>
       <c r="R37" t="n">
-        <v>7058331</v>
+        <v>7058359</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4503,7 +4500,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack på tall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4530,7 +4527,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121388945</v>
+        <v>121388900</v>
       </c>
       <c r="B38" t="n">
         <v>57356</v>
@@ -4570,10 +4567,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>435762</v>
+        <v>435952</v>
       </c>
       <c r="R38" t="n">
-        <v>7058369</v>
+        <v>7058237</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4610,7 +4607,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4637,7 +4634,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121388894</v>
+        <v>121388911</v>
       </c>
       <c r="B39" t="n">
         <v>57356</v>
@@ -4677,10 +4674,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>435836</v>
+        <v>436006</v>
       </c>
       <c r="R39" t="n">
-        <v>7058627</v>
+        <v>7057655</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4717,7 +4714,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4744,7 +4741,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121388896</v>
+        <v>121388920</v>
       </c>
       <c r="B40" t="n">
         <v>57356</v>
@@ -4784,10 +4781,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>435860</v>
+        <v>435928</v>
       </c>
       <c r="R40" t="n">
-        <v>7058614</v>
+        <v>7057577</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4824,7 +4821,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4851,7 +4848,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121388906</v>
+        <v>121388939</v>
       </c>
       <c r="B41" t="n">
         <v>57356</v>
@@ -4891,10 +4888,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>435931</v>
+        <v>435870</v>
       </c>
       <c r="R41" t="n">
-        <v>7057902</v>
+        <v>7058288</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4931,7 +4928,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4958,7 +4955,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121388900</v>
+        <v>121388898</v>
       </c>
       <c r="B42" t="n">
         <v>57356</v>
@@ -4998,10 +4995,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>435952</v>
+        <v>435841</v>
       </c>
       <c r="R42" t="n">
-        <v>7058237</v>
+        <v>7058582</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5038,7 +5035,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5065,10 +5062,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121388943</v>
+        <v>121388953</v>
       </c>
       <c r="B43" t="n">
-        <v>57356</v>
+        <v>57509</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5081,34 +5078,42 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Ångsjön, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>435742</v>
+        <v>435836</v>
       </c>
       <c r="R43" t="n">
-        <v>7058327</v>
+        <v>7058421</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5141,11 +5146,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2024-11-28</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5172,7 +5172,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121388917</v>
+        <v>121388942</v>
       </c>
       <c r="B44" t="n">
         <v>57356</v>
@@ -5212,10 +5212,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>435975</v>
+        <v>435757</v>
       </c>
       <c r="R44" t="n">
-        <v>7057462</v>
+        <v>7058329</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5252,7 +5252,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5279,7 +5279,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121388909</v>
+        <v>121388901</v>
       </c>
       <c r="B45" t="n">
         <v>57356</v>
@@ -5319,10 +5319,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>436008</v>
+        <v>435925</v>
       </c>
       <c r="R45" t="n">
-        <v>7057730</v>
+        <v>7058082</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5359,7 +5359,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5386,7 +5386,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121388914</v>
+        <v>121388917</v>
       </c>
       <c r="B46" t="n">
         <v>57356</v>
@@ -5426,10 +5426,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>435985</v>
+        <v>435975</v>
       </c>
       <c r="R46" t="n">
-        <v>7057600</v>
+        <v>7057462</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5493,7 +5493,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121388950</v>
+        <v>121388904</v>
       </c>
       <c r="B47" t="n">
         <v>57356</v>
@@ -5533,10 +5533,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>435782</v>
+        <v>435893</v>
       </c>
       <c r="R47" t="n">
-        <v>7058658</v>
+        <v>7058002</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5600,7 +5600,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121388895</v>
+        <v>121388906</v>
       </c>
       <c r="B48" t="n">
         <v>57356</v>
@@ -5640,10 +5640,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>435847</v>
+        <v>435931</v>
       </c>
       <c r="R48" t="n">
-        <v>7058626</v>
+        <v>7057902</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5680,7 +5680,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>ringhack färska till äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5707,7 +5707,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121388928</v>
+        <v>121388919</v>
       </c>
       <c r="B49" t="n">
         <v>57356</v>
@@ -5747,10 +5747,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>435802</v>
+        <v>435924</v>
       </c>
       <c r="R49" t="n">
-        <v>7058016</v>
+        <v>7057563</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5814,7 +5814,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121388947</v>
+        <v>121388923</v>
       </c>
       <c r="B50" t="n">
         <v>57356</v>
@@ -5854,10 +5854,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>435805</v>
+        <v>435967</v>
       </c>
       <c r="R50" t="n">
-        <v>7058511</v>
+        <v>7057788</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5894,7 +5894,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5921,7 +5921,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121388912</v>
+        <v>121388908</v>
       </c>
       <c r="B51" t="n">
         <v>57356</v>
@@ -5961,10 +5961,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>436005</v>
+        <v>436018</v>
       </c>
       <c r="R51" t="n">
-        <v>7057657</v>
+        <v>7057811</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6028,7 +6028,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121388932</v>
+        <v>121388909</v>
       </c>
       <c r="B52" t="n">
         <v>57356</v>
@@ -6068,10 +6068,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>435890</v>
+        <v>436008</v>
       </c>
       <c r="R52" t="n">
-        <v>7058190</v>
+        <v>7057730</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6108,7 +6108,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6135,7 +6135,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121388904</v>
+        <v>121388896</v>
       </c>
       <c r="B53" t="n">
         <v>57356</v>
@@ -6175,10 +6175,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>435893</v>
+        <v>435860</v>
       </c>
       <c r="R53" t="n">
-        <v>7058002</v>
+        <v>7058614</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6215,7 +6215,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6242,7 +6242,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121388927</v>
+        <v>121388924</v>
       </c>
       <c r="B54" t="n">
         <v>57356</v>
@@ -6282,10 +6282,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>435855</v>
+        <v>435972</v>
       </c>
       <c r="R54" t="n">
-        <v>7057933</v>
+        <v>7057798</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6322,7 +6322,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6349,7 +6349,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121388951</v>
+        <v>121388949</v>
       </c>
       <c r="B55" t="n">
         <v>57356</v>
@@ -6389,10 +6389,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>435794</v>
+        <v>435790</v>
       </c>
       <c r="R55" t="n">
-        <v>7058714</v>
+        <v>7058674</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6456,7 +6456,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121388901</v>
+        <v>121388921</v>
       </c>
       <c r="B56" t="n">
         <v>57356</v>
@@ -6496,10 +6496,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>435925</v>
+        <v>435927</v>
       </c>
       <c r="R56" t="n">
-        <v>7058082</v>
+        <v>7057591</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6563,7 +6563,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121388915</v>
+        <v>121388943</v>
       </c>
       <c r="B57" t="n">
         <v>57356</v>
@@ -6603,10 +6603,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>435989</v>
+        <v>435742</v>
       </c>
       <c r="R57" t="n">
-        <v>7057570</v>
+        <v>7058327</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6670,7 +6670,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121388910</v>
+        <v>121388934</v>
       </c>
       <c r="B58" t="n">
         <v>57356</v>
@@ -6710,10 +6710,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>436007</v>
+        <v>435875</v>
       </c>
       <c r="R58" t="n">
-        <v>7057694</v>
+        <v>7058202</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6750,7 +6750,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6777,7 +6777,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121388905</v>
+        <v>121388951</v>
       </c>
       <c r="B59" t="n">
         <v>57356</v>
@@ -6817,10 +6817,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>435889</v>
+        <v>435794</v>
       </c>
       <c r="R59" t="n">
-        <v>7057953</v>
+        <v>7058714</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6884,7 +6884,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121388921</v>
+        <v>121388931</v>
       </c>
       <c r="B60" t="n">
         <v>57356</v>
@@ -6924,10 +6924,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>435927</v>
+        <v>435865</v>
       </c>
       <c r="R60" t="n">
-        <v>7057591</v>
+        <v>7058110</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6964,7 +6964,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6991,7 +6991,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121388944</v>
+        <v>121388925</v>
       </c>
       <c r="B61" t="n">
         <v>57356</v>
@@ -7031,10 +7031,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>435747</v>
+        <v>435850</v>
       </c>
       <c r="R61" t="n">
-        <v>7058359</v>
+        <v>7057928</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7071,7 +7071,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>ringhack på tall</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD61" t="b">

--- a/artfynd/A 38630-2024 artfynd.xlsx
+++ b/artfynd/A 38630-2024 artfynd.xlsx
@@ -4527,10 +4527,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121388900</v>
+        <v>121388953</v>
       </c>
       <c r="B38" t="n">
-        <v>57356</v>
+        <v>57509</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4543,34 +4543,42 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Ångsjön, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>435952</v>
+        <v>435836</v>
       </c>
       <c r="R38" t="n">
-        <v>7058237</v>
+        <v>7058421</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4603,11 +4611,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2024-11-28</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4634,7 +4637,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121388911</v>
+        <v>121388898</v>
       </c>
       <c r="B39" t="n">
         <v>57356</v>
@@ -4674,10 +4677,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>436006</v>
+        <v>435841</v>
       </c>
       <c r="R39" t="n">
-        <v>7057655</v>
+        <v>7058582</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4714,7 +4717,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4741,7 +4744,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121388920</v>
+        <v>121388900</v>
       </c>
       <c r="B40" t="n">
         <v>57356</v>
@@ -4781,10 +4784,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>435928</v>
+        <v>435952</v>
       </c>
       <c r="R40" t="n">
-        <v>7057577</v>
+        <v>7058237</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4821,7 +4824,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4848,7 +4851,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121388939</v>
+        <v>121388911</v>
       </c>
       <c r="B41" t="n">
         <v>57356</v>
@@ -4888,10 +4891,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>435870</v>
+        <v>436006</v>
       </c>
       <c r="R41" t="n">
-        <v>7058288</v>
+        <v>7057655</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4955,7 +4958,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121388898</v>
+        <v>121388920</v>
       </c>
       <c r="B42" t="n">
         <v>57356</v>
@@ -4995,10 +4998,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>435841</v>
+        <v>435928</v>
       </c>
       <c r="R42" t="n">
-        <v>7058582</v>
+        <v>7057577</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5035,7 +5038,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5062,10 +5065,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121388953</v>
+        <v>121388939</v>
       </c>
       <c r="B43" t="n">
-        <v>57509</v>
+        <v>57356</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5078,42 +5081,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Ångsjön, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>435836</v>
+        <v>435870</v>
       </c>
       <c r="R43" t="n">
-        <v>7058421</v>
+        <v>7058288</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5146,6 +5141,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2024-11-28</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5600,7 +5600,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121388906</v>
+        <v>121388919</v>
       </c>
       <c r="B48" t="n">
         <v>57356</v>
@@ -5640,10 +5640,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>435931</v>
+        <v>435924</v>
       </c>
       <c r="R48" t="n">
-        <v>7057902</v>
+        <v>7057563</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5680,7 +5680,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5707,7 +5707,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121388919</v>
+        <v>121388906</v>
       </c>
       <c r="B49" t="n">
         <v>57356</v>
@@ -5747,10 +5747,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>435924</v>
+        <v>435931</v>
       </c>
       <c r="R49" t="n">
-        <v>7057563</v>
+        <v>7057902</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5787,7 +5787,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD49" t="b">

--- a/artfynd/A 38630-2024 artfynd.xlsx
+++ b/artfynd/A 38630-2024 artfynd.xlsx
@@ -5814,7 +5814,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121388923</v>
+        <v>121388909</v>
       </c>
       <c r="B50" t="n">
         <v>57356</v>
@@ -5854,10 +5854,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>435967</v>
+        <v>436008</v>
       </c>
       <c r="R50" t="n">
-        <v>7057788</v>
+        <v>7057730</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5894,7 +5894,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5921,7 +5921,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121388908</v>
+        <v>121388923</v>
       </c>
       <c r="B51" t="n">
         <v>57356</v>
@@ -5961,10 +5961,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>436018</v>
+        <v>435967</v>
       </c>
       <c r="R51" t="n">
-        <v>7057811</v>
+        <v>7057788</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6001,7 +6001,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6028,7 +6028,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121388909</v>
+        <v>121388908</v>
       </c>
       <c r="B52" t="n">
         <v>57356</v>
@@ -6068,10 +6068,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>436008</v>
+        <v>436018</v>
       </c>
       <c r="R52" t="n">
-        <v>7057730</v>
+        <v>7057811</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6242,7 +6242,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121388924</v>
+        <v>121388949</v>
       </c>
       <c r="B54" t="n">
         <v>57356</v>
@@ -6282,10 +6282,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>435972</v>
+        <v>435790</v>
       </c>
       <c r="R54" t="n">
-        <v>7057798</v>
+        <v>7058674</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6322,7 +6322,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6349,7 +6349,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121388949</v>
+        <v>121388924</v>
       </c>
       <c r="B55" t="n">
         <v>57356</v>
@@ -6389,10 +6389,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>435790</v>
+        <v>435972</v>
       </c>
       <c r="R55" t="n">
-        <v>7058674</v>
+        <v>7057798</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6429,7 +6429,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD55" t="b">

--- a/artfynd/A 38630-2024 artfynd.xlsx
+++ b/artfynd/A 38630-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121388915</v>
+        <v>121388897</v>
       </c>
       <c r="B2" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>435989</v>
+        <v>435853</v>
       </c>
       <c r="R2" t="n">
-        <v>7057570</v>
+        <v>7058608</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121388932</v>
+        <v>121388952</v>
       </c>
       <c r="B3" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>435890</v>
+        <v>435812</v>
       </c>
       <c r="R3" t="n">
-        <v>7058190</v>
+        <v>7058763</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121388914</v>
+        <v>121388933</v>
       </c>
       <c r="B4" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>435985</v>
+        <v>435884</v>
       </c>
       <c r="R4" t="n">
-        <v>7057600</v>
+        <v>7058208</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121388946</v>
+        <v>121388904</v>
       </c>
       <c r="B5" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>435771</v>
+        <v>435893</v>
       </c>
       <c r="R5" t="n">
-        <v>7058417</v>
+        <v>7058002</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>ringhack färska till äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121388893</v>
+        <v>121388924</v>
       </c>
       <c r="B6" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>435833</v>
+        <v>435972</v>
       </c>
       <c r="R6" t="n">
-        <v>7058665</v>
+        <v>7057798</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1210,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121388950</v>
+        <v>121388936</v>
       </c>
       <c r="B7" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1250,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>435782</v>
+        <v>435878</v>
       </c>
       <c r="R7" t="n">
-        <v>7058658</v>
+        <v>7058242</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1290,7 +1290,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121388913</v>
+        <v>121388898</v>
       </c>
       <c r="B8" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>436005</v>
+        <v>435841</v>
       </c>
       <c r="R8" t="n">
-        <v>7057639</v>
+        <v>7058582</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1397,7 +1397,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1424,10 +1424,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121388935</v>
+        <v>121388951</v>
       </c>
       <c r="B9" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1464,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>435868</v>
+        <v>435794</v>
       </c>
       <c r="R9" t="n">
-        <v>7058203</v>
+        <v>7058714</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1531,10 +1531,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121388941</v>
+        <v>121388949</v>
       </c>
       <c r="B10" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1571,10 +1571,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>435759</v>
+        <v>435790</v>
       </c>
       <c r="R10" t="n">
-        <v>7058331</v>
+        <v>7058674</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1611,7 +1611,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1638,10 +1638,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121388952</v>
+        <v>121388953</v>
       </c>
       <c r="B11" t="n">
-        <v>57356</v>
+        <v>57510</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1654,34 +1654,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Ångsjön, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>435812</v>
+        <v>435836</v>
       </c>
       <c r="R11" t="n">
-        <v>7058763</v>
+        <v>7058421</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1714,11 +1722,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-11-28</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1745,10 +1748,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121388894</v>
+        <v>121388937</v>
       </c>
       <c r="B12" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1785,10 +1788,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>435836</v>
+        <v>435873</v>
       </c>
       <c r="R12" t="n">
-        <v>7058627</v>
+        <v>7058244</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1825,7 +1828,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1852,10 +1855,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121388930</v>
+        <v>121388939</v>
       </c>
       <c r="B13" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1892,10 +1895,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>435898</v>
+        <v>435870</v>
       </c>
       <c r="R13" t="n">
-        <v>7058090</v>
+        <v>7058288</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1932,7 +1935,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1959,10 +1962,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121388926</v>
+        <v>121388894</v>
       </c>
       <c r="B14" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1999,10 +2002,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>435857</v>
+        <v>435836</v>
       </c>
       <c r="R14" t="n">
-        <v>7057933</v>
+        <v>7058627</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2039,7 +2042,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2066,10 +2069,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121388899</v>
+        <v>121388931</v>
       </c>
       <c r="B15" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2109,7 +2112,7 @@
         <v>435865</v>
       </c>
       <c r="R15" t="n">
-        <v>7058514</v>
+        <v>7058110</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2146,7 +2149,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2173,10 +2176,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121388933</v>
+        <v>121388926</v>
       </c>
       <c r="B16" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2213,10 +2216,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>435884</v>
+        <v>435857</v>
       </c>
       <c r="R16" t="n">
-        <v>7058208</v>
+        <v>7057933</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2280,10 +2283,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121388910</v>
+        <v>121388900</v>
       </c>
       <c r="B17" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2320,10 +2323,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>436007</v>
+        <v>435952</v>
       </c>
       <c r="R17" t="n">
-        <v>7057694</v>
+        <v>7058237</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2387,10 +2390,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121388947</v>
+        <v>121388911</v>
       </c>
       <c r="B18" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2427,10 +2430,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>435805</v>
+        <v>436006</v>
       </c>
       <c r="R18" t="n">
-        <v>7058511</v>
+        <v>7057655</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2494,10 +2497,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121388945</v>
+        <v>121388905</v>
       </c>
       <c r="B19" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2534,10 +2537,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>435762</v>
+        <v>435889</v>
       </c>
       <c r="R19" t="n">
-        <v>7058369</v>
+        <v>7057953</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2574,7 +2577,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2601,10 +2604,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121388903</v>
+        <v>121388917</v>
       </c>
       <c r="B20" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2641,10 +2644,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>435913</v>
+        <v>435975</v>
       </c>
       <c r="R20" t="n">
-        <v>7058004</v>
+        <v>7057462</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2681,7 +2684,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>ringhack färska till äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2708,10 +2711,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121388907</v>
+        <v>121388921</v>
       </c>
       <c r="B21" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2748,10 +2751,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>435997</v>
+        <v>435927</v>
       </c>
       <c r="R21" t="n">
-        <v>7057821</v>
+        <v>7057591</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2815,10 +2818,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121388916</v>
+        <v>121388927</v>
       </c>
       <c r="B22" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2855,10 +2858,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>435983</v>
+        <v>435855</v>
       </c>
       <c r="R22" t="n">
-        <v>7057467</v>
+        <v>7057933</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2895,7 +2898,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2922,10 +2925,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121388948</v>
+        <v>121388935</v>
       </c>
       <c r="B23" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2962,10 +2965,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>435777</v>
+        <v>435868</v>
       </c>
       <c r="R23" t="n">
-        <v>7058633</v>
+        <v>7058203</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3002,7 +3005,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3029,10 +3032,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121388928</v>
+        <v>121388906</v>
       </c>
       <c r="B24" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3069,10 +3072,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>435802</v>
+        <v>435931</v>
       </c>
       <c r="R24" t="n">
-        <v>7058016</v>
+        <v>7057902</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3109,7 +3112,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3136,10 +3139,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121388937</v>
+        <v>121388932</v>
       </c>
       <c r="B25" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3176,10 +3179,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>435873</v>
+        <v>435890</v>
       </c>
       <c r="R25" t="n">
-        <v>7058244</v>
+        <v>7058190</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3243,10 +3246,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121388897</v>
+        <v>121388947</v>
       </c>
       <c r="B26" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3283,10 +3286,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>435853</v>
+        <v>435805</v>
       </c>
       <c r="R26" t="n">
-        <v>7058608</v>
+        <v>7058511</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3323,7 +3326,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3350,10 +3353,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121388927</v>
+        <v>121388946</v>
       </c>
       <c r="B27" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3390,10 +3393,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>435855</v>
+        <v>435771</v>
       </c>
       <c r="R27" t="n">
-        <v>7057933</v>
+        <v>7058417</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3430,7 +3433,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3457,10 +3460,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121388938</v>
+        <v>121388923</v>
       </c>
       <c r="B28" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3497,10 +3500,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>435877</v>
+        <v>435967</v>
       </c>
       <c r="R28" t="n">
-        <v>7058290</v>
+        <v>7057788</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3537,7 +3540,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>ringhack färska till äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3564,10 +3567,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121388905</v>
+        <v>121388938</v>
       </c>
       <c r="B29" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3604,10 +3607,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>435889</v>
+        <v>435877</v>
       </c>
       <c r="R29" t="n">
-        <v>7057953</v>
+        <v>7058290</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3644,7 +3647,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3671,10 +3674,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121388895</v>
+        <v>121388940</v>
       </c>
       <c r="B30" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3711,10 +3714,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>435847</v>
+        <v>435760</v>
       </c>
       <c r="R30" t="n">
-        <v>7058626</v>
+        <v>7058327</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3751,7 +3754,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>ringhack färska till äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3778,10 +3781,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121388940</v>
+        <v>121388928</v>
       </c>
       <c r="B31" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3818,10 +3821,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>435760</v>
+        <v>435802</v>
       </c>
       <c r="R31" t="n">
-        <v>7058327</v>
+        <v>7058016</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3858,7 +3861,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3885,10 +3888,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121388902</v>
+        <v>121388929</v>
       </c>
       <c r="B32" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3925,10 +3928,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>435918</v>
+        <v>435896</v>
       </c>
       <c r="R32" t="n">
-        <v>7058070</v>
+        <v>7058085</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3965,7 +3968,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3992,10 +3995,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121388929</v>
+        <v>121388901</v>
       </c>
       <c r="B33" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4032,10 +4035,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>435896</v>
+        <v>435925</v>
       </c>
       <c r="R33" t="n">
-        <v>7058085</v>
+        <v>7058082</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4072,7 +4075,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4099,10 +4102,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121388918</v>
+        <v>121388909</v>
       </c>
       <c r="B34" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4139,10 +4142,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>435965</v>
+        <v>436008</v>
       </c>
       <c r="R34" t="n">
-        <v>7057511</v>
+        <v>7057730</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4179,7 +4182,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4209,7 +4212,7 @@
         <v>121388912</v>
       </c>
       <c r="B35" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4313,10 +4316,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121388936</v>
+        <v>121388920</v>
       </c>
       <c r="B36" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4353,10 +4356,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>435878</v>
+        <v>435928</v>
       </c>
       <c r="R36" t="n">
-        <v>7058242</v>
+        <v>7057577</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4420,10 +4423,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121388944</v>
+        <v>121388942</v>
       </c>
       <c r="B37" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4460,10 +4463,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>435747</v>
+        <v>435757</v>
       </c>
       <c r="R37" t="n">
-        <v>7058359</v>
+        <v>7058329</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4500,7 +4503,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>ringhack på tall</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4527,10 +4530,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121388953</v>
+        <v>121388915</v>
       </c>
       <c r="B38" t="n">
-        <v>57509</v>
+        <v>57357</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4543,42 +4546,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Ångsjön, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>435836</v>
+        <v>435989</v>
       </c>
       <c r="R38" t="n">
-        <v>7058421</v>
+        <v>7057570</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4611,6 +4606,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2024-11-28</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4637,10 +4637,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121388898</v>
+        <v>121388908</v>
       </c>
       <c r="B39" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4677,10 +4677,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>435841</v>
+        <v>436018</v>
       </c>
       <c r="R39" t="n">
-        <v>7058582</v>
+        <v>7057811</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4744,10 +4744,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121388900</v>
+        <v>121388950</v>
       </c>
       <c r="B40" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4784,10 +4784,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>435952</v>
+        <v>435782</v>
       </c>
       <c r="R40" t="n">
-        <v>7058237</v>
+        <v>7058658</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4824,7 +4824,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4851,10 +4851,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121388911</v>
+        <v>121388919</v>
       </c>
       <c r="B41" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4891,10 +4891,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>436006</v>
+        <v>435924</v>
       </c>
       <c r="R41" t="n">
-        <v>7057655</v>
+        <v>7057563</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4958,10 +4958,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121388920</v>
+        <v>121388916</v>
       </c>
       <c r="B42" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4998,10 +4998,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>435928</v>
+        <v>435983</v>
       </c>
       <c r="R42" t="n">
-        <v>7057577</v>
+        <v>7057467</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5038,7 +5038,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5065,10 +5065,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121388939</v>
+        <v>121388945</v>
       </c>
       <c r="B43" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5105,10 +5105,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>435870</v>
+        <v>435762</v>
       </c>
       <c r="R43" t="n">
-        <v>7058288</v>
+        <v>7058369</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5172,10 +5172,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121388942</v>
+        <v>121388899</v>
       </c>
       <c r="B44" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5212,10 +5212,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>435757</v>
+        <v>435865</v>
       </c>
       <c r="R44" t="n">
-        <v>7058329</v>
+        <v>7058514</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5252,7 +5252,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5279,10 +5279,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121388901</v>
+        <v>121388896</v>
       </c>
       <c r="B45" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5319,10 +5319,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>435925</v>
+        <v>435860</v>
       </c>
       <c r="R45" t="n">
-        <v>7058082</v>
+        <v>7058614</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5359,7 +5359,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5386,10 +5386,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121388917</v>
+        <v>121388944</v>
       </c>
       <c r="B46" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5426,10 +5426,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>435975</v>
+        <v>435747</v>
       </c>
       <c r="R46" t="n">
-        <v>7057462</v>
+        <v>7058359</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5466,7 +5466,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack på tall</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5493,10 +5493,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121388904</v>
+        <v>121388925</v>
       </c>
       <c r="B47" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5533,10 +5533,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>435893</v>
+        <v>435850</v>
       </c>
       <c r="R47" t="n">
-        <v>7058002</v>
+        <v>7057928</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5573,7 +5573,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5600,10 +5600,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121388919</v>
+        <v>121388914</v>
       </c>
       <c r="B48" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5640,10 +5640,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>435924</v>
+        <v>435985</v>
       </c>
       <c r="R48" t="n">
-        <v>7057563</v>
+        <v>7057600</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5680,7 +5680,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5707,10 +5707,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121388906</v>
+        <v>121388893</v>
       </c>
       <c r="B49" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5747,10 +5747,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>435931</v>
+        <v>435833</v>
       </c>
       <c r="R49" t="n">
-        <v>7057902</v>
+        <v>7058665</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5787,7 +5787,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5814,10 +5814,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121388909</v>
+        <v>121388943</v>
       </c>
       <c r="B50" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5854,10 +5854,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>436008</v>
+        <v>435742</v>
       </c>
       <c r="R50" t="n">
-        <v>7057730</v>
+        <v>7058327</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5894,7 +5894,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5921,10 +5921,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121388923</v>
+        <v>121388895</v>
       </c>
       <c r="B51" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5961,10 +5961,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>435967</v>
+        <v>435847</v>
       </c>
       <c r="R51" t="n">
-        <v>7057788</v>
+        <v>7058626</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6001,7 +6001,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6028,10 +6028,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121388908</v>
+        <v>121388903</v>
       </c>
       <c r="B52" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6068,10 +6068,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>436018</v>
+        <v>435913</v>
       </c>
       <c r="R52" t="n">
-        <v>7057811</v>
+        <v>7058004</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6108,7 +6108,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6135,10 +6135,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121388896</v>
+        <v>121388948</v>
       </c>
       <c r="B53" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6175,10 +6175,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>435860</v>
+        <v>435777</v>
       </c>
       <c r="R53" t="n">
-        <v>7058614</v>
+        <v>7058633</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6215,7 +6215,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6242,10 +6242,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121388949</v>
+        <v>121388941</v>
       </c>
       <c r="B54" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6282,10 +6282,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>435790</v>
+        <v>435759</v>
       </c>
       <c r="R54" t="n">
-        <v>7058674</v>
+        <v>7058331</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6322,7 +6322,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6349,10 +6349,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121388924</v>
+        <v>121388910</v>
       </c>
       <c r="B55" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6389,10 +6389,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>435972</v>
+        <v>436007</v>
       </c>
       <c r="R55" t="n">
-        <v>7057798</v>
+        <v>7057694</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6429,7 +6429,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6456,10 +6456,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121388921</v>
+        <v>121388918</v>
       </c>
       <c r="B56" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6496,10 +6496,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>435927</v>
+        <v>435965</v>
       </c>
       <c r="R56" t="n">
-        <v>7057591</v>
+        <v>7057511</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6536,7 +6536,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6563,10 +6563,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121388943</v>
+        <v>121388930</v>
       </c>
       <c r="B57" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6603,10 +6603,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>435742</v>
+        <v>435898</v>
       </c>
       <c r="R57" t="n">
-        <v>7058327</v>
+        <v>7058090</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6643,7 +6643,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6670,10 +6670,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121388934</v>
+        <v>121388913</v>
       </c>
       <c r="B58" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6710,10 +6710,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>435875</v>
+        <v>436005</v>
       </c>
       <c r="R58" t="n">
-        <v>7058202</v>
+        <v>7057639</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6750,7 +6750,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6777,10 +6777,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121388951</v>
+        <v>121388907</v>
       </c>
       <c r="B59" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6817,10 +6817,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>435794</v>
+        <v>435997</v>
       </c>
       <c r="R59" t="n">
-        <v>7058714</v>
+        <v>7057821</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6857,7 +6857,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6884,10 +6884,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121388931</v>
+        <v>121388934</v>
       </c>
       <c r="B60" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6924,10 +6924,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>435865</v>
+        <v>435875</v>
       </c>
       <c r="R60" t="n">
-        <v>7058110</v>
+        <v>7058202</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6964,7 +6964,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6991,10 +6991,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121388925</v>
+        <v>121388902</v>
       </c>
       <c r="B61" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7031,10 +7031,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>435850</v>
+        <v>435918</v>
       </c>
       <c r="R61" t="n">
-        <v>7057928</v>
+        <v>7058070</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7071,7 +7071,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD61" t="b">
